--- a/DecompositionLU/docs/version_3.2_statistics.xlsx
+++ b/DecompositionLU/docs/version_3.2_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36476871-5B0C-44C9-99AF-08F53CABC895}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A3883F-4249-4585-ACBF-20DC4AA82CB9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Графики" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="32">
   <si>
     <t>Замеры версии 3.2</t>
   </si>
@@ -228,6 +228,12 @@
       <t>кластер risk-V</t>
     </r>
   </si>
+  <si>
+    <t>размер блока:</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
 </sst>
 </file>
 
@@ -397,7 +403,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -477,12 +483,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -532,6 +564,36 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -540,6 +602,33 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -559,63 +648,31 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -29301,30 +29358,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="50" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="52"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="45"/>
+      <c r="T1" s="46"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -29336,15 +29393,15 @@
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -29371,7 +29428,7 @@
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
+      <c r="A3" s="39"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -29410,7 +29467,7 @@
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -29449,7 +29506,7 @@
       <c r="AC4" s="1"/>
     </row>
     <row r="5" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
+      <c r="A5" s="39"/>
       <c r="B5" s="4">
         <v>2</v>
       </c>
@@ -29488,7 +29545,7 @@
       <c r="AC5" s="1"/>
     </row>
     <row r="6" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
+      <c r="A6" s="39"/>
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -29527,7 +29584,7 @@
       <c r="AC6" s="1"/>
     </row>
     <row r="7" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
+      <c r="A7" s="39"/>
       <c r="B7" s="4">
         <v>6</v>
       </c>
@@ -29566,7 +29623,7 @@
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
+      <c r="A8" s="39"/>
       <c r="B8" s="4">
         <v>8</v>
       </c>
@@ -29605,7 +29662,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="4">
         <v>10</v>
       </c>
@@ -29644,7 +29701,7 @@
       <c r="AC9" s="1"/>
     </row>
     <row r="10" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
+      <c r="A10" s="39"/>
       <c r="B10" s="4">
         <v>12</v>
       </c>
@@ -29683,7 +29740,7 @@
       <c r="AC10" s="1"/>
     </row>
     <row r="11" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
+      <c r="A11" s="39"/>
       <c r="B11" s="4">
         <v>16</v>
       </c>
@@ -29722,13 +29779,13 @@
       <c r="AC11" s="1"/>
     </row>
     <row r="12" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
-      <c r="B12" s="22" t="s">
+      <c r="A12" s="39"/>
+      <c r="B12" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="24"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="49"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -29755,7 +29812,7 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
+      <c r="A13" s="39"/>
       <c r="B13" s="3" t="s">
         <v>4</v>
       </c>
@@ -29794,7 +29851,7 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
+      <c r="A14" s="39"/>
       <c r="B14" s="3">
         <v>1</v>
       </c>
@@ -29836,7 +29893,7 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="3">
         <v>2</v>
       </c>
@@ -29878,7 +29935,7 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
+      <c r="A16" s="39"/>
       <c r="B16" s="3">
         <v>4</v>
       </c>
@@ -29920,7 +29977,7 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="3">
         <v>6</v>
       </c>
@@ -29962,7 +30019,7 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="3">
         <v>8</v>
       </c>
@@ -30004,7 +30061,7 @@
       <c r="AC18" s="1"/>
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
+      <c r="A19" s="39"/>
       <c r="B19" s="3">
         <v>10</v>
       </c>
@@ -30046,7 +30103,7 @@
       <c r="AC19" s="1"/>
     </row>
     <row r="20" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
+      <c r="A20" s="39"/>
       <c r="B20" s="3">
         <v>12</v>
       </c>
@@ -30088,7 +30145,7 @@
       <c r="AC20" s="1"/>
     </row>
     <row r="21" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
+      <c r="A21" s="39"/>
       <c r="B21" s="3">
         <v>16</v>
       </c>
@@ -30130,13 +30187,13 @@
       <c r="AC21" s="1"/>
     </row>
     <row r="22" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="39"/>
+      <c r="B22" s="47" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="24"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="49"/>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -30163,7 +30220,7 @@
       <c r="AC22" s="1"/>
     </row>
     <row r="23" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
+      <c r="A23" s="39"/>
       <c r="B23" s="3" t="s">
         <v>4</v>
       </c>
@@ -30202,7 +30259,7 @@
       <c r="AC23" s="1"/>
     </row>
     <row r="24" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28"/>
+      <c r="A24" s="39"/>
       <c r="B24" s="3">
         <v>1</v>
       </c>
@@ -30244,7 +30301,7 @@
       <c r="AC24" s="1"/>
     </row>
     <row r="25" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
+      <c r="A25" s="39"/>
       <c r="B25" s="3">
         <v>2</v>
       </c>
@@ -30286,7 +30343,7 @@
       <c r="AC25" s="1"/>
     </row>
     <row r="26" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
+      <c r="A26" s="39"/>
       <c r="B26" s="3">
         <v>4</v>
       </c>
@@ -30328,7 +30385,7 @@
       <c r="AC26" s="1"/>
     </row>
     <row r="27" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
+      <c r="A27" s="39"/>
       <c r="B27" s="3">
         <v>6</v>
       </c>
@@ -30370,7 +30427,7 @@
       <c r="AC27" s="1"/>
     </row>
     <row r="28" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
+      <c r="A28" s="39"/>
       <c r="B28" s="3">
         <v>8</v>
       </c>
@@ -30412,7 +30469,7 @@
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
+      <c r="A29" s="39"/>
       <c r="B29" s="3">
         <v>10</v>
       </c>
@@ -30454,7 +30511,7 @@
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
+      <c r="A30" s="39"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
@@ -30496,7 +30553,7 @@
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="3">
         <v>16</v>
       </c>
@@ -30538,30 +30595,30 @@
       <c r="AC31" s="1"/>
     </row>
     <row r="32" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
+      <c r="A32" s="39"/>
       <c r="B32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="26"/>
-      <c r="O32" s="26"/>
-      <c r="P32" s="26"/>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="26"/>
-      <c r="S32" s="26"/>
-      <c r="T32" s="27"/>
+      <c r="D32" s="51"/>
+      <c r="E32" s="51"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="51"/>
+      <c r="H32" s="51"/>
+      <c r="I32" s="51"/>
+      <c r="J32" s="51"/>
+      <c r="K32" s="51"/>
+      <c r="L32" s="51"/>
+      <c r="M32" s="51"/>
+      <c r="N32" s="51"/>
+      <c r="O32" s="51"/>
+      <c r="P32" s="51"/>
+      <c r="Q32" s="51"/>
+      <c r="R32" s="51"/>
+      <c r="S32" s="51"/>
+      <c r="T32" s="52"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -30573,15 +30630,15 @@
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -30604,11 +30661,11 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
-      <c r="AB33" s="33"/>
-      <c r="AC33" s="33"/>
+      <c r="AB33" s="19"/>
+      <c r="AC33" s="19"/>
     </row>
     <row r="34" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="21"/>
+      <c r="A34" s="37"/>
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
@@ -30643,11 +30700,11 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
       <c r="AA34" s="2"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
+      <c r="AB34" s="19"/>
+      <c r="AC34" s="19"/>
     </row>
     <row r="35" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21"/>
+      <c r="A35" s="37"/>
       <c r="B35" s="4">
         <v>1</v>
       </c>
@@ -30682,11 +30739,11 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
-      <c r="AB35" s="33"/>
-      <c r="AC35" s="33"/>
+      <c r="AB35" s="19"/>
+      <c r="AC35" s="19"/>
     </row>
     <row r="36" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
+      <c r="A36" s="37"/>
       <c r="B36" s="4">
         <v>2</v>
       </c>
@@ -30721,11 +30778,11 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
       <c r="AA36" s="2"/>
-      <c r="AB36" s="33"/>
-      <c r="AC36" s="33"/>
+      <c r="AB36" s="19"/>
+      <c r="AC36" s="19"/>
     </row>
     <row r="37" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21"/>
+      <c r="A37" s="37"/>
       <c r="B37" s="4">
         <v>4</v>
       </c>
@@ -30760,11 +30817,11 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
-      <c r="AB37" s="33"/>
-      <c r="AC37" s="33"/>
+      <c r="AB37" s="19"/>
+      <c r="AC37" s="19"/>
     </row>
     <row r="38" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21"/>
+      <c r="A38" s="37"/>
       <c r="B38" s="4">
         <v>6</v>
       </c>
@@ -30799,11 +30856,11 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
-      <c r="AB38" s="33"/>
-      <c r="AC38" s="33"/>
+      <c r="AB38" s="19"/>
+      <c r="AC38" s="19"/>
     </row>
     <row r="39" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="21"/>
+      <c r="A39" s="37"/>
       <c r="B39" s="4">
         <v>8</v>
       </c>
@@ -30838,11 +30895,11 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
+      <c r="AB39" s="19"/>
+      <c r="AC39" s="19"/>
     </row>
     <row r="40" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="21"/>
+      <c r="A40" s="37"/>
       <c r="B40" s="4">
         <v>10</v>
       </c>
@@ -30877,11 +30934,11 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
-      <c r="AB40" s="33"/>
-      <c r="AC40" s="33"/>
+      <c r="AB40" s="19"/>
+      <c r="AC40" s="19"/>
     </row>
     <row r="41" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="21"/>
+      <c r="A41" s="37"/>
       <c r="B41" s="4">
         <v>12</v>
       </c>
@@ -30916,11 +30973,11 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
-      <c r="AB41" s="33"/>
-      <c r="AC41" s="33"/>
+      <c r="AB41" s="19"/>
+      <c r="AC41" s="19"/>
     </row>
     <row r="42" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="21"/>
+      <c r="A42" s="37"/>
       <c r="B42" s="4">
         <v>14</v>
       </c>
@@ -30955,11 +31012,11 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
       <c r="AA42" s="2"/>
-      <c r="AB42" s="33"/>
-      <c r="AC42" s="33"/>
+      <c r="AB42" s="19"/>
+      <c r="AC42" s="19"/>
     </row>
     <row r="43" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21"/>
+      <c r="A43" s="37"/>
       <c r="B43" s="4">
         <v>16</v>
       </c>
@@ -30994,11 +31051,11 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
       <c r="AA43" s="2"/>
-      <c r="AB43" s="33"/>
-      <c r="AC43" s="33"/>
+      <c r="AB43" s="19"/>
+      <c r="AC43" s="19"/>
     </row>
     <row r="44" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="21"/>
+      <c r="A44" s="37"/>
       <c r="B44" s="4">
         <v>18</v>
       </c>
@@ -31033,11 +31090,11 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
-      <c r="AB44" s="33"/>
-      <c r="AC44" s="33"/>
+      <c r="AB44" s="19"/>
+      <c r="AC44" s="19"/>
     </row>
     <row r="45" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="21"/>
+      <c r="A45" s="37"/>
       <c r="B45" s="4">
         <v>20</v>
       </c>
@@ -31072,11 +31129,11 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
       <c r="AA45" s="2"/>
-      <c r="AB45" s="33"/>
-      <c r="AC45" s="33"/>
+      <c r="AB45" s="19"/>
+      <c r="AC45" s="19"/>
     </row>
     <row r="46" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="21"/>
+      <c r="A46" s="37"/>
       <c r="B46" s="10">
         <v>40</v>
       </c>
@@ -31111,17 +31168,17 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
       <c r="AA46" s="2"/>
-      <c r="AB46" s="33"/>
-      <c r="AC46" s="33"/>
+      <c r="AB46" s="19"/>
+      <c r="AC46" s="19"/>
     </row>
     <row r="47" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="21"/>
-      <c r="B47" s="29" t="s">
+      <c r="A47" s="37"/>
+      <c r="B47" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38"/>
+      <c r="E47" s="38"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -31144,11 +31201,11 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
       <c r="AA47" s="2"/>
-      <c r="AB47" s="33"/>
-      <c r="AC47" s="33"/>
+      <c r="AB47" s="19"/>
+      <c r="AC47" s="19"/>
     </row>
     <row r="48" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="21"/>
+      <c r="A48" s="37"/>
       <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
@@ -31183,11 +31240,11 @@
       <c r="Y48" s="8"/>
       <c r="Z48" s="8"/>
       <c r="AA48" s="8"/>
-      <c r="AB48" s="34"/>
-      <c r="AC48" s="34"/>
+      <c r="AB48" s="20"/>
+      <c r="AC48" s="20"/>
     </row>
     <row r="49" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="21"/>
+      <c r="A49" s="37"/>
       <c r="B49" s="4">
         <v>1</v>
       </c>
@@ -31225,11 +31282,11 @@
       <c r="Y49" s="8"/>
       <c r="Z49" s="8"/>
       <c r="AA49" s="8"/>
-      <c r="AB49" s="34"/>
-      <c r="AC49" s="34"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
     </row>
     <row r="50" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="21"/>
+      <c r="A50" s="37"/>
       <c r="B50" s="4">
         <v>2</v>
       </c>
@@ -31267,11 +31324,11 @@
       <c r="Y50" s="8"/>
       <c r="Z50" s="8"/>
       <c r="AA50" s="8"/>
-      <c r="AB50" s="34"/>
-      <c r="AC50" s="34"/>
+      <c r="AB50" s="20"/>
+      <c r="AC50" s="20"/>
     </row>
     <row r="51" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="21"/>
+      <c r="A51" s="37"/>
       <c r="B51" s="4">
         <v>4</v>
       </c>
@@ -31309,11 +31366,11 @@
       <c r="Y51" s="8"/>
       <c r="Z51" s="8"/>
       <c r="AA51" s="8"/>
-      <c r="AB51" s="34"/>
-      <c r="AC51" s="34"/>
+      <c r="AB51" s="20"/>
+      <c r="AC51" s="20"/>
     </row>
     <row r="52" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="21"/>
+      <c r="A52" s="37"/>
       <c r="B52" s="4">
         <v>6</v>
       </c>
@@ -31351,11 +31408,11 @@
       <c r="Y52" s="8"/>
       <c r="Z52" s="8"/>
       <c r="AA52" s="8"/>
-      <c r="AB52" s="34"/>
-      <c r="AC52" s="34"/>
+      <c r="AB52" s="20"/>
+      <c r="AC52" s="20"/>
     </row>
     <row r="53" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21"/>
+      <c r="A53" s="37"/>
       <c r="B53" s="13">
         <v>8</v>
       </c>
@@ -31393,11 +31450,11 @@
       <c r="Y53" s="8"/>
       <c r="Z53" s="8"/>
       <c r="AA53" s="8"/>
-      <c r="AB53" s="34"/>
-      <c r="AC53" s="34"/>
+      <c r="AB53" s="20"/>
+      <c r="AC53" s="20"/>
     </row>
     <row r="54" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="21"/>
+      <c r="A54" s="37"/>
       <c r="B54" s="4">
         <v>10</v>
       </c>
@@ -31435,11 +31492,11 @@
       <c r="Y54" s="8"/>
       <c r="Z54" s="8"/>
       <c r="AA54" s="8"/>
-      <c r="AB54" s="34"/>
-      <c r="AC54" s="34"/>
+      <c r="AB54" s="20"/>
+      <c r="AC54" s="20"/>
     </row>
     <row r="55" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="21"/>
+      <c r="A55" s="37"/>
       <c r="B55" s="4">
         <v>12</v>
       </c>
@@ -31477,11 +31534,11 @@
       <c r="Y55" s="8"/>
       <c r="Z55" s="8"/>
       <c r="AA55" s="8"/>
-      <c r="AB55" s="34"/>
-      <c r="AC55" s="34"/>
+      <c r="AB55" s="20"/>
+      <c r="AC55" s="20"/>
     </row>
     <row r="56" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="21"/>
+      <c r="A56" s="37"/>
       <c r="B56" s="4">
         <v>14</v>
       </c>
@@ -31519,11 +31576,11 @@
       <c r="Y56" s="8"/>
       <c r="Z56" s="8"/>
       <c r="AA56" s="8"/>
-      <c r="AB56" s="34"/>
-      <c r="AC56" s="34"/>
+      <c r="AB56" s="20"/>
+      <c r="AC56" s="20"/>
     </row>
     <row r="57" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="21"/>
+      <c r="A57" s="37"/>
       <c r="B57" s="4">
         <v>16</v>
       </c>
@@ -31561,11 +31618,11 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
       <c r="AA57" s="2"/>
-      <c r="AB57" s="33"/>
-      <c r="AC57" s="33"/>
+      <c r="AB57" s="19"/>
+      <c r="AC57" s="19"/>
     </row>
     <row r="58" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="21"/>
+      <c r="A58" s="37"/>
       <c r="B58" s="4">
         <v>18</v>
       </c>
@@ -31603,11 +31660,11 @@
       <c r="Y58" s="8"/>
       <c r="Z58" s="8"/>
       <c r="AA58" s="8"/>
-      <c r="AB58" s="34"/>
-      <c r="AC58" s="34"/>
+      <c r="AB58" s="20"/>
+      <c r="AC58" s="20"/>
     </row>
     <row r="59" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="21"/>
+      <c r="A59" s="37"/>
       <c r="B59" s="4">
         <v>20</v>
       </c>
@@ -31645,11 +31702,11 @@
       <c r="Y59" s="8"/>
       <c r="Z59" s="8"/>
       <c r="AA59" s="8"/>
-      <c r="AB59" s="34"/>
-      <c r="AC59" s="34"/>
+      <c r="AB59" s="20"/>
+      <c r="AC59" s="20"/>
     </row>
     <row r="60" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="21"/>
+      <c r="A60" s="37"/>
       <c r="B60" s="10">
         <v>40</v>
       </c>
@@ -31687,17 +31744,17 @@
       <c r="Y60" s="8"/>
       <c r="Z60" s="8"/>
       <c r="AA60" s="8"/>
-      <c r="AB60" s="34"/>
-      <c r="AC60" s="34"/>
+      <c r="AB60" s="20"/>
+      <c r="AC60" s="20"/>
     </row>
     <row r="61" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="21"/>
-      <c r="B61" s="29" t="s">
+      <c r="A61" s="37"/>
+      <c r="B61" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -31720,11 +31777,11 @@
       <c r="Y61" s="8"/>
       <c r="Z61" s="8"/>
       <c r="AA61" s="8"/>
-      <c r="AB61" s="34"/>
-      <c r="AC61" s="34"/>
+      <c r="AB61" s="20"/>
+      <c r="AC61" s="20"/>
     </row>
     <row r="62" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="21"/>
+      <c r="A62" s="37"/>
       <c r="B62" s="3" t="s">
         <v>4</v>
       </c>
@@ -31759,11 +31816,11 @@
       <c r="Y62" s="8"/>
       <c r="Z62" s="8"/>
       <c r="AA62" s="8"/>
-      <c r="AB62" s="34"/>
-      <c r="AC62" s="34"/>
+      <c r="AB62" s="20"/>
+      <c r="AC62" s="20"/>
     </row>
     <row r="63" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="21"/>
+      <c r="A63" s="37"/>
       <c r="B63" s="4">
         <v>1</v>
       </c>
@@ -31801,11 +31858,11 @@
       <c r="Y63" s="8"/>
       <c r="Z63" s="8"/>
       <c r="AA63" s="8"/>
-      <c r="AB63" s="34"/>
-      <c r="AC63" s="34"/>
+      <c r="AB63" s="20"/>
+      <c r="AC63" s="20"/>
     </row>
     <row r="64" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="21"/>
+      <c r="A64" s="37"/>
       <c r="B64" s="4">
         <v>2</v>
       </c>
@@ -31843,11 +31900,11 @@
       <c r="Y64" s="8"/>
       <c r="Z64" s="8"/>
       <c r="AA64" s="8"/>
-      <c r="AB64" s="34"/>
-      <c r="AC64" s="34"/>
+      <c r="AB64" s="20"/>
+      <c r="AC64" s="20"/>
     </row>
     <row r="65" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="21"/>
+      <c r="A65" s="37"/>
       <c r="B65" s="4">
         <v>4</v>
       </c>
@@ -31885,11 +31942,11 @@
       <c r="Y65" s="8"/>
       <c r="Z65" s="8"/>
       <c r="AA65" s="8"/>
-      <c r="AB65" s="34"/>
-      <c r="AC65" s="34"/>
+      <c r="AB65" s="20"/>
+      <c r="AC65" s="20"/>
     </row>
     <row r="66" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="21"/>
+      <c r="A66" s="37"/>
       <c r="B66" s="4">
         <v>6</v>
       </c>
@@ -31927,11 +31984,11 @@
       <c r="Y66" s="8"/>
       <c r="Z66" s="8"/>
       <c r="AA66" s="8"/>
-      <c r="AB66" s="34"/>
-      <c r="AC66" s="34"/>
+      <c r="AB66" s="20"/>
+      <c r="AC66" s="20"/>
     </row>
     <row r="67" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="21"/>
+      <c r="A67" s="37"/>
       <c r="B67" s="15">
         <v>8</v>
       </c>
@@ -31969,11 +32026,11 @@
       <c r="Y67" s="8"/>
       <c r="Z67" s="8"/>
       <c r="AA67" s="8"/>
-      <c r="AB67" s="34"/>
-      <c r="AC67" s="34"/>
+      <c r="AB67" s="20"/>
+      <c r="AC67" s="20"/>
     </row>
     <row r="68" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="21"/>
+      <c r="A68" s="37"/>
       <c r="B68" s="4">
         <v>10</v>
       </c>
@@ -32011,11 +32068,11 @@
       <c r="Y68" s="8"/>
       <c r="Z68" s="8"/>
       <c r="AA68" s="8"/>
-      <c r="AB68" s="34"/>
-      <c r="AC68" s="34"/>
+      <c r="AB68" s="20"/>
+      <c r="AC68" s="20"/>
     </row>
     <row r="69" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="21"/>
+      <c r="A69" s="37"/>
       <c r="B69" s="4">
         <v>12</v>
       </c>
@@ -32053,11 +32110,11 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
       <c r="AA69" s="2"/>
-      <c r="AB69" s="33"/>
-      <c r="AC69" s="33"/>
+      <c r="AB69" s="19"/>
+      <c r="AC69" s="19"/>
     </row>
     <row r="70" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="21"/>
+      <c r="A70" s="37"/>
       <c r="B70" s="4">
         <v>14</v>
       </c>
@@ -32095,11 +32152,11 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
       <c r="AA70" s="2"/>
-      <c r="AB70" s="33"/>
-      <c r="AC70" s="33"/>
+      <c r="AB70" s="19"/>
+      <c r="AC70" s="19"/>
     </row>
     <row r="71" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="21"/>
+      <c r="A71" s="37"/>
       <c r="B71" s="4">
         <v>16</v>
       </c>
@@ -32137,11 +32194,11 @@
       <c r="Y71" s="8"/>
       <c r="Z71" s="8"/>
       <c r="AA71" s="8"/>
-      <c r="AB71" s="34"/>
-      <c r="AC71" s="34"/>
+      <c r="AB71" s="20"/>
+      <c r="AC71" s="20"/>
     </row>
     <row r="72" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="21"/>
+      <c r="A72" s="37"/>
       <c r="B72" s="4">
         <v>18</v>
       </c>
@@ -32179,12 +32236,12 @@
       <c r="Y72" s="8"/>
       <c r="Z72" s="8"/>
       <c r="AA72" s="8"/>
-      <c r="AB72" s="35"/>
-      <c r="AC72" s="35"/>
-      <c r="AD72" s="36"/>
+      <c r="AB72" s="21"/>
+      <c r="AC72" s="21"/>
+      <c r="AD72" s="22"/>
     </row>
     <row r="73" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="21"/>
+      <c r="A73" s="37"/>
       <c r="B73" s="4">
         <v>20</v>
       </c>
@@ -32222,12 +32279,12 @@
       <c r="Y73" s="8"/>
       <c r="Z73" s="8"/>
       <c r="AA73" s="8"/>
-      <c r="AB73" s="35"/>
-      <c r="AC73" s="35"/>
-      <c r="AD73" s="36"/>
+      <c r="AB73" s="21"/>
+      <c r="AC73" s="21"/>
+      <c r="AD73" s="22"/>
     </row>
     <row r="74" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="21"/>
+      <c r="A74" s="37"/>
       <c r="B74" s="10">
         <v>40</v>
       </c>
@@ -32265,56 +32322,56 @@
       <c r="Y74" s="8"/>
       <c r="Z74" s="8"/>
       <c r="AA74" s="8"/>
-      <c r="AB74" s="35"/>
-      <c r="AC74" s="35"/>
-      <c r="AD74" s="36"/>
+      <c r="AB74" s="21"/>
+      <c r="AC74" s="21"/>
+      <c r="AD74" s="22"/>
     </row>
     <row r="75" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="21"/>
+      <c r="A75" s="37"/>
       <c r="B75" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="39" t="s">
+      <c r="C75" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="39"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="39"/>
-      <c r="H75" s="39"/>
-      <c r="I75" s="39"/>
-      <c r="J75" s="39"/>
-      <c r="K75" s="39"/>
-      <c r="L75" s="39"/>
-      <c r="M75" s="39"/>
-      <c r="N75" s="39"/>
-      <c r="O75" s="39"/>
-      <c r="P75" s="39"/>
-      <c r="Q75" s="39"/>
-      <c r="R75" s="39"/>
-      <c r="S75" s="39"/>
-      <c r="T75" s="39"/>
-      <c r="U75" s="39"/>
-      <c r="V75" s="39"/>
-      <c r="W75" s="39"/>
-      <c r="X75" s="39"/>
-      <c r="Y75" s="39"/>
-      <c r="Z75" s="39"/>
-      <c r="AA75" s="39"/>
-      <c r="AB75" s="37"/>
-      <c r="AC75" s="37"/>
-      <c r="AD75" s="36"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
+      <c r="J75" s="41"/>
+      <c r="K75" s="41"/>
+      <c r="L75" s="41"/>
+      <c r="M75" s="41"/>
+      <c r="N75" s="41"/>
+      <c r="O75" s="41"/>
+      <c r="P75" s="41"/>
+      <c r="Q75" s="41"/>
+      <c r="R75" s="41"/>
+      <c r="S75" s="41"/>
+      <c r="T75" s="41"/>
+      <c r="U75" s="41"/>
+      <c r="V75" s="41"/>
+      <c r="W75" s="41"/>
+      <c r="X75" s="41"/>
+      <c r="Y75" s="41"/>
+      <c r="Z75" s="41"/>
+      <c r="AA75" s="41"/>
+      <c r="AB75" s="23"/>
+      <c r="AC75" s="23"/>
+      <c r="AD75" s="22"/>
     </row>
     <row r="76" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="28" t="s">
+      <c r="A76" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="38"/>
+      <c r="E76" s="38"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -32337,12 +32394,12 @@
       <c r="Y76" s="1"/>
       <c r="Z76" s="1"/>
       <c r="AA76" s="1"/>
-      <c r="AB76" s="38"/>
-      <c r="AC76" s="38"/>
-      <c r="AD76" s="36"/>
+      <c r="AB76" s="24"/>
+      <c r="AC76" s="24"/>
+      <c r="AD76" s="22"/>
     </row>
     <row r="77" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="28"/>
+      <c r="A77" s="39"/>
       <c r="B77" s="3" t="s">
         <v>4</v>
       </c>
@@ -32377,12 +32434,12 @@
       <c r="Y77" s="1"/>
       <c r="Z77" s="1"/>
       <c r="AA77" s="1"/>
-      <c r="AB77" s="38"/>
-      <c r="AC77" s="38"/>
-      <c r="AD77" s="36"/>
+      <c r="AB77" s="24"/>
+      <c r="AC77" s="24"/>
+      <c r="AD77" s="22"/>
     </row>
     <row r="78" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="28"/>
+      <c r="A78" s="39"/>
       <c r="B78" s="4">
         <v>1</v>
       </c>
@@ -32417,12 +32474,12 @@
       <c r="Y78" s="1"/>
       <c r="Z78" s="1"/>
       <c r="AA78" s="1"/>
-      <c r="AB78" s="38"/>
-      <c r="AC78" s="38"/>
-      <c r="AD78" s="36"/>
+      <c r="AB78" s="24"/>
+      <c r="AC78" s="24"/>
+      <c r="AD78" s="22"/>
     </row>
     <row r="79" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="28"/>
+      <c r="A79" s="39"/>
       <c r="B79" s="4">
         <v>2</v>
       </c>
@@ -32461,7 +32518,7 @@
       <c r="AC79" s="1"/>
     </row>
     <row r="80" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="28"/>
+      <c r="A80" s="39"/>
       <c r="B80" s="4">
         <v>4</v>
       </c>
@@ -32500,7 +32557,7 @@
       <c r="AC80" s="1"/>
     </row>
     <row r="81" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="28"/>
+      <c r="A81" s="39"/>
       <c r="B81" s="4">
         <v>6</v>
       </c>
@@ -32539,7 +32596,7 @@
       <c r="AC81" s="1"/>
     </row>
     <row r="82" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="28"/>
+      <c r="A82" s="39"/>
       <c r="B82" s="4">
         <v>8</v>
       </c>
@@ -32578,13 +32635,13 @@
       <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="28"/>
-      <c r="B83" s="29" t="s">
+      <c r="A83" s="39"/>
+      <c r="B83" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -32611,7 +32668,7 @@
       <c r="AC83" s="1"/>
     </row>
     <row r="84" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="28"/>
+      <c r="A84" s="39"/>
       <c r="B84" s="3" t="s">
         <v>4</v>
       </c>
@@ -32650,7 +32707,7 @@
       <c r="AC84" s="1"/>
     </row>
     <row r="85" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="28"/>
+      <c r="A85" s="39"/>
       <c r="B85" s="3">
         <v>1</v>
       </c>
@@ -32692,7 +32749,7 @@
       <c r="AC85" s="1"/>
     </row>
     <row r="86" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="28"/>
+      <c r="A86" s="39"/>
       <c r="B86" s="3">
         <v>2</v>
       </c>
@@ -32734,7 +32791,7 @@
       <c r="AC86" s="1"/>
     </row>
     <row r="87" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="28"/>
+      <c r="A87" s="39"/>
       <c r="B87" s="3">
         <v>4</v>
       </c>
@@ -32776,7 +32833,7 @@
       <c r="AC87" s="1"/>
     </row>
     <row r="88" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="28"/>
+      <c r="A88" s="39"/>
       <c r="B88" s="3">
         <v>6</v>
       </c>
@@ -32818,7 +32875,7 @@
       <c r="AC88" s="1"/>
     </row>
     <row r="89" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="28"/>
+      <c r="A89" s="39"/>
       <c r="B89" s="17">
         <v>8</v>
       </c>
@@ -32860,13 +32917,13 @@
       <c r="AC89" s="1"/>
     </row>
     <row r="90" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="28"/>
-      <c r="B90" s="29" t="s">
+      <c r="A90" s="39"/>
+      <c r="B90" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
-      <c r="E90" s="29"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="38"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -32893,7 +32950,7 @@
       <c r="AC90" s="1"/>
     </row>
     <row r="91" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="28"/>
+      <c r="A91" s="39"/>
       <c r="B91" s="3" t="s">
         <v>4</v>
       </c>
@@ -32932,7 +32989,7 @@
       <c r="AC91" s="1"/>
     </row>
     <row r="92" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="28"/>
+      <c r="A92" s="39"/>
       <c r="B92" s="3">
         <v>1</v>
       </c>
@@ -32974,7 +33031,7 @@
       <c r="AC92" s="1"/>
     </row>
     <row r="93" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="28"/>
+      <c r="A93" s="39"/>
       <c r="B93" s="3">
         <v>2</v>
       </c>
@@ -33016,7 +33073,7 @@
       <c r="AC93" s="1"/>
     </row>
     <row r="94" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="28"/>
+      <c r="A94" s="39"/>
       <c r="B94" s="3">
         <v>4</v>
       </c>
@@ -33058,7 +33115,7 @@
       <c r="AC94" s="1"/>
     </row>
     <row r="95" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="28"/>
+      <c r="A95" s="39"/>
       <c r="B95" s="3">
         <v>6</v>
       </c>
@@ -33100,7 +33157,7 @@
       <c r="AC95" s="1"/>
     </row>
     <row r="96" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="28"/>
+      <c r="A96" s="39"/>
       <c r="B96" s="18">
         <v>8</v>
       </c>
@@ -33142,13 +33199,13 @@
       <c r="AC96" s="1"/>
     </row>
     <row r="97" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="28"/>
-      <c r="B97" s="30" t="s">
+      <c r="A97" s="39"/>
+      <c r="B97" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="30"/>
-      <c r="D97" s="30"/>
-      <c r="E97" s="30"/>
+      <c r="C97" s="40"/>
+      <c r="D97" s="40"/>
+      <c r="E97" s="40"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
@@ -33175,13 +33232,13 @@
       <c r="AC97" s="1"/>
     </row>
     <row r="98" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="28"/>
-      <c r="B98" s="19" t="s">
+      <c r="A98" s="39"/>
+      <c r="B98" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
+      <c r="C98" s="35"/>
+      <c r="D98" s="35"/>
+      <c r="E98" s="35"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -33208,11 +33265,11 @@
       <c r="AC98" s="1"/>
     </row>
     <row r="99" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="28"/>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
+      <c r="A99" s="39"/>
+      <c r="B99" s="35"/>
+      <c r="C99" s="35"/>
+      <c r="D99" s="35"/>
+      <c r="E99" s="35"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
@@ -33239,11 +33296,11 @@
       <c r="AC99" s="1"/>
     </row>
     <row r="100" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="28"/>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
+      <c r="A100" s="39"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="35"/>
+      <c r="D100" s="35"/>
+      <c r="E100" s="35"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
@@ -33270,11 +33327,11 @@
       <c r="AC100" s="1"/>
     </row>
     <row r="101" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="28"/>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
+      <c r="A101" s="39"/>
+      <c r="B101" s="35"/>
+      <c r="C101" s="35"/>
+      <c r="D101" s="35"/>
+      <c r="E101" s="35"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
@@ -33301,11 +33358,11 @@
       <c r="AC101" s="1"/>
     </row>
     <row r="102" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="28"/>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19"/>
+      <c r="A102" s="39"/>
+      <c r="B102" s="35"/>
+      <c r="C102" s="35"/>
+      <c r="D102" s="35"/>
+      <c r="E102" s="35"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="8"/>
@@ -33332,11 +33389,11 @@
       <c r="AC102" s="1"/>
     </row>
     <row r="103" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="28"/>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="19"/>
+      <c r="A103" s="39"/>
+      <c r="B103" s="35"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="35"/>
+      <c r="E103" s="35"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="8"/>
@@ -33363,11 +33420,11 @@
       <c r="AC103" s="1"/>
     </row>
     <row r="104" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="28"/>
-      <c r="B104" s="19"/>
-      <c r="C104" s="19"/>
-      <c r="D104" s="19"/>
-      <c r="E104" s="19"/>
+      <c r="A104" s="39"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="35"/>
+      <c r="E104" s="35"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -33394,11 +33451,11 @@
       <c r="AC104" s="1"/>
     </row>
     <row r="105" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="28"/>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
+      <c r="A105" s="39"/>
+      <c r="B105" s="35"/>
+      <c r="C105" s="35"/>
+      <c r="D105" s="35"/>
+      <c r="E105" s="35"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -33457,270 +33514,402 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD6B2D-C446-466B-9C71-121C80824D6F}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="21.7109375" customWidth="1"/>
+    <col min="7" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+    <row r="1" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="49" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="60" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="41" t="s">
+    <row r="2" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
     </row>
-    <row r="3" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
+    <row r="3" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
     </row>
-    <row r="4" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+    <row r="4" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="45">
+      <c r="B4" s="27">
         <v>1000</v>
       </c>
-      <c r="C4" s="45">
+      <c r="C4" s="27">
         <v>3000</v>
       </c>
-      <c r="D4" s="45">
+      <c r="D4" s="27">
         <v>7000</v>
       </c>
-      <c r="E4" s="45">
+      <c r="E4" s="27">
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="46">
+      <c r="B5" s="28">
         <v>13</v>
       </c>
-      <c r="C5" s="46">
+      <c r="C5" s="28">
         <v>117</v>
       </c>
-      <c r="D5" s="46">
+      <c r="D5" s="28">
         <v>633</v>
       </c>
-      <c r="E5" s="46">
+      <c r="E5" s="28">
         <v>1101</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+    <row r="6" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="48">
+      <c r="B6" s="30">
         <v>50</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="30">
         <v>461</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="30">
         <v>4644</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="30">
         <v>11709</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+    <row r="7" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="46">
+      <c r="B7" s="28">
         <v>64</v>
       </c>
-      <c r="C7" s="46">
+      <c r="C7" s="28">
         <v>582</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="28">
         <v>5284</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="28">
         <v>12810</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
+    <row r="8" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="31"/>
     </row>
-    <row r="9" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44" t="s">
+    <row r="9" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="45">
+      <c r="B9" s="27">
         <v>3000</v>
       </c>
-      <c r="C9" s="45">
+      <c r="C9" s="27">
         <v>5000</v>
       </c>
-      <c r="D9" s="45">
+      <c r="D9" s="27">
         <v>7000</v>
       </c>
-      <c r="E9" s="45">
+      <c r="E9" s="27">
         <v>10000</v>
       </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
-    <row r="10" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+    <row r="10" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="46">
+      <c r="B10" s="28">
         <v>1175</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="28">
         <v>2668</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="28">
         <v>4787</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="28">
         <v>9358</v>
       </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
     </row>
-    <row r="11" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+    <row r="11" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="48">
+      <c r="B11" s="30">
         <v>514</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="30">
         <v>719</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="30">
         <v>1689</v>
       </c>
-      <c r="E11" s="48">
+      <c r="E11" s="30">
         <v>3658</v>
       </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="31"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="31"/>
     </row>
-    <row r="12" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="46">
+      <c r="B12" s="28">
         <v>1689</v>
       </c>
-      <c r="C12" s="46">
+      <c r="C12" s="28">
         <v>3387</v>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="28">
         <v>6476</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="28">
         <v>12974</v>
       </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="31"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="31"/>
     </row>
-    <row r="13" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+    <row r="13" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="31"/>
+      <c r="L13" s="31"/>
     </row>
-    <row r="14" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+    <row r="14" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="45">
+      <c r="B14" s="27">
         <v>2000</v>
       </c>
-      <c r="C14" s="45">
+      <c r="C14" s="27">
         <v>3000</v>
       </c>
-      <c r="D14" s="45">
+      <c r="D14" s="27">
         <v>5000</v>
       </c>
-      <c r="E14" s="45">
+      <c r="E14" s="27">
         <v>7000</v>
       </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="55"/>
+      <c r="L14" s="31"/>
     </row>
-    <row r="15" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44" t="s">
+    <row r="15" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="46">
-        <v>427</v>
-      </c>
-      <c r="C15" s="46">
-        <v>962</v>
-      </c>
-      <c r="D15" s="46">
-        <v>2591</v>
-      </c>
-      <c r="E15" s="46">
-        <v>5213</v>
-      </c>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="33">
+        <v>16</v>
+      </c>
+      <c r="I15" s="33">
+        <v>32</v>
+      </c>
+      <c r="J15" s="33">
+        <v>64</v>
+      </c>
+      <c r="K15" s="33">
+        <v>128</v>
+      </c>
+      <c r="L15" s="31"/>
     </row>
-    <row r="16" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
+    <row r="16" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="48">
-        <v>1848</v>
-      </c>
-      <c r="C16" s="48">
-        <v>5601</v>
-      </c>
-      <c r="D16" s="48">
-        <v>24408</v>
-      </c>
-      <c r="E16" s="48">
-        <v>70536</v>
-      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="33">
+        <v>2000</v>
+      </c>
+      <c r="H16" s="34">
+        <v>2256</v>
+      </c>
+      <c r="I16" s="34">
+        <v>1332</v>
+      </c>
+      <c r="J16" s="34">
+        <v>1844</v>
+      </c>
+      <c r="K16" s="34">
+        <v>4329</v>
+      </c>
+      <c r="L16" s="31"/>
     </row>
-    <row r="17" spans="1:5" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44" t="s">
+    <row r="17" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="46">
-        <v>2276</v>
-      </c>
-      <c r="C17" s="46">
-        <v>6563</v>
-      </c>
-      <c r="D17" s="46">
-        <v>26999</v>
-      </c>
-      <c r="E17" s="46">
-        <v>75750</v>
-      </c>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="33">
+        <v>3000</v>
+      </c>
+      <c r="H17" s="34">
+        <v>7481</v>
+      </c>
+      <c r="I17" s="34">
+        <v>4620</v>
+      </c>
+      <c r="J17" s="34">
+        <v>5585</v>
+      </c>
+      <c r="K17" s="34">
+        <v>13227</v>
+      </c>
+      <c r="L17" s="31"/>
+    </row>
+    <row r="18" spans="1:12" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="F18" s="31"/>
+      <c r="L18" s="31"/>
+    </row>
+    <row r="19" spans="1:12" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="F19" s="31"/>
+      <c r="G19" s="31"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="31"/>
+    </row>
+    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="31"/>
+      <c r="L20" s="31"/>
+    </row>
+    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="31"/>
+      <c r="L21" s="31"/>
+    </row>
+    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="31"/>
+      <c r="L22" s="31"/>
+    </row>
+    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="31"/>
+      <c r="L23" s="31"/>
+    </row>
+    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="20"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F25" s="20"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="20"/>
+    </row>
+    <row r="26" spans="1:12" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="G14:G15"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="D1:E1"/>
@@ -33733,6 +33922,7 @@
     <hyperlink ref="D1:E1" location="Графики!A1" display="Соотв. Графики" xr:uid="{1CAB3C67-9149-433C-ADF0-E6817A5FDD65}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/DecompositionLU/docs/version_3.2_statistics.xlsx
+++ b/DecompositionLU/docs/version_3.2_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A3883F-4249-4585-ACBF-20DC4AA82CB9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60934757-5DBF-423F-8AEB-8B05DDB7DCF7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Графики" sheetId="1" r:id="rId1"/>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>n = 2000</t>
-  </si>
-  <si>
-    <t>10000 на этом кластере я вряд ли дождусь. Ускорение и эффективность ощутимо хуже, чем на кластере х86, хотелось бы выяснить, почему.</t>
   </si>
   <si>
     <t>Версия 3.2</t>
@@ -233,6 +230,9 @@
   </si>
   <si>
     <t>n</t>
+  </si>
+  <si>
+    <t>ЭТО КАК</t>
   </si>
 </sst>
 </file>
@@ -3293,16 +3293,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7080103359173127</c:v>
+                  <c:v>2.000378787878788</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.842137592137592</c:v>
+                  <c:v>4.0420972062763108</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.0552147239263805</c:v>
+                  <c:v>5.7937465715852987</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.878228782287823</c:v>
+                  <c:v>7.5174377224199285</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3747,16 +3747,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.85400516795865633</c:v>
+                  <c:v>1.000189393939394</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.710534398034398</c:v>
+                  <c:v>1.0105243015690777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.67586912065439675</c:v>
+                  <c:v>0.96562442859754982</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.60977859778597787</c:v>
+                  <c:v>0.93967971530249106</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3845,6 +3845,7 @@
         <c:axId val="1826559071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -4108,19 +4109,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>9254</c:v>
+                  <c:v>10562</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5418</c:v>
+                  <c:v>5280</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3256</c:v>
+                  <c:v>2613</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2282</c:v>
+                  <c:v>1823</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1897</c:v>
+                  <c:v>1405</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4460,19 +4461,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>28038</c:v>
+                  <c:v>36099</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16116</c:v>
+                  <c:v>17609</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9714</c:v>
+                  <c:v>8670</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6841</c:v>
+                  <c:v>5968</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5606</c:v>
+                  <c:v>4618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4908,16 +4909,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7397617274758004</c:v>
+                  <c:v>2.050031234028054</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.8863495985176035</c:v>
+                  <c:v>4.1636678200692039</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.0985236076596987</c:v>
+                  <c:v>6.0487600536193034</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.0014270424545133</c:v>
+                  <c:v>7.817020355132092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5352,16 +5353,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86988086373790019</c:v>
+                  <c:v>1.025015617014027</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.72158739962940088</c:v>
+                  <c:v>1.040916955017301</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.68308726794328312</c:v>
+                  <c:v>1.0081266756032172</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.62517838030681416</c:v>
+                  <c:v>0.9771275443915115</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5450,6 +5451,7 @@
         <c:axId val="1826559071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -6179,19 +6181,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>123285</c:v>
+                  <c:v>167489</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>71387</c:v>
+                  <c:v>80815</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43124</c:v>
+                  <c:v>39609</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>29783</c:v>
+                  <c:v>27215</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>24270</c:v>
+                  <c:v>20859</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6616,7 +6618,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Графики!$C$85:$C$89</c:f>
+              <c:f>Графики!$D$85:$D$89</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -6624,16 +6626,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7080103359173127</c:v>
+                  <c:v>2.050031234028054</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.842137592137592</c:v>
+                  <c:v>4.1636678200692039</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.0552147239263805</c:v>
+                  <c:v>6.0487600536193034</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.878228782287823</c:v>
+                  <c:v>7.817020355132092</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7065,16 +7067,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.86349755557734598</c:v>
+                  <c:v>1.0362494586401039</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.7147122252110194</c:v>
+                  <c:v>1.0571397914615366</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.68990699392270749</c:v>
+                  <c:v>1.0257149856084267</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.63496600741656362</c:v>
+                  <c:v>1.0036974447480704</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7163,6 +7165,7 @@
         <c:axId val="1826559071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -32444,13 +32447,13 @@
         <v>1</v>
       </c>
       <c r="C78" s="5">
-        <v>9254</v>
+        <v>10562</v>
       </c>
       <c r="D78" s="6">
-        <v>28038</v>
+        <v>36099</v>
       </c>
       <c r="E78" s="6">
-        <v>123285</v>
+        <v>167489</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -32484,13 +32487,13 @@
         <v>2</v>
       </c>
       <c r="C79" s="5">
-        <v>5418</v>
+        <v>5280</v>
       </c>
       <c r="D79" s="6">
-        <v>16116</v>
+        <v>17609</v>
       </c>
       <c r="E79" s="6">
-        <v>71387</v>
+        <v>80815</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -32523,13 +32526,13 @@
         <v>4</v>
       </c>
       <c r="C80" s="5">
-        <v>3256</v>
+        <v>2613</v>
       </c>
       <c r="D80" s="6">
-        <v>9714</v>
+        <v>8670</v>
       </c>
       <c r="E80" s="6">
-        <v>43124</v>
+        <v>39609</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -32562,13 +32565,13 @@
         <v>6</v>
       </c>
       <c r="C81" s="5">
-        <v>2282</v>
+        <v>1823</v>
       </c>
       <c r="D81" s="6">
-        <v>6841</v>
+        <v>5968</v>
       </c>
       <c r="E81" s="6">
-        <v>29783</v>
+        <v>27215</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -32601,13 +32604,13 @@
         <v>8</v>
       </c>
       <c r="C82" s="5">
-        <v>1897</v>
+        <v>1405</v>
       </c>
       <c r="D82" s="6">
-        <v>5606</v>
+        <v>4618</v>
       </c>
       <c r="E82" s="6">
-        <v>24270</v>
+        <v>20859</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -32755,15 +32758,15 @@
       </c>
       <c r="C86" s="5">
         <f>C78/C79</f>
-        <v>1.7080103359173127</v>
+        <v>2.000378787878788</v>
       </c>
       <c r="D86" s="5">
         <f>D78/D79</f>
-        <v>1.7397617274758004</v>
+        <v>2.050031234028054</v>
       </c>
       <c r="E86" s="5">
         <f>E78/E79</f>
-        <v>1.726995111154692</v>
+        <v>2.0724989172802077</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -32797,15 +32800,15 @@
       </c>
       <c r="C87" s="5">
         <f>C78/C80</f>
-        <v>2.842137592137592</v>
+        <v>4.0420972062763108</v>
       </c>
       <c r="D87" s="5">
         <f>D78/D80</f>
-        <v>2.8863495985176035</v>
+        <v>4.1636678200692039</v>
       </c>
       <c r="E87" s="5">
         <f>E78/E80</f>
-        <v>2.8588489008440776</v>
+        <v>4.2285591658461463</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -32839,15 +32842,15 @@
       </c>
       <c r="C88" s="5">
         <f>C78/C81</f>
-        <v>4.0552147239263805</v>
+        <v>5.7937465715852987</v>
       </c>
       <c r="D88" s="5">
         <f>D78/D81</f>
-        <v>4.0985236076596987</v>
+        <v>6.0487600536193034</v>
       </c>
       <c r="E88" s="5">
         <f>E78/E81</f>
-        <v>4.1394419635362452</v>
+        <v>6.15428991365056</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -32881,15 +32884,15 @@
       </c>
       <c r="C89" s="14">
         <f>C78/C82</f>
-        <v>4.878228782287823</v>
+        <v>7.5174377224199285</v>
       </c>
       <c r="D89" s="14">
         <f>D78/D82</f>
-        <v>5.0014270424545133</v>
+        <v>7.817020355132092</v>
       </c>
       <c r="E89" s="14">
         <f>E78/E82</f>
-        <v>5.0797280593325089</v>
+        <v>8.0295795579845635</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -33037,15 +33040,15 @@
       </c>
       <c r="C93" s="5">
         <f>C86/B86</f>
-        <v>0.85400516795865633</v>
+        <v>1.000189393939394</v>
       </c>
       <c r="D93" s="5">
         <f>D86/B86</f>
-        <v>0.86988086373790019</v>
+        <v>1.025015617014027</v>
       </c>
       <c r="E93" s="5">
         <f>E86/B86</f>
-        <v>0.86349755557734598</v>
+        <v>1.0362494586401039</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -33079,15 +33082,15 @@
       </c>
       <c r="C94" s="5">
         <f>C87/B87</f>
-        <v>0.710534398034398</v>
+        <v>1.0105243015690777</v>
       </c>
       <c r="D94" s="5">
         <f>D87/B87</f>
-        <v>0.72158739962940088</v>
+        <v>1.040916955017301</v>
       </c>
       <c r="E94" s="5">
         <f>E87/B87</f>
-        <v>0.7147122252110194</v>
+        <v>1.0571397914615366</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -33121,15 +33124,15 @@
       </c>
       <c r="C95" s="5">
         <f>C88/B88</f>
-        <v>0.67586912065439675</v>
+        <v>0.96562442859754982</v>
       </c>
       <c r="D95" s="5">
         <f>D88/B88</f>
-        <v>0.68308726794328312</v>
+        <v>1.0081266756032172</v>
       </c>
       <c r="E95" s="5">
         <f>E88/B88</f>
-        <v>0.68990699392270749</v>
+        <v>1.0257149856084267</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -33163,15 +33166,15 @@
       </c>
       <c r="C96" s="16">
         <f>C89/B89</f>
-        <v>0.60977859778597787</v>
+        <v>0.93967971530249106</v>
       </c>
       <c r="D96" s="16">
         <f>D89/B89</f>
-        <v>0.62517838030681416</v>
+        <v>0.9771275443915115</v>
       </c>
       <c r="E96" s="16">
         <f>E89/B89</f>
-        <v>0.63496600741656362</v>
+        <v>1.0036974447480704</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -33234,7 +33237,7 @@
     <row r="98" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="39"/>
       <c r="B98" s="35" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C98" s="35"/>
       <c r="D98" s="35"/>
@@ -33524,23 +33527,23 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="59"/>
       <c r="D1" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="60" t="s">
         <v>19</v>
-      </c>
-      <c r="E1" s="60" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="61" t="s">
         <v>21</v>
-      </c>
-      <c r="B2" s="61" t="s">
-        <v>22</v>
       </c>
       <c r="C2" s="61"/>
       <c r="D2" s="61"/>
@@ -33548,7 +33551,7 @@
     </row>
     <row r="3" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -33557,7 +33560,7 @@
     </row>
     <row r="4" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="27">
         <v>1000</v>
@@ -33574,7 +33577,7 @@
     </row>
     <row r="5" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="28">
         <v>13</v>
@@ -33591,7 +33594,7 @@
     </row>
     <row r="6" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6" s="30">
         <v>50</v>
@@ -33608,7 +33611,7 @@
     </row>
     <row r="7" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="28">
         <v>64</v>
@@ -33625,7 +33628,7 @@
     </row>
     <row r="8" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="58"/>
       <c r="C8" s="58"/>
@@ -33641,7 +33644,7 @@
     </row>
     <row r="9" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="27">
         <v>3000</v>
@@ -33665,7 +33668,7 @@
     </row>
     <row r="10" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B10" s="28">
         <v>1175</v>
@@ -33689,7 +33692,7 @@
     </row>
     <row r="11" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="30">
         <v>514</v>
@@ -33713,7 +33716,7 @@
     </row>
     <row r="12" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B12" s="28">
         <v>1689</v>
@@ -33737,7 +33740,7 @@
     </row>
     <row r="13" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="58" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
@@ -33748,7 +33751,7 @@
     </row>
     <row r="14" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="27">
         <v>2000</v>
@@ -33764,10 +33767,10 @@
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="53" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I14" s="54"/>
       <c r="J14" s="54"/>
@@ -33776,12 +33779,20 @@
     </row>
     <row r="15" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
+        <v>24</v>
+      </c>
+      <c r="B15" s="28">
+        <v>467</v>
+      </c>
+      <c r="C15" s="28">
+        <v>1041</v>
+      </c>
+      <c r="D15" s="28">
+        <v>2894</v>
+      </c>
+      <c r="E15" s="28">
+        <v>5610</v>
+      </c>
       <c r="F15" s="31"/>
       <c r="G15" s="57"/>
       <c r="H15" s="33">
@@ -33800,12 +33811,20 @@
     </row>
     <row r="16" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
+        <v>25</v>
+      </c>
+      <c r="B16" s="30">
+        <v>1407</v>
+      </c>
+      <c r="C16" s="30">
+        <v>4607</v>
+      </c>
+      <c r="D16" s="30">
+        <v>20957</v>
+      </c>
+      <c r="E16" s="30">
+        <v>58068</v>
+      </c>
       <c r="F16" s="31"/>
       <c r="G16" s="33">
         <v>2000</v>
@@ -33826,12 +33845,20 @@
     </row>
     <row r="17" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
+        <v>26</v>
+      </c>
+      <c r="B17" s="28">
+        <v>1875</v>
+      </c>
+      <c r="C17" s="28">
+        <v>5648</v>
+      </c>
+      <c r="D17" s="28">
+        <v>23852</v>
+      </c>
+      <c r="E17" s="28">
+        <v>63679</v>
+      </c>
       <c r="F17" s="31"/>
       <c r="G17" s="33">
         <v>3000</v>

--- a/DecompositionLU/docs/version_3.2_statistics.xlsx
+++ b/DecompositionLU/docs/version_3.2_statistics.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEDEAFF-3E89-49B9-A174-28F269601D5C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B778901E-AF75-4789-BD7E-7899687AB1EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Графики" sheetId="1" r:id="rId1"/>
     <sheet name="Замеры блоков" sheetId="3" r:id="rId2"/>
     <sheet name="Таблица" sheetId="2" r:id="rId3"/>
+    <sheet name="Сравнение с Eigen" sheetId="4" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="49">
   <si>
     <t>Замеры версии 3.2</t>
   </si>
@@ -262,6 +263,30 @@
       <t>кластер risk-V</t>
     </r>
   </si>
+  <si>
+    <t>Сравнение версии 3.2 и Eigen::PartialPivLU&lt;Eigen::MatrixXd&gt;</t>
+  </si>
+  <si>
+    <t>Примечание: приведено только время LU разложения</t>
+  </si>
+  <si>
+    <t>Время вычисления версии 3.2, мс:</t>
+  </si>
+  <si>
+    <t>Время вычисления Eigen::PartialPivLU, мс:</t>
+  </si>
+  <si>
+    <t>Разница (&gt;0 при более быстрой работе версии 3.2), %</t>
+  </si>
+  <si>
+    <t>Хорошо</t>
+  </si>
+  <si>
+    <t>Бал + деж</t>
+  </si>
+  <si>
+    <t>Есть некоторые проблемы</t>
+  </si>
 </sst>
 </file>
 
@@ -366,16 +391,15 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
       <u/>
-      <sz val="16"/>
+      <sz val="18"/>
       <color theme="0"/>
       <name val="GOST Common"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,6 +457,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -557,7 +587,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -637,19 +667,29 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -691,6 +731,27 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -709,32 +770,29 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -29089,6 +29147,121 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9054</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>113168</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="TextBox 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B27C40F3-13E6-48F1-943D-4310E1495EA8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8365403" y="5780637"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9054</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>113168</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B093D744-D74B-4593-903E-446A2AC939BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8365403" y="6550182"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -29422,30 +29595,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
-      <c r="K1" s="36"/>
-      <c r="L1" s="36"/>
-      <c r="M1" s="36"/>
-      <c r="N1" s="36"/>
-      <c r="O1" s="37" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="38"/>
-      <c r="T1" s="39"/>
+      <c r="P1" s="76"/>
+      <c r="Q1" s="76"/>
+      <c r="R1" s="76"/>
+      <c r="S1" s="76"/>
+      <c r="T1" s="77"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -29457,15 +29630,15 @@
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="43"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="47"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -29492,7 +29665,7 @@
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="40"/>
+      <c r="A3" s="44"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -29531,7 +29704,7 @@
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -29570,7 +29743,7 @@
       <c r="AC4" s="1"/>
     </row>
     <row r="5" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="40"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="4">
         <v>2</v>
       </c>
@@ -29609,7 +29782,7 @@
       <c r="AC5" s="1"/>
     </row>
     <row r="6" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="40"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -29648,7 +29821,7 @@
       <c r="AC6" s="1"/>
     </row>
     <row r="7" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="40"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="4">
         <v>6</v>
       </c>
@@ -29687,7 +29860,7 @@
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40"/>
+      <c r="A8" s="44"/>
       <c r="B8" s="4">
         <v>8</v>
       </c>
@@ -29726,7 +29899,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="4">
         <v>10</v>
       </c>
@@ -29765,7 +29938,7 @@
       <c r="AC9" s="1"/>
     </row>
     <row r="10" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="40"/>
+      <c r="A10" s="44"/>
       <c r="B10" s="4">
         <v>12</v>
       </c>
@@ -29804,7 +29977,7 @@
       <c r="AC10" s="1"/>
     </row>
     <row r="11" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="40"/>
+      <c r="A11" s="44"/>
       <c r="B11" s="4">
         <v>16</v>
       </c>
@@ -29843,13 +30016,13 @@
       <c r="AC11" s="1"/>
     </row>
     <row r="12" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="40"/>
-      <c r="B12" s="41" t="s">
+      <c r="A12" s="44"/>
+      <c r="B12" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="43"/>
+      <c r="C12" s="46"/>
+      <c r="D12" s="46"/>
+      <c r="E12" s="47"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -29876,7 +30049,7 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
+      <c r="A13" s="44"/>
       <c r="B13" s="3" t="s">
         <v>4</v>
       </c>
@@ -29915,7 +30088,7 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="40"/>
+      <c r="A14" s="44"/>
       <c r="B14" s="3">
         <v>1</v>
       </c>
@@ -29957,7 +30130,7 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="40"/>
+      <c r="A15" s="44"/>
       <c r="B15" s="3">
         <v>2</v>
       </c>
@@ -29999,7 +30172,7 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="40"/>
+      <c r="A16" s="44"/>
       <c r="B16" s="3">
         <v>4</v>
       </c>
@@ -30041,7 +30214,7 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="40"/>
+      <c r="A17" s="44"/>
       <c r="B17" s="3">
         <v>6</v>
       </c>
@@ -30083,7 +30256,7 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="40"/>
+      <c r="A18" s="44"/>
       <c r="B18" s="3">
         <v>8</v>
       </c>
@@ -30125,7 +30298,7 @@
       <c r="AC18" s="1"/>
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="40"/>
+      <c r="A19" s="44"/>
       <c r="B19" s="3">
         <v>10</v>
       </c>
@@ -30167,7 +30340,7 @@
       <c r="AC19" s="1"/>
     </row>
     <row r="20" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40"/>
+      <c r="A20" s="44"/>
       <c r="B20" s="3">
         <v>12</v>
       </c>
@@ -30209,7 +30382,7 @@
       <c r="AC20" s="1"/>
     </row>
     <row r="21" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="40"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="3">
         <v>16</v>
       </c>
@@ -30251,13 +30424,13 @@
       <c r="AC21" s="1"/>
     </row>
     <row r="22" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="40"/>
-      <c r="B22" s="41" t="s">
+      <c r="A22" s="44"/>
+      <c r="B22" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="43"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="47"/>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -30284,7 +30457,7 @@
       <c r="AC22" s="1"/>
     </row>
     <row r="23" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="40"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="3" t="s">
         <v>4</v>
       </c>
@@ -30323,7 +30496,7 @@
       <c r="AC23" s="1"/>
     </row>
     <row r="24" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="40"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="3">
         <v>1</v>
       </c>
@@ -30365,7 +30538,7 @@
       <c r="AC24" s="1"/>
     </row>
     <row r="25" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="40"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="3">
         <v>2</v>
       </c>
@@ -30407,7 +30580,7 @@
       <c r="AC25" s="1"/>
     </row>
     <row r="26" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="40"/>
+      <c r="A26" s="44"/>
       <c r="B26" s="3">
         <v>4</v>
       </c>
@@ -30449,7 +30622,7 @@
       <c r="AC26" s="1"/>
     </row>
     <row r="27" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
+      <c r="A27" s="44"/>
       <c r="B27" s="3">
         <v>6</v>
       </c>
@@ -30491,7 +30664,7 @@
       <c r="AC27" s="1"/>
     </row>
     <row r="28" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="40"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="3">
         <v>8</v>
       </c>
@@ -30533,7 +30706,7 @@
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="40"/>
+      <c r="A29" s="44"/>
       <c r="B29" s="3">
         <v>10</v>
       </c>
@@ -30575,7 +30748,7 @@
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="40"/>
+      <c r="A30" s="44"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
@@ -30617,7 +30790,7 @@
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="40"/>
+      <c r="A31" s="44"/>
       <c r="B31" s="3">
         <v>16</v>
       </c>
@@ -30659,30 +30832,30 @@
       <c r="AC31" s="1"/>
     </row>
     <row r="32" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="40"/>
+      <c r="A32" s="44"/>
       <c r="B32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
-      <c r="O32" s="45"/>
-      <c r="P32" s="45"/>
-      <c r="Q32" s="45"/>
-      <c r="R32" s="45"/>
-      <c r="S32" s="45"/>
-      <c r="T32" s="46"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="49"/>
+      <c r="I32" s="49"/>
+      <c r="J32" s="49"/>
+      <c r="K32" s="49"/>
+      <c r="L32" s="49"/>
+      <c r="M32" s="49"/>
+      <c r="N32" s="49"/>
+      <c r="O32" s="49"/>
+      <c r="P32" s="49"/>
+      <c r="Q32" s="49"/>
+      <c r="R32" s="49"/>
+      <c r="S32" s="49"/>
+      <c r="T32" s="50"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -30694,15 +30867,15 @@
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -30729,7 +30902,7 @@
       <c r="AC33" s="19"/>
     </row>
     <row r="34" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="49"/>
+      <c r="A34" s="53"/>
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
@@ -30768,7 +30941,7 @@
       <c r="AC34" s="19"/>
     </row>
     <row r="35" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="49"/>
+      <c r="A35" s="53"/>
       <c r="B35" s="4">
         <v>1</v>
       </c>
@@ -30807,7 +30980,7 @@
       <c r="AC35" s="19"/>
     </row>
     <row r="36" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="49"/>
+      <c r="A36" s="53"/>
       <c r="B36" s="4">
         <v>2</v>
       </c>
@@ -30846,7 +31019,7 @@
       <c r="AC36" s="19"/>
     </row>
     <row r="37" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="49"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="4">
         <v>4</v>
       </c>
@@ -30885,7 +31058,7 @@
       <c r="AC37" s="19"/>
     </row>
     <row r="38" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="49"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="4">
         <v>6</v>
       </c>
@@ -30924,7 +31097,7 @@
       <c r="AC38" s="19"/>
     </row>
     <row r="39" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="49"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="4">
         <v>8</v>
       </c>
@@ -30963,7 +31136,7 @@
       <c r="AC39" s="19"/>
     </row>
     <row r="40" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="49"/>
+      <c r="A40" s="53"/>
       <c r="B40" s="4">
         <v>10</v>
       </c>
@@ -31002,7 +31175,7 @@
       <c r="AC40" s="19"/>
     </row>
     <row r="41" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="49"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="4">
         <v>12</v>
       </c>
@@ -31041,7 +31214,7 @@
       <c r="AC41" s="19"/>
     </row>
     <row r="42" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="49"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="4">
         <v>14</v>
       </c>
@@ -31080,7 +31253,7 @@
       <c r="AC42" s="19"/>
     </row>
     <row r="43" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="49"/>
+      <c r="A43" s="53"/>
       <c r="B43" s="4">
         <v>16</v>
       </c>
@@ -31119,7 +31292,7 @@
       <c r="AC43" s="19"/>
     </row>
     <row r="44" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="49"/>
+      <c r="A44" s="53"/>
       <c r="B44" s="4">
         <v>18</v>
       </c>
@@ -31158,7 +31331,7 @@
       <c r="AC44" s="19"/>
     </row>
     <row r="45" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="49"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="4">
         <v>20</v>
       </c>
@@ -31197,7 +31370,7 @@
       <c r="AC45" s="19"/>
     </row>
     <row r="46" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="49"/>
+      <c r="A46" s="53"/>
       <c r="B46" s="10">
         <v>40</v>
       </c>
@@ -31236,13 +31409,13 @@
       <c r="AC46" s="19"/>
     </row>
     <row r="47" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="49"/>
-      <c r="B47" s="50" t="s">
+      <c r="A47" s="53"/>
+      <c r="B47" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="50"/>
-      <c r="D47" s="50"/>
-      <c r="E47" s="50"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="54"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -31269,7 +31442,7 @@
       <c r="AC47" s="19"/>
     </row>
     <row r="48" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="49"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
@@ -31308,7 +31481,7 @@
       <c r="AC48" s="20"/>
     </row>
     <row r="49" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="49"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="4">
         <v>1</v>
       </c>
@@ -31350,7 +31523,7 @@
       <c r="AC49" s="20"/>
     </row>
     <row r="50" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="49"/>
+      <c r="A50" s="53"/>
       <c r="B50" s="4">
         <v>2</v>
       </c>
@@ -31392,7 +31565,7 @@
       <c r="AC50" s="20"/>
     </row>
     <row r="51" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="49"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="4">
         <v>4</v>
       </c>
@@ -31434,7 +31607,7 @@
       <c r="AC51" s="20"/>
     </row>
     <row r="52" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="49"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="4">
         <v>6</v>
       </c>
@@ -31476,7 +31649,7 @@
       <c r="AC52" s="20"/>
     </row>
     <row r="53" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="49"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="13">
         <v>8</v>
       </c>
@@ -31518,7 +31691,7 @@
       <c r="AC53" s="20"/>
     </row>
     <row r="54" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="49"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="4">
         <v>10</v>
       </c>
@@ -31560,7 +31733,7 @@
       <c r="AC54" s="20"/>
     </row>
     <row r="55" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="49"/>
+      <c r="A55" s="53"/>
       <c r="B55" s="4">
         <v>12</v>
       </c>
@@ -31602,7 +31775,7 @@
       <c r="AC55" s="20"/>
     </row>
     <row r="56" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="49"/>
+      <c r="A56" s="53"/>
       <c r="B56" s="4">
         <v>14</v>
       </c>
@@ -31644,7 +31817,7 @@
       <c r="AC56" s="20"/>
     </row>
     <row r="57" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="49"/>
+      <c r="A57" s="53"/>
       <c r="B57" s="4">
         <v>16</v>
       </c>
@@ -31686,7 +31859,7 @@
       <c r="AC57" s="19"/>
     </row>
     <row r="58" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="49"/>
+      <c r="A58" s="53"/>
       <c r="B58" s="4">
         <v>18</v>
       </c>
@@ -31728,7 +31901,7 @@
       <c r="AC58" s="20"/>
     </row>
     <row r="59" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="49"/>
+      <c r="A59" s="53"/>
       <c r="B59" s="4">
         <v>20</v>
       </c>
@@ -31770,7 +31943,7 @@
       <c r="AC59" s="20"/>
     </row>
     <row r="60" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="49"/>
+      <c r="A60" s="53"/>
       <c r="B60" s="10">
         <v>40</v>
       </c>
@@ -31812,13 +31985,13 @@
       <c r="AC60" s="20"/>
     </row>
     <row r="61" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="49"/>
-      <c r="B61" s="50" t="s">
+      <c r="A61" s="53"/>
+      <c r="B61" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="50"/>
-      <c r="D61" s="50"/>
-      <c r="E61" s="50"/>
+      <c r="C61" s="54"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="54"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -31845,7 +32018,7 @@
       <c r="AC61" s="20"/>
     </row>
     <row r="62" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="49"/>
+      <c r="A62" s="53"/>
       <c r="B62" s="3" t="s">
         <v>4</v>
       </c>
@@ -31884,7 +32057,7 @@
       <c r="AC62" s="20"/>
     </row>
     <row r="63" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="49"/>
+      <c r="A63" s="53"/>
       <c r="B63" s="4">
         <v>1</v>
       </c>
@@ -31926,7 +32099,7 @@
       <c r="AC63" s="20"/>
     </row>
     <row r="64" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="49"/>
+      <c r="A64" s="53"/>
       <c r="B64" s="4">
         <v>2</v>
       </c>
@@ -31968,7 +32141,7 @@
       <c r="AC64" s="20"/>
     </row>
     <row r="65" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="49"/>
+      <c r="A65" s="53"/>
       <c r="B65" s="4">
         <v>4</v>
       </c>
@@ -32010,7 +32183,7 @@
       <c r="AC65" s="20"/>
     </row>
     <row r="66" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="49"/>
+      <c r="A66" s="53"/>
       <c r="B66" s="4">
         <v>6</v>
       </c>
@@ -32052,7 +32225,7 @@
       <c r="AC66" s="20"/>
     </row>
     <row r="67" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="49"/>
+      <c r="A67" s="53"/>
       <c r="B67" s="15">
         <v>8</v>
       </c>
@@ -32094,7 +32267,7 @@
       <c r="AC67" s="20"/>
     </row>
     <row r="68" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="49"/>
+      <c r="A68" s="53"/>
       <c r="B68" s="4">
         <v>10</v>
       </c>
@@ -32136,7 +32309,7 @@
       <c r="AC68" s="20"/>
     </row>
     <row r="69" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="49"/>
+      <c r="A69" s="53"/>
       <c r="B69" s="4">
         <v>12</v>
       </c>
@@ -32178,7 +32351,7 @@
       <c r="AC69" s="19"/>
     </row>
     <row r="70" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="49"/>
+      <c r="A70" s="53"/>
       <c r="B70" s="4">
         <v>14</v>
       </c>
@@ -32220,7 +32393,7 @@
       <c r="AC70" s="19"/>
     </row>
     <row r="71" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="49"/>
+      <c r="A71" s="53"/>
       <c r="B71" s="4">
         <v>16</v>
       </c>
@@ -32262,7 +32435,7 @@
       <c r="AC71" s="20"/>
     </row>
     <row r="72" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="49"/>
+      <c r="A72" s="53"/>
       <c r="B72" s="4">
         <v>18</v>
       </c>
@@ -32305,7 +32478,7 @@
       <c r="AD72" s="22"/>
     </row>
     <row r="73" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="49"/>
+      <c r="A73" s="53"/>
       <c r="B73" s="4">
         <v>20</v>
       </c>
@@ -32348,7 +32521,7 @@
       <c r="AD73" s="22"/>
     </row>
     <row r="74" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="49"/>
+      <c r="A74" s="53"/>
       <c r="B74" s="10">
         <v>40</v>
       </c>
@@ -32391,51 +32564,51 @@
       <c r="AD74" s="22"/>
     </row>
     <row r="75" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="49"/>
+      <c r="A75" s="53"/>
       <c r="B75" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="52" t="s">
+      <c r="C75" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="52"/>
-      <c r="I75" s="52"/>
-      <c r="J75" s="52"/>
-      <c r="K75" s="52"/>
-      <c r="L75" s="52"/>
-      <c r="M75" s="52"/>
-      <c r="N75" s="52"/>
-      <c r="O75" s="52"/>
-      <c r="P75" s="52"/>
-      <c r="Q75" s="52"/>
-      <c r="R75" s="52"/>
-      <c r="S75" s="52"/>
-      <c r="T75" s="52"/>
-      <c r="U75" s="52"/>
-      <c r="V75" s="52"/>
-      <c r="W75" s="52"/>
-      <c r="X75" s="52"/>
-      <c r="Y75" s="52"/>
-      <c r="Z75" s="52"/>
-      <c r="AA75" s="52"/>
+      <c r="D75" s="56"/>
+      <c r="E75" s="56"/>
+      <c r="F75" s="56"/>
+      <c r="G75" s="56"/>
+      <c r="H75" s="56"/>
+      <c r="I75" s="56"/>
+      <c r="J75" s="56"/>
+      <c r="K75" s="56"/>
+      <c r="L75" s="56"/>
+      <c r="M75" s="56"/>
+      <c r="N75" s="56"/>
+      <c r="O75" s="56"/>
+      <c r="P75" s="56"/>
+      <c r="Q75" s="56"/>
+      <c r="R75" s="56"/>
+      <c r="S75" s="56"/>
+      <c r="T75" s="56"/>
+      <c r="U75" s="56"/>
+      <c r="V75" s="56"/>
+      <c r="W75" s="56"/>
+      <c r="X75" s="56"/>
+      <c r="Y75" s="56"/>
+      <c r="Z75" s="56"/>
+      <c r="AA75" s="56"/>
       <c r="AB75" s="23"/>
       <c r="AC75" s="23"/>
       <c r="AD75" s="22"/>
     </row>
     <row r="76" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="40" t="s">
+      <c r="A76" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="B76" s="50" t="s">
+      <c r="B76" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="50"/>
-      <c r="D76" s="50"/>
-      <c r="E76" s="50"/>
+      <c r="C76" s="54"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="54"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -32463,7 +32636,7 @@
       <c r="AD76" s="22"/>
     </row>
     <row r="77" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="40"/>
+      <c r="A77" s="44"/>
       <c r="B77" s="3" t="s">
         <v>4</v>
       </c>
@@ -32503,7 +32676,7 @@
       <c r="AD77" s="22"/>
     </row>
     <row r="78" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="40"/>
+      <c r="A78" s="44"/>
       <c r="B78" s="4">
         <v>1</v>
       </c>
@@ -32543,7 +32716,7 @@
       <c r="AD78" s="22"/>
     </row>
     <row r="79" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="40"/>
+      <c r="A79" s="44"/>
       <c r="B79" s="4">
         <v>2</v>
       </c>
@@ -32582,7 +32755,7 @@
       <c r="AC79" s="1"/>
     </row>
     <row r="80" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="40"/>
+      <c r="A80" s="44"/>
       <c r="B80" s="4">
         <v>4</v>
       </c>
@@ -32621,7 +32794,7 @@
       <c r="AC80" s="1"/>
     </row>
     <row r="81" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="40"/>
+      <c r="A81" s="44"/>
       <c r="B81" s="4">
         <v>6</v>
       </c>
@@ -32660,7 +32833,7 @@
       <c r="AC81" s="1"/>
     </row>
     <row r="82" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="40"/>
+      <c r="A82" s="44"/>
       <c r="B82" s="4">
         <v>8</v>
       </c>
@@ -32699,13 +32872,13 @@
       <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="40"/>
-      <c r="B83" s="50" t="s">
+      <c r="A83" s="44"/>
+      <c r="B83" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="C83" s="50"/>
-      <c r="D83" s="50"/>
-      <c r="E83" s="50"/>
+      <c r="C83" s="54"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="54"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -32732,7 +32905,7 @@
       <c r="AC83" s="1"/>
     </row>
     <row r="84" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="40"/>
+      <c r="A84" s="44"/>
       <c r="B84" s="3" t="s">
         <v>4</v>
       </c>
@@ -32771,7 +32944,7 @@
       <c r="AC84" s="1"/>
     </row>
     <row r="85" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="40"/>
+      <c r="A85" s="44"/>
       <c r="B85" s="3">
         <v>1</v>
       </c>
@@ -32813,7 +32986,7 @@
       <c r="AC85" s="1"/>
     </row>
     <row r="86" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="40"/>
+      <c r="A86" s="44"/>
       <c r="B86" s="3">
         <v>2</v>
       </c>
@@ -32855,7 +33028,7 @@
       <c r="AC86" s="1"/>
     </row>
     <row r="87" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="40"/>
+      <c r="A87" s="44"/>
       <c r="B87" s="3">
         <v>4</v>
       </c>
@@ -32897,7 +33070,7 @@
       <c r="AC87" s="1"/>
     </row>
     <row r="88" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="40"/>
+      <c r="A88" s="44"/>
       <c r="B88" s="3">
         <v>6</v>
       </c>
@@ -32939,7 +33112,7 @@
       <c r="AC88" s="1"/>
     </row>
     <row r="89" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="40"/>
+      <c r="A89" s="44"/>
       <c r="B89" s="17">
         <v>8</v>
       </c>
@@ -32981,13 +33154,13 @@
       <c r="AC89" s="1"/>
     </row>
     <row r="90" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="40"/>
-      <c r="B90" s="50" t="s">
+      <c r="A90" s="44"/>
+      <c r="B90" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="50"/>
-      <c r="D90" s="50"/>
-      <c r="E90" s="50"/>
+      <c r="C90" s="54"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="54"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -33014,7 +33187,7 @@
       <c r="AC90" s="1"/>
     </row>
     <row r="91" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="40"/>
+      <c r="A91" s="44"/>
       <c r="B91" s="3" t="s">
         <v>4</v>
       </c>
@@ -33053,7 +33226,7 @@
       <c r="AC91" s="1"/>
     </row>
     <row r="92" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="40"/>
+      <c r="A92" s="44"/>
       <c r="B92" s="3">
         <v>1</v>
       </c>
@@ -33095,7 +33268,7 @@
       <c r="AC92" s="1"/>
     </row>
     <row r="93" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="40"/>
+      <c r="A93" s="44"/>
       <c r="B93" s="3">
         <v>2</v>
       </c>
@@ -33137,7 +33310,7 @@
       <c r="AC93" s="1"/>
     </row>
     <row r="94" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="40"/>
+      <c r="A94" s="44"/>
       <c r="B94" s="3">
         <v>4</v>
       </c>
@@ -33179,7 +33352,7 @@
       <c r="AC94" s="1"/>
     </row>
     <row r="95" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="40"/>
+      <c r="A95" s="44"/>
       <c r="B95" s="3">
         <v>6</v>
       </c>
@@ -33221,7 +33394,7 @@
       <c r="AC95" s="1"/>
     </row>
     <row r="96" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="40"/>
+      <c r="A96" s="44"/>
       <c r="B96" s="18">
         <v>8</v>
       </c>
@@ -33263,13 +33436,13 @@
       <c r="AC96" s="1"/>
     </row>
     <row r="97" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="40"/>
-      <c r="B97" s="51" t="s">
+      <c r="A97" s="44"/>
+      <c r="B97" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
@@ -33296,13 +33469,13 @@
       <c r="AC97" s="1"/>
     </row>
     <row r="98" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="40"/>
-      <c r="B98" s="47" t="s">
+      <c r="A98" s="44"/>
+      <c r="B98" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="C98" s="47"/>
-      <c r="D98" s="47"/>
-      <c r="E98" s="47"/>
+      <c r="C98" s="51"/>
+      <c r="D98" s="51"/>
+      <c r="E98" s="51"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -33329,11 +33502,11 @@
       <c r="AC98" s="1"/>
     </row>
     <row r="99" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="40"/>
-      <c r="B99" s="47"/>
-      <c r="C99" s="47"/>
-      <c r="D99" s="47"/>
-      <c r="E99" s="47"/>
+      <c r="A99" s="44"/>
+      <c r="B99" s="51"/>
+      <c r="C99" s="51"/>
+      <c r="D99" s="51"/>
+      <c r="E99" s="51"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
@@ -33360,11 +33533,11 @@
       <c r="AC99" s="1"/>
     </row>
     <row r="100" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="40"/>
-      <c r="B100" s="47"/>
-      <c r="C100" s="47"/>
-      <c r="D100" s="47"/>
-      <c r="E100" s="47"/>
+      <c r="A100" s="44"/>
+      <c r="B100" s="51"/>
+      <c r="C100" s="51"/>
+      <c r="D100" s="51"/>
+      <c r="E100" s="51"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
@@ -33391,11 +33564,11 @@
       <c r="AC100" s="1"/>
     </row>
     <row r="101" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="40"/>
-      <c r="B101" s="47"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="47"/>
-      <c r="E101" s="47"/>
+      <c r="A101" s="44"/>
+      <c r="B101" s="51"/>
+      <c r="C101" s="51"/>
+      <c r="D101" s="51"/>
+      <c r="E101" s="51"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
@@ -33422,11 +33595,11 @@
       <c r="AC101" s="1"/>
     </row>
     <row r="102" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="40"/>
-      <c r="B102" s="47"/>
-      <c r="C102" s="47"/>
-      <c r="D102" s="47"/>
-      <c r="E102" s="47"/>
+      <c r="A102" s="44"/>
+      <c r="B102" s="51"/>
+      <c r="C102" s="51"/>
+      <c r="D102" s="51"/>
+      <c r="E102" s="51"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="8"/>
@@ -33453,11 +33626,11 @@
       <c r="AC102" s="1"/>
     </row>
     <row r="103" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="40"/>
-      <c r="B103" s="47"/>
-      <c r="C103" s="47"/>
-      <c r="D103" s="47"/>
-      <c r="E103" s="47"/>
+      <c r="A103" s="44"/>
+      <c r="B103" s="51"/>
+      <c r="C103" s="51"/>
+      <c r="D103" s="51"/>
+      <c r="E103" s="51"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="8"/>
@@ -33484,11 +33657,11 @@
       <c r="AC103" s="1"/>
     </row>
     <row r="104" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="40"/>
-      <c r="B104" s="47"/>
-      <c r="C104" s="47"/>
-      <c r="D104" s="47"/>
-      <c r="E104" s="47"/>
+      <c r="A104" s="44"/>
+      <c r="B104" s="51"/>
+      <c r="C104" s="51"/>
+      <c r="D104" s="51"/>
+      <c r="E104" s="51"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -33515,11 +33688,11 @@
       <c r="AC104" s="1"/>
     </row>
     <row r="105" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="40"/>
-      <c r="B105" s="47"/>
-      <c r="C105" s="47"/>
-      <c r="D105" s="47"/>
-      <c r="E105" s="47"/>
+      <c r="A105" s="44"/>
+      <c r="B105" s="51"/>
+      <c r="C105" s="51"/>
+      <c r="D105" s="51"/>
+      <c r="E105" s="51"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -33568,7 +33741,7 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O1" location="Таблица!A44" display="Соотв. таблица" xr:uid="{83FF44B0-CA98-46DE-9446-E04E222E13B0}"/>
-    <hyperlink ref="O1:T1" location="Таблица!A1" display="&gt;---------&lt; Соотв. Таблица &gt;---------&lt;" xr:uid="{43C05201-5D9E-4235-90B2-C549AD74846E}"/>
+    <hyperlink ref="O1:T1" location="Таблица!A1" display="&gt;---------&lt; Соотв. Таблица &gt;---------&lt;" xr:uid="{37FA7A4C-9A01-4954-9425-A9EC480166D8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -33599,50 +33772,50 @@
       <c r="F1" s="59"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="58" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="62" t="s">
+      <c r="F2" s="58" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
+      <c r="A3" s="57"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="61">
+      <c r="A4" s="60">
         <v>3000</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="60">
         <v>4613</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
     </row>
     <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="34">
         <v>16.673999999999999</v>
       </c>
@@ -33657,18 +33830,18 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="62" t="s">
+      <c r="A6" s="60"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="62"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="62"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
+      <c r="A7" s="60"/>
+      <c r="B7" s="60"/>
       <c r="C7" s="34">
         <f>ROUND(C5/$B4*100,2)</f>
         <v>0.36</v>
@@ -33687,22 +33860,22 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="61">
+      <c r="A8" s="60">
         <v>5000</v>
       </c>
-      <c r="B8" s="61">
+      <c r="B8" s="60">
         <v>21014</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="C8" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="60"/>
-      <c r="E8" s="60"/>
-      <c r="F8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="61"/>
-      <c r="B9" s="61"/>
+      <c r="A9" s="60"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="34">
         <v>25.027000000000001</v>
       </c>
@@ -33717,18 +33890,18 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="61"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="62" t="s">
+      <c r="A10" s="60"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
     </row>
     <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="61"/>
-      <c r="B11" s="61"/>
+      <c r="A11" s="60"/>
+      <c r="B11" s="60"/>
       <c r="C11" s="34">
         <f>ROUND(C9/$B8*100,2)</f>
         <v>0.12</v>
@@ -33747,22 +33920,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="61">
+      <c r="A12" s="60">
         <v>7000</v>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="60">
         <v>57613</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
-      <c r="F12" s="62"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
     </row>
     <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="61"/>
-      <c r="B13" s="61"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="60"/>
       <c r="C13" s="34">
         <v>90.486000000000004</v>
       </c>
@@ -33777,18 +33950,18 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="61"/>
-      <c r="B14" s="61"/>
-      <c r="C14" s="62" t="s">
+      <c r="A14" s="60"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="62"/>
-      <c r="E14" s="62"/>
-      <c r="F14" s="62"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
     </row>
     <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="61"/>
-      <c r="B15" s="61"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="34">
         <f>ROUND(C13/$B12*100,2)</f>
         <v>0.16</v>
@@ -33807,36 +33980,36 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="61"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="62" t="s">
+      <c r="A16" s="60"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="62"/>
-      <c r="E16" s="62"/>
-      <c r="F16" s="62"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
     </row>
     <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="61"/>
-      <c r="B17" s="61"/>
+      <c r="A17" s="60"/>
+      <c r="B17" s="60"/>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
     </row>
     <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="61"/>
-      <c r="B18" s="61"/>
-      <c r="C18" s="62" t="s">
+      <c r="A18" s="60"/>
+      <c r="B18" s="60"/>
+      <c r="C18" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="62"/>
-      <c r="E18" s="62"/>
-      <c r="F18" s="62"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
     </row>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="60"/>
       <c r="C19" s="34" t="e">
         <f>ROUND(C17/$B16*100,2)</f>
         <v>#DIV/0!</v>
@@ -33922,15 +34095,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="55" t="s">
+      <c r="B1" s="43"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="E1" s="66" t="s">
         <v>19</v>
       </c>
     </row>
@@ -33938,21 +34111,21 @@
       <c r="A2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
     </row>
     <row r="3" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
     </row>
     <row r="4" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -34023,13 +34196,13 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
@@ -34055,16 +34228,16 @@
         <v>10000</v>
       </c>
       <c r="F9" s="31"/>
-      <c r="G9" s="66" t="s">
+      <c r="G9" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="57" t="s">
+      <c r="H9" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
     </row>
     <row r="10" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
@@ -34083,14 +34256,14 @@
         <v>9358</v>
       </c>
       <c r="F10" s="31"/>
-      <c r="G10" s="67"/>
+      <c r="G10" s="63"/>
       <c r="H10" s="33">
         <v>16</v>
       </c>
       <c r="I10" s="33">
         <v>32</v>
       </c>
-      <c r="J10" s="64">
+      <c r="J10" s="35">
         <v>64</v>
       </c>
       <c r="K10" s="33">
@@ -34126,7 +34299,7 @@
       <c r="I11" s="34">
         <v>946</v>
       </c>
-      <c r="J11" s="65">
+      <c r="J11" s="36">
         <v>756</v>
       </c>
       <c r="K11" s="34">
@@ -34162,7 +34335,7 @@
       <c r="I12" s="34">
         <v>5578</v>
       </c>
-      <c r="J12" s="65">
+      <c r="J12" s="36">
         <v>3586</v>
       </c>
       <c r="K12" s="34">
@@ -34173,13 +34346,13 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+      <c r="A13" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
       <c r="F13" s="31"/>
       <c r="L13" s="31"/>
     </row>
@@ -34200,15 +34373,15 @@
         <v>7000</v>
       </c>
       <c r="F14" s="31"/>
-      <c r="G14" s="66" t="s">
+      <c r="G14" s="62" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="35" t="s">
+      <c r="H14" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="36"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
       <c r="L14" s="31"/>
     </row>
     <row r="15" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
@@ -34228,11 +34401,11 @@
         <v>1698</v>
       </c>
       <c r="F15" s="31"/>
-      <c r="G15" s="67"/>
+      <c r="G15" s="63"/>
       <c r="H15" s="33">
         <v>16</v>
       </c>
-      <c r="I15" s="64">
+      <c r="I15" s="35">
         <v>32</v>
       </c>
       <c r="J15" s="33">
@@ -34266,7 +34439,7 @@
       <c r="H16" s="34">
         <v>2256</v>
       </c>
-      <c r="I16" s="65">
+      <c r="I16" s="36">
         <v>1332</v>
       </c>
       <c r="J16" s="34">
@@ -34300,7 +34473,7 @@
       <c r="H17" s="34">
         <v>7481</v>
       </c>
-      <c r="I17" s="65">
+      <c r="I17" s="36">
         <v>4620</v>
       </c>
       <c r="J17" s="34">
@@ -34388,4 +34561,564 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84842B6-7842-488D-9BA9-218EFFDB7E51}">
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="69" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="21.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="1"/>
+    <col min="7" max="12" width="11.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="70"/>
+    </row>
+    <row r="2" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+    </row>
+    <row r="3" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="64" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+    </row>
+    <row r="4" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="37">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="37">
+        <v>3000</v>
+      </c>
+      <c r="D4" s="37">
+        <v>7000</v>
+      </c>
+      <c r="E4" s="37">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="72">
+        <v>44</v>
+      </c>
+      <c r="C5" s="72">
+        <v>454</v>
+      </c>
+      <c r="D5" s="72">
+        <v>4432</v>
+      </c>
+      <c r="E5" s="72">
+        <v>12310</v>
+      </c>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+    </row>
+    <row r="6" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="28">
+        <v>25</v>
+      </c>
+      <c r="C6" s="28">
+        <v>408</v>
+      </c>
+      <c r="D6" s="28">
+        <v>3188</v>
+      </c>
+      <c r="E6" s="28">
+        <v>7513</v>
+      </c>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+    </row>
+    <row r="7" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="30">
+        <f>ROUND(100 - B5*100/B6,2)</f>
+        <v>-76</v>
+      </c>
+      <c r="C7" s="30">
+        <f t="shared" ref="C7:E7" si="0">ROUND(100 - C5*100/C6,2)</f>
+        <v>-11.27</v>
+      </c>
+      <c r="D7" s="30">
+        <f t="shared" si="0"/>
+        <v>-39.020000000000003</v>
+      </c>
+      <c r="E7" s="30">
+        <f t="shared" si="0"/>
+        <v>-63.85</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+    </row>
+    <row r="8" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="24"/>
+    </row>
+    <row r="9" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="37">
+        <v>3000</v>
+      </c>
+      <c r="C9" s="37">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="37">
+        <v>7000</v>
+      </c>
+      <c r="E9" s="37">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="21"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="40"/>
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="40"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="24"/>
+    </row>
+    <row r="10" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="72">
+        <v>169</v>
+      </c>
+      <c r="C10" s="72">
+        <v>522</v>
+      </c>
+      <c r="D10" s="72">
+        <v>1230</v>
+      </c>
+      <c r="E10" s="72">
+        <v>4092</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="24"/>
+    </row>
+    <row r="11" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="28">
+        <v>188</v>
+      </c>
+      <c r="C11" s="28">
+        <v>563</v>
+      </c>
+      <c r="D11" s="28">
+        <v>1383</v>
+      </c>
+      <c r="E11" s="28">
+        <v>4204</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="39"/>
+      <c r="J11" s="39"/>
+      <c r="K11" s="39"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="24"/>
+    </row>
+    <row r="12" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" s="79">
+        <f>ROUND(100 - B10*100/B11,2)</f>
+        <v>10.11</v>
+      </c>
+      <c r="C12" s="79">
+        <f>ROUND(100 - C10*100/C11,2)</f>
+        <v>7.28</v>
+      </c>
+      <c r="D12" s="79">
+        <f t="shared" ref="D12" si="1">ROUND(100 - D10*100/D11,2)</f>
+        <v>11.06</v>
+      </c>
+      <c r="E12" s="79">
+        <f t="shared" ref="E12" si="2">ROUND(100 - E10*100/E11,2)</f>
+        <v>2.66</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="38"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="24"/>
+    </row>
+    <row r="13" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="24"/>
+    </row>
+    <row r="14" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="37">
+        <v>2000</v>
+      </c>
+      <c r="C14" s="37">
+        <v>3000</v>
+      </c>
+      <c r="D14" s="37">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="37">
+        <v>7000</v>
+      </c>
+      <c r="F14" s="21"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="24"/>
+    </row>
+    <row r="15" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="71" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="72">
+        <v>1402</v>
+      </c>
+      <c r="C15" s="72">
+        <v>4601</v>
+      </c>
+      <c r="D15" s="72">
+        <v>20947</v>
+      </c>
+      <c r="E15" s="72">
+        <v>60964</v>
+      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="24"/>
+    </row>
+    <row r="16" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="28">
+        <v>2260</v>
+      </c>
+      <c r="C16" s="28">
+        <v>6671</v>
+      </c>
+      <c r="D16" s="28">
+        <v>26654</v>
+      </c>
+      <c r="E16" s="28">
+        <v>68131</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="24"/>
+    </row>
+    <row r="17" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="78" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="79">
+        <f>ROUND(100 - B15*100/B16,2)</f>
+        <v>37.96</v>
+      </c>
+      <c r="C17" s="79">
+        <f t="shared" ref="C17" si="3">ROUND(100 - C15*100/C16,2)</f>
+        <v>31.03</v>
+      </c>
+      <c r="D17" s="79">
+        <f t="shared" ref="D17" si="4">ROUND(100 - D15*100/D16,2)</f>
+        <v>21.41</v>
+      </c>
+      <c r="E17" s="79">
+        <f t="shared" ref="E17" si="5">ROUND(100 - E15*100/E16,2)</f>
+        <v>10.52</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="38"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="21"/>
+      <c r="M17" s="24"/>
+    </row>
+    <row r="18" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="F18" s="21"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="21"/>
+      <c r="M18" s="24"/>
+    </row>
+    <row r="19" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21"/>
+      <c r="M19" s="24"/>
+    </row>
+    <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F20" s="21"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="24"/>
+    </row>
+    <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F21" s="31"/>
+      <c r="L21" s="31"/>
+    </row>
+    <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F22" s="31"/>
+      <c r="L22" s="31"/>
+    </row>
+    <row r="23" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F23" s="31"/>
+      <c r="L23" s="31"/>
+    </row>
+    <row r="24" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F24" s="20"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="20"/>
+    </row>
+    <row r="25" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="20"/>
+    </row>
+    <row r="26" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+    </row>
+    <row r="27" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="A27" s="73"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="74"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="74"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="19"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="19"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+    </row>
+    <row r="32" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
+      <c r="A32" s="73"/>
+      <c r="B32" s="74"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="74"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="19"/>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="19"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="19"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="19"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="19"/>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="19"/>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/DecompositionLU/docs/version_3.2_statistics.xlsx
+++ b/DecompositionLU/docs/version_3.2_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B778901E-AF75-4789-BD7E-7899687AB1EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABDE1C9-F645-48BB-8EDE-4FACB14BDEA4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Графики" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="63">
   <si>
     <t>Замеры версии 3.2</t>
   </si>
@@ -264,9 +264,6 @@
     </r>
   </si>
   <si>
-    <t>Сравнение версии 3.2 и Eigen::PartialPivLU&lt;Eigen::MatrixXd&gt;</t>
-  </si>
-  <si>
     <t>Примечание: приведено только время LU разложения</t>
   </si>
   <si>
@@ -286,6 +283,51 @@
   </si>
   <si>
     <t>Есть некоторые проблемы</t>
+  </si>
+  <si>
+    <t>Сравнение версии 3.2 и eigen-3.4.0</t>
+  </si>
+  <si>
+    <t>Сравнение версии 3.2 и eigen-5.0.0</t>
+  </si>
+  <si>
+    <t>Процент времени Eigen от времени версии 3.2,</t>
+  </si>
+  <si>
+    <t>Для справки: год выхода - 2021</t>
+  </si>
+  <si>
+    <t>Для справки: год выхода - 2025</t>
+  </si>
+  <si>
+    <t>Есть проблемы</t>
+  </si>
+  <si>
+    <t>Появились проблемы</t>
+  </si>
+  <si>
+    <t>Всё еще быстрее)</t>
+  </si>
+  <si>
+    <t>Итог:</t>
+  </si>
+  <si>
+    <t>На кластерах версия быстрее, однако на ноутбуке выигрывает eigen</t>
+  </si>
+  <si>
+    <t>Версия eigen выигрывает на процессорах архитектуры х86, но на risk-V работает ощутимо медленнее</t>
+  </si>
+  <si>
+    <t>Время без векторизации</t>
+  </si>
+  <si>
+    <t>Про векторизацию</t>
+  </si>
+  <si>
+    <t>Выигрыш, %</t>
+  </si>
+  <si>
+    <t>Не сработали ключи</t>
   </si>
 </sst>
 </file>
@@ -399,7 +441,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -463,6 +505,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,7 +635,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -673,9 +721,6 @@
     <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -686,14 +731,51 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -713,37 +795,19 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -773,26 +837,39 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -803,6 +880,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF6600"/>
+      <color rgb="FF66FF66"/>
       <color rgb="FF800080"/>
       <color rgb="FFCC00CC"/>
     </mruColors>
@@ -1470,37 +1549,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>42420</c:v>
+                  <c:v>42432</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>21202</c:v>
+                  <c:v>21304</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11078</c:v>
+                  <c:v>11216</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7787</c:v>
+                  <c:v>7807</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6260</c:v>
+                  <c:v>6310</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5372</c:v>
+                  <c:v>5315</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4574</c:v>
+                  <c:v>4635</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4295</c:v>
+                  <c:v>4175</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3969</c:v>
+                  <c:v>3919</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3709</c:v>
+                  <c:v>3662</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3554</c:v>
+                  <c:v>3489</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1871,37 +1950,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>143042</c:v>
+                  <c:v>144977</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>70771</c:v>
+                  <c:v>71552</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36194</c:v>
+                  <c:v>36660</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25435</c:v>
+                  <c:v>25225</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>19632</c:v>
+                  <c:v>20733</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>16476</c:v>
+                  <c:v>16914</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>14220</c:v>
+                  <c:v>13976</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13252</c:v>
+                  <c:v>13026</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12007</c:v>
+                  <c:v>11592</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11351</c:v>
+                  <c:v>11199</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>10371</c:v>
+                  <c:v>10302</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2404,34 +2483,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0211999999999999</c:v>
+                  <c:v>2.0261800000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9520900000000001</c:v>
+                  <c:v>3.9546399999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.6238299999999999</c:v>
+                  <c:v>5.74735</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2861700000000003</c:v>
+                  <c:v>6.9925699999999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6818399999999993</c:v>
+                  <c:v>8.5714199999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.05921</c:v>
+                  <c:v>10.373279999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.793990000000001</c:v>
+                  <c:v>11.12982</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.913220000000001</c:v>
+                  <c:v>12.506640000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.601710000000001</c:v>
+                  <c:v>12.94553</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>13.7925</c:v>
+                  <c:v>14.072699999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2935,34 +3014,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.00075</c:v>
+                  <c:v>1.9917400000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.8292099999999998</c:v>
+                  <c:v>3.7831700000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.44754</c:v>
+                  <c:v>5.4351200000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.7763600000000004</c:v>
+                  <c:v>6.7245600000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.8964999999999996</c:v>
+                  <c:v>7.9834399999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.2741600000000002</c:v>
+                  <c:v>9.1546900000000004</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>9.8765999999999998</c:v>
+                  <c:v>10.163349999999999</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.68783</c:v>
+                  <c:v>10.827249999999999</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.437049999999999</c:v>
+                  <c:v>11.587109999999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11.93585</c:v>
+                  <c:v>12.16165</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7695,34 +7774,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0794699999999999</c:v>
+                  <c:v>0.99890000000000001</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.03521</c:v>
+                  <c:v>0.96716999999999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.94513999999999998</c:v>
+                  <c:v>0.93030999999999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.90297000000000005</c:v>
+                  <c:v>0.84370999999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.86641999999999997</c:v>
+                  <c:v>0.81381000000000003</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.83179000000000003</c:v>
+                  <c:v>0.79518999999999995</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.76739999999999997</c:v>
+                  <c:v>0.70775999999999994</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.70077999999999996</c:v>
+                  <c:v>0.65776999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.66052</c:v>
+                  <c:v>0.59391000000000005</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.62727999999999995</c:v>
+                  <c:v>0.55647000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8222,34 +8301,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.00038</c:v>
+                  <c:v>0.99587000000000003</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.95730000000000004</c:v>
+                  <c:v>0.94579000000000002</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.90791999999999995</c:v>
+                  <c:v>0.90585000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84704999999999997</c:v>
+                  <c:v>0.84057000000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.78964999999999996</c:v>
+                  <c:v>0.79834000000000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.77285000000000004</c:v>
+                  <c:v>0.76288999999999996</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.70547000000000004</c:v>
+                  <c:v>0.72594999999999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.66798999999999997</c:v>
+                  <c:v>0.67669999999999997</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.63539000000000001</c:v>
+                  <c:v>0.64373000000000002</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.59679000000000004</c:v>
+                  <c:v>0.60807999999999995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8790,34 +8869,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0105999999999999</c:v>
+                  <c:v>1.01309</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98802000000000001</c:v>
+                  <c:v>0.98865999999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.93730999999999998</c:v>
+                  <c:v>0.95789000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.91076999999999997</c:v>
+                  <c:v>0.87407000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.86817999999999995</c:v>
+                  <c:v>0.85714000000000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.83826999999999996</c:v>
+                  <c:v>0.86443999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.77100000000000002</c:v>
+                  <c:v>0.79498999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.74458000000000002</c:v>
+                  <c:v>0.78166999999999998</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.70009999999999994</c:v>
+                  <c:v>0.71919999999999995</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.68962999999999997</c:v>
+                  <c:v>0.70364000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9320,34 +9399,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.1589299999999998</c:v>
+                  <c:v>1.99779</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.1408500000000004</c:v>
+                  <c:v>3.8686699999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.6708299999999996</c:v>
+                  <c:v>5.5818700000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.2237200000000001</c:v>
+                  <c:v>6.7496900000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.6642200000000003</c:v>
+                  <c:v>8.1381399999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.98142</c:v>
+                  <c:v>9.5422499999999992</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>10.743639999999999</c:v>
+                  <c:v>9.9085900000000002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>11.21252</c:v>
+                  <c:v>10.52427</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.889340000000001</c:v>
+                  <c:v>10.690340000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.54565</c:v>
+                  <c:v>11.12936</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9719,37 +9798,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>5909</c:v>
+                  <c:v>5420</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2737</c:v>
+                  <c:v>2713</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1427</c:v>
+                  <c:v>1401</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1042</c:v>
+                  <c:v>971</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>818</c:v>
+                  <c:v>803</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>682</c:v>
+                  <c:v>666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>592</c:v>
+                  <c:v>568</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>550</c:v>
+                  <c:v>547</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>527</c:v>
+                  <c:v>515</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>497</c:v>
+                  <c:v>507</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>471</c:v>
+                  <c:v>487</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -29259,6 +29338,116 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9054</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>113168</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="TextBox 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4EFA4A6-A70C-43DC-BBB7-2A6A3B9C1DDD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8510258" y="1851433"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>9054</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>113168</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="65" cy="172227"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="TextBox 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{923E637A-5992-456F-B7A9-7DBB8A2D5FC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8510258" y="2937849"/>
+          <a:ext cx="65" cy="172227"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="ru-RU" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -29595,30 +29784,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="75" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53"/>
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="76"/>
-      <c r="Q1" s="76"/>
-      <c r="R1" s="76"/>
-      <c r="S1" s="76"/>
-      <c r="T1" s="77"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="55"/>
+      <c r="R1" s="55"/>
+      <c r="S1" s="55"/>
+      <c r="T1" s="56"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -29630,15 +29819,15 @@
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="47"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="59"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -29665,7 +29854,7 @@
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="44"/>
+      <c r="A3" s="49"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -29704,7 +29893,7 @@
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44"/>
+      <c r="A4" s="49"/>
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -29743,7 +29932,7 @@
       <c r="AC4" s="1"/>
     </row>
     <row r="5" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="44"/>
+      <c r="A5" s="49"/>
       <c r="B5" s="4">
         <v>2</v>
       </c>
@@ -29782,7 +29971,7 @@
       <c r="AC5" s="1"/>
     </row>
     <row r="6" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -29821,7 +30010,7 @@
       <c r="AC6" s="1"/>
     </row>
     <row r="7" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44"/>
+      <c r="A7" s="49"/>
       <c r="B7" s="4">
         <v>6</v>
       </c>
@@ -29860,7 +30049,7 @@
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
+      <c r="A8" s="49"/>
       <c r="B8" s="4">
         <v>8</v>
       </c>
@@ -29899,7 +30088,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="44"/>
+      <c r="A9" s="49"/>
       <c r="B9" s="4">
         <v>10</v>
       </c>
@@ -29938,7 +30127,7 @@
       <c r="AC9" s="1"/>
     </row>
     <row r="10" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
+      <c r="A10" s="49"/>
       <c r="B10" s="4">
         <v>12</v>
       </c>
@@ -29977,7 +30166,7 @@
       <c r="AC10" s="1"/>
     </row>
     <row r="11" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
+      <c r="A11" s="49"/>
       <c r="B11" s="4">
         <v>16</v>
       </c>
@@ -30016,13 +30205,13 @@
       <c r="AC11" s="1"/>
     </row>
     <row r="12" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="45" t="s">
+      <c r="A12" s="49"/>
+      <c r="B12" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="46"/>
-      <c r="D12" s="46"/>
-      <c r="E12" s="47"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="59"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -30049,7 +30238,7 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
+      <c r="A13" s="49"/>
       <c r="B13" s="3" t="s">
         <v>4</v>
       </c>
@@ -30088,7 +30277,7 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="3">
         <v>1</v>
       </c>
@@ -30130,7 +30319,7 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="44"/>
+      <c r="A15" s="49"/>
       <c r="B15" s="3">
         <v>2</v>
       </c>
@@ -30172,7 +30361,7 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44"/>
+      <c r="A16" s="49"/>
       <c r="B16" s="3">
         <v>4</v>
       </c>
@@ -30214,7 +30403,7 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="44"/>
+      <c r="A17" s="49"/>
       <c r="B17" s="3">
         <v>6</v>
       </c>
@@ -30256,7 +30445,7 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="3">
         <v>8</v>
       </c>
@@ -30298,7 +30487,7 @@
       <c r="AC18" s="1"/>
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="44"/>
+      <c r="A19" s="49"/>
       <c r="B19" s="3">
         <v>10</v>
       </c>
@@ -30340,7 +30529,7 @@
       <c r="AC19" s="1"/>
     </row>
     <row r="20" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
+      <c r="A20" s="49"/>
       <c r="B20" s="3">
         <v>12</v>
       </c>
@@ -30382,7 +30571,7 @@
       <c r="AC20" s="1"/>
     </row>
     <row r="21" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
+      <c r="A21" s="49"/>
       <c r="B21" s="3">
         <v>16</v>
       </c>
@@ -30424,13 +30613,13 @@
       <c r="AC21" s="1"/>
     </row>
     <row r="22" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
-      <c r="B22" s="45" t="s">
+      <c r="A22" s="49"/>
+      <c r="B22" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="46"/>
-      <c r="E22" s="47"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="59"/>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -30457,7 +30646,7 @@
       <c r="AC22" s="1"/>
     </row>
     <row r="23" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
+      <c r="A23" s="49"/>
       <c r="B23" s="3" t="s">
         <v>4</v>
       </c>
@@ -30496,7 +30685,7 @@
       <c r="AC23" s="1"/>
     </row>
     <row r="24" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="44"/>
+      <c r="A24" s="49"/>
       <c r="B24" s="3">
         <v>1</v>
       </c>
@@ -30538,7 +30727,7 @@
       <c r="AC24" s="1"/>
     </row>
     <row r="25" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="3">
         <v>2</v>
       </c>
@@ -30580,7 +30769,7 @@
       <c r="AC25" s="1"/>
     </row>
     <row r="26" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="44"/>
+      <c r="A26" s="49"/>
       <c r="B26" s="3">
         <v>4</v>
       </c>
@@ -30622,7 +30811,7 @@
       <c r="AC26" s="1"/>
     </row>
     <row r="27" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="44"/>
+      <c r="A27" s="49"/>
       <c r="B27" s="3">
         <v>6</v>
       </c>
@@ -30664,7 +30853,7 @@
       <c r="AC27" s="1"/>
     </row>
     <row r="28" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
+      <c r="A28" s="49"/>
       <c r="B28" s="3">
         <v>8</v>
       </c>
@@ -30706,7 +30895,7 @@
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="44"/>
+      <c r="A29" s="49"/>
       <c r="B29" s="3">
         <v>10</v>
       </c>
@@ -30748,7 +30937,7 @@
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="44"/>
+      <c r="A30" s="49"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
@@ -30790,7 +30979,7 @@
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="44"/>
+      <c r="A31" s="49"/>
       <c r="B31" s="3">
         <v>16</v>
       </c>
@@ -30832,30 +31021,30 @@
       <c r="AC31" s="1"/>
     </row>
     <row r="32" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="44"/>
+      <c r="A32" s="49"/>
       <c r="B32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="49"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="49"/>
-      <c r="K32" s="49"/>
-      <c r="L32" s="49"/>
-      <c r="M32" s="49"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="49"/>
-      <c r="P32" s="49"/>
-      <c r="Q32" s="49"/>
-      <c r="R32" s="49"/>
-      <c r="S32" s="49"/>
-      <c r="T32" s="50"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+      <c r="J32" s="61"/>
+      <c r="K32" s="61"/>
+      <c r="L32" s="61"/>
+      <c r="M32" s="61"/>
+      <c r="N32" s="61"/>
+      <c r="O32" s="61"/>
+      <c r="P32" s="61"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="62"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -30867,15 +31056,15 @@
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="52" t="s">
+      <c r="A33" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -30902,7 +31091,7 @@
       <c r="AC33" s="19"/>
     </row>
     <row r="34" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="53"/>
+      <c r="A34" s="47"/>
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
@@ -30941,18 +31130,18 @@
       <c r="AC34" s="19"/>
     </row>
     <row r="35" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="53"/>
+      <c r="A35" s="47"/>
       <c r="B35" s="4">
         <v>1</v>
       </c>
       <c r="C35" s="6">
-        <v>5909</v>
+        <v>5420</v>
       </c>
       <c r="D35" s="6">
-        <v>42420</v>
+        <v>42432</v>
       </c>
       <c r="E35" s="6">
-        <v>143042</v>
+        <v>144977</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -30980,18 +31169,18 @@
       <c r="AC35" s="19"/>
     </row>
     <row r="36" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="53"/>
+      <c r="A36" s="47"/>
       <c r="B36" s="4">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2737</v>
+        <v>2713</v>
       </c>
       <c r="D36" s="6">
-        <v>21202</v>
+        <v>21304</v>
       </c>
       <c r="E36" s="6">
-        <v>70771</v>
+        <v>71552</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -31019,18 +31208,18 @@
       <c r="AC36" s="19"/>
     </row>
     <row r="37" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="53"/>
+      <c r="A37" s="47"/>
       <c r="B37" s="4">
         <v>4</v>
       </c>
       <c r="C37" s="6">
-        <v>1427</v>
+        <v>1401</v>
       </c>
       <c r="D37" s="6">
-        <v>11078</v>
+        <v>11216</v>
       </c>
       <c r="E37" s="6">
-        <v>36194</v>
+        <v>36660</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -31058,18 +31247,18 @@
       <c r="AC37" s="19"/>
     </row>
     <row r="38" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="53"/>
+      <c r="A38" s="47"/>
       <c r="B38" s="4">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>1042</v>
+        <v>971</v>
       </c>
       <c r="D38" s="6">
-        <v>7787</v>
+        <v>7807</v>
       </c>
       <c r="E38" s="6">
-        <v>25435</v>
+        <v>25225</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -31097,18 +31286,18 @@
       <c r="AC38" s="19"/>
     </row>
     <row r="39" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="53"/>
+      <c r="A39" s="47"/>
       <c r="B39" s="4">
         <v>8</v>
       </c>
       <c r="C39" s="5">
-        <v>818</v>
+        <v>803</v>
       </c>
       <c r="D39" s="6">
-        <v>6260</v>
+        <v>6310</v>
       </c>
       <c r="E39" s="6">
-        <v>19632</v>
+        <v>20733</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
@@ -31136,18 +31325,18 @@
       <c r="AC39" s="19"/>
     </row>
     <row r="40" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="53"/>
+      <c r="A40" s="47"/>
       <c r="B40" s="4">
         <v>10</v>
       </c>
       <c r="C40" s="5">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="D40" s="6">
-        <v>5372</v>
+        <v>5315</v>
       </c>
       <c r="E40" s="6">
-        <v>16476</v>
+        <v>16914</v>
       </c>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
@@ -31175,18 +31364,18 @@
       <c r="AC40" s="19"/>
     </row>
     <row r="41" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="53"/>
+      <c r="A41" s="47"/>
       <c r="B41" s="4">
         <v>12</v>
       </c>
       <c r="C41" s="5">
-        <v>592</v>
+        <v>568</v>
       </c>
       <c r="D41" s="6">
-        <v>4574</v>
+        <v>4635</v>
       </c>
       <c r="E41" s="6">
-        <v>14220</v>
+        <v>13976</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
@@ -31214,18 +31403,18 @@
       <c r="AC41" s="19"/>
     </row>
     <row r="42" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="53"/>
+      <c r="A42" s="47"/>
       <c r="B42" s="4">
         <v>14</v>
       </c>
       <c r="C42" s="5">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D42" s="6">
-        <v>4295</v>
+        <v>4175</v>
       </c>
       <c r="E42" s="6">
-        <v>13252</v>
+        <v>13026</v>
       </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
@@ -31253,18 +31442,18 @@
       <c r="AC42" s="19"/>
     </row>
     <row r="43" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="53"/>
+      <c r="A43" s="47"/>
       <c r="B43" s="4">
         <v>16</v>
       </c>
       <c r="C43" s="5">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="D43" s="6">
-        <v>3969</v>
+        <v>3919</v>
       </c>
       <c r="E43" s="6">
-        <v>12007</v>
+        <v>11592</v>
       </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
@@ -31292,18 +31481,18 @@
       <c r="AC43" s="19"/>
     </row>
     <row r="44" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="53"/>
+      <c r="A44" s="47"/>
       <c r="B44" s="4">
         <v>18</v>
       </c>
       <c r="C44" s="5">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="D44" s="6">
-        <v>3709</v>
+        <v>3662</v>
       </c>
       <c r="E44" s="6">
-        <v>11351</v>
+        <v>11199</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -31331,18 +31520,18 @@
       <c r="AC44" s="19"/>
     </row>
     <row r="45" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="53"/>
+      <c r="A45" s="47"/>
       <c r="B45" s="4">
         <v>20</v>
       </c>
       <c r="C45" s="5">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="D45" s="6">
-        <v>3554</v>
+        <v>3489</v>
       </c>
       <c r="E45" s="6">
-        <v>10371</v>
+        <v>10302</v>
       </c>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
@@ -31370,18 +31559,18 @@
       <c r="AC45" s="19"/>
     </row>
     <row r="46" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="53"/>
+      <c r="A46" s="47"/>
       <c r="B46" s="10">
         <v>40</v>
       </c>
       <c r="C46" s="11">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="D46" s="12">
-        <v>3697</v>
+        <v>3675</v>
       </c>
       <c r="E46" s="12">
-        <v>11163</v>
+        <v>10632</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -31409,13 +31598,13 @@
       <c r="AC46" s="19"/>
     </row>
     <row r="47" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="54" t="s">
+      <c r="A47" s="47"/>
+      <c r="B47" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -31442,7 +31631,7 @@
       <c r="AC47" s="19"/>
     </row>
     <row r="48" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
+      <c r="A48" s="47"/>
       <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
@@ -31481,7 +31670,7 @@
       <c r="AC48" s="20"/>
     </row>
     <row r="49" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
+      <c r="A49" s="47"/>
       <c r="B49" s="4">
         <v>1</v>
       </c>
@@ -31523,21 +31712,21 @@
       <c r="AC49" s="20"/>
     </row>
     <row r="50" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
+      <c r="A50" s="47"/>
       <c r="B50" s="4">
         <v>2</v>
       </c>
       <c r="C50" s="5">
         <f>ROUND(C35/C36,5)</f>
-        <v>2.1589299999999998</v>
+        <v>1.99779</v>
       </c>
       <c r="D50" s="5">
         <f>ROUND(D35/D36,5)</f>
-        <v>2.00075</v>
+        <v>1.9917400000000001</v>
       </c>
       <c r="E50" s="5">
         <f>ROUND(E35/E36,5)</f>
-        <v>2.0211999999999999</v>
+        <v>2.0261800000000001</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
@@ -31565,21 +31754,21 @@
       <c r="AC50" s="20"/>
     </row>
     <row r="51" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="53"/>
+      <c r="A51" s="47"/>
       <c r="B51" s="4">
         <v>4</v>
       </c>
       <c r="C51" s="5">
         <f>ROUND(C35/C37,5)</f>
-        <v>4.1408500000000004</v>
+        <v>3.8686699999999998</v>
       </c>
       <c r="D51" s="5">
         <f>ROUND(D35/D37,5)</f>
-        <v>3.8292099999999998</v>
+        <v>3.7831700000000001</v>
       </c>
       <c r="E51" s="5">
         <f>ROUND(E35/E37,5)</f>
-        <v>3.9520900000000001</v>
+        <v>3.9546399999999999</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
@@ -31607,21 +31796,21 @@
       <c r="AC51" s="20"/>
     </row>
     <row r="52" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="53"/>
+      <c r="A52" s="47"/>
       <c r="B52" s="4">
         <v>6</v>
       </c>
       <c r="C52" s="5">
         <f>ROUND(C35/C38,5)</f>
-        <v>5.6708299999999996</v>
+        <v>5.5818700000000003</v>
       </c>
       <c r="D52" s="5">
         <f>ROUND(D35/D38,5)</f>
-        <v>5.44754</v>
+        <v>5.4351200000000004</v>
       </c>
       <c r="E52" s="5">
         <f>ROUND(E35/E38,5)</f>
-        <v>5.6238299999999999</v>
+        <v>5.74735</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
@@ -31649,21 +31838,21 @@
       <c r="AC52" s="20"/>
     </row>
     <row r="53" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="53"/>
+      <c r="A53" s="47"/>
       <c r="B53" s="13">
         <v>8</v>
       </c>
       <c r="C53" s="14">
         <f>ROUND(C35/C39,5)</f>
-        <v>7.2237200000000001</v>
+        <v>6.7496900000000002</v>
       </c>
       <c r="D53" s="14">
         <f>ROUND(D35/D39,5)</f>
-        <v>6.7763600000000004</v>
+        <v>6.7245600000000003</v>
       </c>
       <c r="E53" s="14">
         <f>ROUND(E35/E39,5)</f>
-        <v>7.2861700000000003</v>
+        <v>6.9925699999999997</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
@@ -31691,21 +31880,21 @@
       <c r="AC53" s="20"/>
     </row>
     <row r="54" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
+      <c r="A54" s="47"/>
       <c r="B54" s="4">
         <v>10</v>
       </c>
       <c r="C54" s="5">
         <f>ROUND(C35/C40,5)</f>
-        <v>8.6642200000000003</v>
+        <v>8.1381399999999999</v>
       </c>
       <c r="D54" s="5">
         <f>ROUND(D35/D40,5)</f>
-        <v>7.8964999999999996</v>
+        <v>7.9834399999999999</v>
       </c>
       <c r="E54" s="5">
         <f>ROUND(E35/E40,5)</f>
-        <v>8.6818399999999993</v>
+        <v>8.5714199999999998</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
@@ -31733,21 +31922,21 @@
       <c r="AC54" s="20"/>
     </row>
     <row r="55" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
+      <c r="A55" s="47"/>
       <c r="B55" s="4">
         <v>12</v>
       </c>
       <c r="C55" s="5">
         <f>ROUND(C35/C41,5)</f>
-        <v>9.98142</v>
+        <v>9.5422499999999992</v>
       </c>
       <c r="D55" s="5">
         <f>ROUND(D$35/D41,5)</f>
-        <v>9.2741600000000002</v>
+        <v>9.1546900000000004</v>
       </c>
       <c r="E55" s="5">
         <f>ROUND(E$35/E41,5)</f>
-        <v>10.05921</v>
+        <v>10.373279999999999</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
@@ -31775,21 +31964,21 @@
       <c r="AC55" s="20"/>
     </row>
     <row r="56" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
+      <c r="A56" s="47"/>
       <c r="B56" s="4">
         <v>14</v>
       </c>
       <c r="C56" s="5">
         <f>ROUND(C$35/C42,5)</f>
-        <v>10.743639999999999</v>
+        <v>9.9085900000000002</v>
       </c>
       <c r="D56" s="5">
         <f t="shared" ref="D56:E60" si="3">ROUND(D$35/D42,5)</f>
-        <v>9.8765999999999998</v>
+        <v>10.163349999999999</v>
       </c>
       <c r="E56" s="5">
         <f t="shared" si="3"/>
-        <v>10.793990000000001</v>
+        <v>11.12982</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
@@ -31817,21 +32006,21 @@
       <c r="AC56" s="20"/>
     </row>
     <row r="57" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="53"/>
+      <c r="A57" s="47"/>
       <c r="B57" s="4">
         <v>16</v>
       </c>
       <c r="C57" s="5">
         <f t="shared" ref="C57:C60" si="4">ROUND(C$35/C43,5)</f>
-        <v>11.21252</v>
+        <v>10.52427</v>
       </c>
       <c r="D57" s="5">
         <f t="shared" si="3"/>
-        <v>10.68783</v>
+        <v>10.827249999999999</v>
       </c>
       <c r="E57" s="5">
         <f t="shared" si="3"/>
-        <v>11.913220000000001</v>
+        <v>12.506640000000001</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -31859,21 +32048,21 @@
       <c r="AC57" s="19"/>
     </row>
     <row r="58" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="53"/>
+      <c r="A58" s="47"/>
       <c r="B58" s="4">
         <v>18</v>
       </c>
       <c r="C58" s="5">
         <f t="shared" si="4"/>
-        <v>11.889340000000001</v>
+        <v>10.690340000000001</v>
       </c>
       <c r="D58" s="5">
         <f t="shared" si="3"/>
-        <v>11.437049999999999</v>
+        <v>11.587109999999999</v>
       </c>
       <c r="E58" s="5">
         <f t="shared" si="3"/>
-        <v>12.601710000000001</v>
+        <v>12.94553</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
@@ -31901,21 +32090,21 @@
       <c r="AC58" s="20"/>
     </row>
     <row r="59" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="53"/>
+      <c r="A59" s="47"/>
       <c r="B59" s="4">
         <v>20</v>
       </c>
       <c r="C59" s="5">
         <f t="shared" si="4"/>
-        <v>12.54565</v>
+        <v>11.12936</v>
       </c>
       <c r="D59" s="5">
         <f t="shared" si="3"/>
-        <v>11.93585</v>
+        <v>12.16165</v>
       </c>
       <c r="E59" s="5">
         <f t="shared" si="3"/>
-        <v>13.7925</v>
+        <v>14.072699999999999</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
@@ -31943,21 +32132,21 @@
       <c r="AC59" s="20"/>
     </row>
     <row r="60" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="53"/>
+      <c r="A60" s="47"/>
       <c r="B60" s="10">
         <v>40</v>
       </c>
       <c r="C60" s="11">
         <f t="shared" si="4"/>
-        <v>11.40734</v>
+        <v>10.77535</v>
       </c>
       <c r="D60" s="11">
         <f t="shared" si="3"/>
-        <v>11.474170000000001</v>
+        <v>11.54612</v>
       </c>
       <c r="E60" s="11">
         <f t="shared" si="3"/>
-        <v>12.813940000000001</v>
+        <v>13.635910000000001</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
@@ -31985,13 +32174,13 @@
       <c r="AC60" s="20"/>
     </row>
     <row r="61" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="53"/>
-      <c r="B61" s="54" t="s">
+      <c r="A61" s="47"/>
+      <c r="B61" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
+      <c r="C61" s="48"/>
+      <c r="D61" s="48"/>
+      <c r="E61" s="48"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -32018,7 +32207,7 @@
       <c r="AC61" s="20"/>
     </row>
     <row r="62" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="53"/>
+      <c r="A62" s="47"/>
       <c r="B62" s="3" t="s">
         <v>4</v>
       </c>
@@ -32057,7 +32246,7 @@
       <c r="AC62" s="20"/>
     </row>
     <row r="63" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="53"/>
+      <c r="A63" s="47"/>
       <c r="B63" s="4">
         <v>1</v>
       </c>
@@ -32099,21 +32288,21 @@
       <c r="AC63" s="20"/>
     </row>
     <row r="64" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="53"/>
+      <c r="A64" s="47"/>
       <c r="B64" s="4">
         <v>2</v>
       </c>
       <c r="C64" s="5">
         <f t="shared" si="5"/>
-        <v>1.0794699999999999</v>
+        <v>0.99890000000000001</v>
       </c>
       <c r="D64" s="5">
         <f t="shared" si="5"/>
-        <v>1.00038</v>
+        <v>0.99587000000000003</v>
       </c>
       <c r="E64" s="5">
         <f t="shared" si="5"/>
-        <v>1.0105999999999999</v>
+        <v>1.01309</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
@@ -32141,21 +32330,21 @@
       <c r="AC64" s="20"/>
     </row>
     <row r="65" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="53"/>
+      <c r="A65" s="47"/>
       <c r="B65" s="4">
         <v>4</v>
       </c>
       <c r="C65" s="5">
         <f t="shared" si="5"/>
-        <v>1.03521</v>
+        <v>0.96716999999999997</v>
       </c>
       <c r="D65" s="5">
         <f>ROUND(D51/$B51,5)</f>
-        <v>0.95730000000000004</v>
+        <v>0.94579000000000002</v>
       </c>
       <c r="E65" s="5">
         <f t="shared" si="5"/>
-        <v>0.98802000000000001</v>
+        <v>0.98865999999999998</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -32183,21 +32372,21 @@
       <c r="AC65" s="20"/>
     </row>
     <row r="66" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="53"/>
+      <c r="A66" s="47"/>
       <c r="B66" s="4">
         <v>6</v>
       </c>
       <c r="C66" s="5">
         <f t="shared" si="5"/>
-        <v>0.94513999999999998</v>
+        <v>0.93030999999999997</v>
       </c>
       <c r="D66" s="5">
         <f t="shared" si="5"/>
-        <v>0.90791999999999995</v>
+        <v>0.90585000000000004</v>
       </c>
       <c r="E66" s="5">
         <f t="shared" si="5"/>
-        <v>0.93730999999999998</v>
+        <v>0.95789000000000002</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
@@ -32225,21 +32414,21 @@
       <c r="AC66" s="20"/>
     </row>
     <row r="67" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="53"/>
+      <c r="A67" s="47"/>
       <c r="B67" s="15">
         <v>8</v>
       </c>
       <c r="C67" s="16">
         <f t="shared" si="5"/>
-        <v>0.90297000000000005</v>
+        <v>0.84370999999999996</v>
       </c>
       <c r="D67" s="16">
         <f t="shared" si="5"/>
-        <v>0.84704999999999997</v>
+        <v>0.84057000000000004</v>
       </c>
       <c r="E67" s="16">
         <f t="shared" si="5"/>
-        <v>0.91076999999999997</v>
+        <v>0.87407000000000001</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
@@ -32267,21 +32456,21 @@
       <c r="AC67" s="20"/>
     </row>
     <row r="68" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="53"/>
+      <c r="A68" s="47"/>
       <c r="B68" s="4">
         <v>10</v>
       </c>
       <c r="C68" s="5">
         <f t="shared" si="5"/>
-        <v>0.86641999999999997</v>
+        <v>0.81381000000000003</v>
       </c>
       <c r="D68" s="5">
         <f t="shared" si="5"/>
-        <v>0.78964999999999996</v>
+        <v>0.79834000000000005</v>
       </c>
       <c r="E68" s="5">
         <f t="shared" si="5"/>
-        <v>0.86817999999999995</v>
+        <v>0.85714000000000001</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
@@ -32309,21 +32498,21 @@
       <c r="AC68" s="20"/>
     </row>
     <row r="69" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="53"/>
+      <c r="A69" s="47"/>
       <c r="B69" s="4">
         <v>12</v>
       </c>
       <c r="C69" s="5">
         <f t="shared" si="5"/>
-        <v>0.83179000000000003</v>
+        <v>0.79518999999999995</v>
       </c>
       <c r="D69" s="5">
         <f t="shared" si="5"/>
-        <v>0.77285000000000004</v>
+        <v>0.76288999999999996</v>
       </c>
       <c r="E69" s="5">
         <f t="shared" si="5"/>
-        <v>0.83826999999999996</v>
+        <v>0.86443999999999999</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -32351,21 +32540,21 @@
       <c r="AC69" s="19"/>
     </row>
     <row r="70" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="53"/>
+      <c r="A70" s="47"/>
       <c r="B70" s="4">
         <v>14</v>
       </c>
       <c r="C70" s="5">
         <f t="shared" si="5"/>
-        <v>0.76739999999999997</v>
+        <v>0.70775999999999994</v>
       </c>
       <c r="D70" s="5">
         <f t="shared" si="5"/>
-        <v>0.70547000000000004</v>
+        <v>0.72594999999999998</v>
       </c>
       <c r="E70" s="5">
         <f t="shared" si="5"/>
-        <v>0.77100000000000002</v>
+        <v>0.79498999999999997</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -32393,21 +32582,21 @@
       <c r="AC70" s="19"/>
     </row>
     <row r="71" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="53"/>
+      <c r="A71" s="47"/>
       <c r="B71" s="4">
         <v>16</v>
       </c>
       <c r="C71" s="5">
         <f t="shared" si="5"/>
-        <v>0.70077999999999996</v>
+        <v>0.65776999999999997</v>
       </c>
       <c r="D71" s="5">
         <f t="shared" si="5"/>
-        <v>0.66798999999999997</v>
+        <v>0.67669999999999997</v>
       </c>
       <c r="E71" s="5">
         <f t="shared" si="5"/>
-        <v>0.74458000000000002</v>
+        <v>0.78166999999999998</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
@@ -32435,21 +32624,21 @@
       <c r="AC71" s="20"/>
     </row>
     <row r="72" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="53"/>
+      <c r="A72" s="47"/>
       <c r="B72" s="4">
         <v>18</v>
       </c>
       <c r="C72" s="5">
         <f t="shared" si="5"/>
-        <v>0.66052</v>
+        <v>0.59391000000000005</v>
       </c>
       <c r="D72" s="5">
         <f t="shared" si="5"/>
-        <v>0.63539000000000001</v>
+        <v>0.64373000000000002</v>
       </c>
       <c r="E72" s="5">
         <f t="shared" si="5"/>
-        <v>0.70009999999999994</v>
+        <v>0.71919999999999995</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -32478,21 +32667,21 @@
       <c r="AD72" s="22"/>
     </row>
     <row r="73" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="53"/>
+      <c r="A73" s="47"/>
       <c r="B73" s="4">
         <v>20</v>
       </c>
       <c r="C73" s="5">
         <f t="shared" si="5"/>
-        <v>0.62727999999999995</v>
+        <v>0.55647000000000002</v>
       </c>
       <c r="D73" s="5">
         <f t="shared" si="5"/>
-        <v>0.59679000000000004</v>
+        <v>0.60807999999999995</v>
       </c>
       <c r="E73" s="5">
         <f t="shared" si="5"/>
-        <v>0.68962999999999997</v>
+        <v>0.70364000000000004</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
@@ -32521,21 +32710,21 @@
       <c r="AD73" s="22"/>
     </row>
     <row r="74" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="53"/>
+      <c r="A74" s="47"/>
       <c r="B74" s="10">
         <v>40</v>
       </c>
       <c r="C74" s="11">
         <f t="shared" si="5"/>
-        <v>0.28517999999999999</v>
+        <v>0.26938000000000001</v>
       </c>
       <c r="D74" s="11">
         <f t="shared" si="5"/>
-        <v>0.28684999999999999</v>
+        <v>0.28865000000000002</v>
       </c>
       <c r="E74" s="11">
         <f t="shared" si="5"/>
-        <v>0.32035000000000002</v>
+        <v>0.34089999999999998</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
@@ -32564,51 +32753,51 @@
       <c r="AD74" s="22"/>
     </row>
     <row r="75" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="53"/>
+      <c r="A75" s="47"/>
       <c r="B75" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="56" t="s">
+      <c r="C75" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="56"/>
-      <c r="E75" s="56"/>
-      <c r="F75" s="56"/>
-      <c r="G75" s="56"/>
-      <c r="H75" s="56"/>
-      <c r="I75" s="56"/>
-      <c r="J75" s="56"/>
-      <c r="K75" s="56"/>
-      <c r="L75" s="56"/>
-      <c r="M75" s="56"/>
-      <c r="N75" s="56"/>
-      <c r="O75" s="56"/>
-      <c r="P75" s="56"/>
-      <c r="Q75" s="56"/>
-      <c r="R75" s="56"/>
-      <c r="S75" s="56"/>
-      <c r="T75" s="56"/>
-      <c r="U75" s="56"/>
-      <c r="V75" s="56"/>
-      <c r="W75" s="56"/>
-      <c r="X75" s="56"/>
-      <c r="Y75" s="56"/>
-      <c r="Z75" s="56"/>
-      <c r="AA75" s="56"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="51"/>
+      <c r="F75" s="51"/>
+      <c r="G75" s="51"/>
+      <c r="H75" s="51"/>
+      <c r="I75" s="51"/>
+      <c r="J75" s="51"/>
+      <c r="K75" s="51"/>
+      <c r="L75" s="51"/>
+      <c r="M75" s="51"/>
+      <c r="N75" s="51"/>
+      <c r="O75" s="51"/>
+      <c r="P75" s="51"/>
+      <c r="Q75" s="51"/>
+      <c r="R75" s="51"/>
+      <c r="S75" s="51"/>
+      <c r="T75" s="51"/>
+      <c r="U75" s="51"/>
+      <c r="V75" s="51"/>
+      <c r="W75" s="51"/>
+      <c r="X75" s="51"/>
+      <c r="Y75" s="51"/>
+      <c r="Z75" s="51"/>
+      <c r="AA75" s="51"/>
       <c r="AB75" s="23"/>
       <c r="AC75" s="23"/>
       <c r="AD75" s="22"/>
     </row>
     <row r="76" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="44" t="s">
+      <c r="A76" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B76" s="54" t="s">
+      <c r="B76" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="54"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="54"/>
+      <c r="C76" s="48"/>
+      <c r="D76" s="48"/>
+      <c r="E76" s="48"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -32636,7 +32825,7 @@
       <c r="AD76" s="22"/>
     </row>
     <row r="77" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="44"/>
+      <c r="A77" s="49"/>
       <c r="B77" s="3" t="s">
         <v>4</v>
       </c>
@@ -32676,7 +32865,7 @@
       <c r="AD77" s="22"/>
     </row>
     <row r="78" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="44"/>
+      <c r="A78" s="49"/>
       <c r="B78" s="4">
         <v>1</v>
       </c>
@@ -32716,7 +32905,7 @@
       <c r="AD78" s="22"/>
     </row>
     <row r="79" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="44"/>
+      <c r="A79" s="49"/>
       <c r="B79" s="4">
         <v>2</v>
       </c>
@@ -32755,7 +32944,7 @@
       <c r="AC79" s="1"/>
     </row>
     <row r="80" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="44"/>
+      <c r="A80" s="49"/>
       <c r="B80" s="4">
         <v>4</v>
       </c>
@@ -32794,7 +32983,7 @@
       <c r="AC80" s="1"/>
     </row>
     <row r="81" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="44"/>
+      <c r="A81" s="49"/>
       <c r="B81" s="4">
         <v>6</v>
       </c>
@@ -32833,7 +33022,7 @@
       <c r="AC81" s="1"/>
     </row>
     <row r="82" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="44"/>
+      <c r="A82" s="49"/>
       <c r="B82" s="4">
         <v>8</v>
       </c>
@@ -32872,13 +33061,13 @@
       <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="44"/>
-      <c r="B83" s="54" t="s">
+      <c r="A83" s="49"/>
+      <c r="B83" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="C83" s="54"/>
-      <c r="D83" s="54"/>
-      <c r="E83" s="54"/>
+      <c r="C83" s="48"/>
+      <c r="D83" s="48"/>
+      <c r="E83" s="48"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -32905,7 +33094,7 @@
       <c r="AC83" s="1"/>
     </row>
     <row r="84" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="44"/>
+      <c r="A84" s="49"/>
       <c r="B84" s="3" t="s">
         <v>4</v>
       </c>
@@ -32944,7 +33133,7 @@
       <c r="AC84" s="1"/>
     </row>
     <row r="85" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="44"/>
+      <c r="A85" s="49"/>
       <c r="B85" s="3">
         <v>1</v>
       </c>
@@ -32986,7 +33175,7 @@
       <c r="AC85" s="1"/>
     </row>
     <row r="86" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="44"/>
+      <c r="A86" s="49"/>
       <c r="B86" s="3">
         <v>2</v>
       </c>
@@ -33028,7 +33217,7 @@
       <c r="AC86" s="1"/>
     </row>
     <row r="87" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="44"/>
+      <c r="A87" s="49"/>
       <c r="B87" s="3">
         <v>4</v>
       </c>
@@ -33070,7 +33259,7 @@
       <c r="AC87" s="1"/>
     </row>
     <row r="88" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="44"/>
+      <c r="A88" s="49"/>
       <c r="B88" s="3">
         <v>6</v>
       </c>
@@ -33112,7 +33301,7 @@
       <c r="AC88" s="1"/>
     </row>
     <row r="89" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="44"/>
+      <c r="A89" s="49"/>
       <c r="B89" s="17">
         <v>8</v>
       </c>
@@ -33154,13 +33343,13 @@
       <c r="AC89" s="1"/>
     </row>
     <row r="90" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="44"/>
-      <c r="B90" s="54" t="s">
+      <c r="A90" s="49"/>
+      <c r="B90" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="54"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="54"/>
+      <c r="C90" s="48"/>
+      <c r="D90" s="48"/>
+      <c r="E90" s="48"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -33187,7 +33376,7 @@
       <c r="AC90" s="1"/>
     </row>
     <row r="91" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="44"/>
+      <c r="A91" s="49"/>
       <c r="B91" s="3" t="s">
         <v>4</v>
       </c>
@@ -33226,7 +33415,7 @@
       <c r="AC91" s="1"/>
     </row>
     <row r="92" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="44"/>
+      <c r="A92" s="49"/>
       <c r="B92" s="3">
         <v>1</v>
       </c>
@@ -33268,7 +33457,7 @@
       <c r="AC92" s="1"/>
     </row>
     <row r="93" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="44"/>
+      <c r="A93" s="49"/>
       <c r="B93" s="3">
         <v>2</v>
       </c>
@@ -33310,7 +33499,7 @@
       <c r="AC93" s="1"/>
     </row>
     <row r="94" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="44"/>
+      <c r="A94" s="49"/>
       <c r="B94" s="3">
         <v>4</v>
       </c>
@@ -33352,7 +33541,7 @@
       <c r="AC94" s="1"/>
     </row>
     <row r="95" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="44"/>
+      <c r="A95" s="49"/>
       <c r="B95" s="3">
         <v>6</v>
       </c>
@@ -33394,7 +33583,7 @@
       <c r="AC95" s="1"/>
     </row>
     <row r="96" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="44"/>
+      <c r="A96" s="49"/>
       <c r="B96" s="18">
         <v>8</v>
       </c>
@@ -33436,13 +33625,13 @@
       <c r="AC96" s="1"/>
     </row>
     <row r="97" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="44"/>
-      <c r="B97" s="55" t="s">
+      <c r="A97" s="49"/>
+      <c r="B97" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="55"/>
-      <c r="D97" s="55"/>
-      <c r="E97" s="55"/>
+      <c r="C97" s="50"/>
+      <c r="D97" s="50"/>
+      <c r="E97" s="50"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
@@ -33469,13 +33658,13 @@
       <c r="AC97" s="1"/>
     </row>
     <row r="98" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="44"/>
-      <c r="B98" s="51" t="s">
+      <c r="A98" s="49"/>
+      <c r="B98" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
+      <c r="C98" s="45"/>
+      <c r="D98" s="45"/>
+      <c r="E98" s="45"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -33502,11 +33691,11 @@
       <c r="AC98" s="1"/>
     </row>
     <row r="99" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="44"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
+      <c r="A99" s="49"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="45"/>
+      <c r="D99" s="45"/>
+      <c r="E99" s="45"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
@@ -33533,11 +33722,11 @@
       <c r="AC99" s="1"/>
     </row>
     <row r="100" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="44"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
+      <c r="A100" s="49"/>
+      <c r="B100" s="45"/>
+      <c r="C100" s="45"/>
+      <c r="D100" s="45"/>
+      <c r="E100" s="45"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
@@ -33564,11 +33753,11 @@
       <c r="AC100" s="1"/>
     </row>
     <row r="101" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="44"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
+      <c r="A101" s="49"/>
+      <c r="B101" s="45"/>
+      <c r="C101" s="45"/>
+      <c r="D101" s="45"/>
+      <c r="E101" s="45"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
@@ -33595,11 +33784,11 @@
       <c r="AC101" s="1"/>
     </row>
     <row r="102" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="44"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
+      <c r="A102" s="49"/>
+      <c r="B102" s="45"/>
+      <c r="C102" s="45"/>
+      <c r="D102" s="45"/>
+      <c r="E102" s="45"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="8"/>
@@ -33626,11 +33815,11 @@
       <c r="AC102" s="1"/>
     </row>
     <row r="103" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="44"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
+      <c r="A103" s="49"/>
+      <c r="B103" s="45"/>
+      <c r="C103" s="45"/>
+      <c r="D103" s="45"/>
+      <c r="E103" s="45"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="8"/>
@@ -33657,11 +33846,11 @@
       <c r="AC103" s="1"/>
     </row>
     <row r="104" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="44"/>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
+      <c r="A104" s="49"/>
+      <c r="B104" s="45"/>
+      <c r="C104" s="45"/>
+      <c r="D104" s="45"/>
+      <c r="E104" s="45"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -33688,11 +33877,11 @@
       <c r="AC104" s="1"/>
     </row>
     <row r="105" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="44"/>
-      <c r="B105" s="51"/>
-      <c r="C105" s="51"/>
-      <c r="D105" s="51"/>
-      <c r="E105" s="51"/>
+      <c r="A105" s="49"/>
+      <c r="B105" s="45"/>
+      <c r="C105" s="45"/>
+      <c r="D105" s="45"/>
+      <c r="E105" s="45"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -33720,6 +33909,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="A2:A32"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C32:T32"/>
     <mergeCell ref="B98:E105"/>
     <mergeCell ref="A33:A75"/>
     <mergeCell ref="B33:E33"/>
@@ -33731,13 +33927,6 @@
     <mergeCell ref="B90:E90"/>
     <mergeCell ref="B97:E97"/>
     <mergeCell ref="C75:AA75"/>
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="A2:A32"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C32:T32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O1" location="Таблица!A44" display="Соотв. таблица" xr:uid="{83FF44B0-CA98-46DE-9446-E04E222E13B0}"/>
@@ -33762,60 +33951,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="64" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="64" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="57"/>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="60">
+      <c r="A4" s="63">
         <v>3000</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="63">
         <v>4613</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
     </row>
     <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
+      <c r="A5" s="63"/>
+      <c r="B5" s="63"/>
       <c r="C5" s="34">
         <v>16.673999999999999</v>
       </c>
@@ -33830,18 +34019,18 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="58" t="s">
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="63"/>
       <c r="C7" s="34">
         <f>ROUND(C5/$B4*100,2)</f>
         <v>0.36</v>
@@ -33860,22 +34049,22 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="60">
+      <c r="A8" s="63">
         <v>5000</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="63">
         <v>21014</v>
       </c>
-      <c r="C8" s="61" t="s">
+      <c r="C8" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="61"/>
-      <c r="E8" s="61"/>
-      <c r="F8" s="61"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
+      <c r="A9" s="63"/>
+      <c r="B9" s="63"/>
       <c r="C9" s="34">
         <v>25.027000000000001</v>
       </c>
@@ -33890,18 +34079,18 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="60"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="58" t="s">
+      <c r="A10" s="63"/>
+      <c r="B10" s="63"/>
+      <c r="C10" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
     </row>
     <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="63"/>
       <c r="C11" s="34">
         <f>ROUND(C9/$B8*100,2)</f>
         <v>0.12</v>
@@ -33920,22 +34109,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="60">
+      <c r="A12" s="63">
         <v>7000</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="63">
         <v>57613</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
     </row>
     <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="60"/>
-      <c r="B13" s="60"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="63"/>
       <c r="C13" s="34">
         <v>90.486000000000004</v>
       </c>
@@ -33950,18 +34139,18 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="60"/>
-      <c r="B14" s="60"/>
-      <c r="C14" s="58" t="s">
+      <c r="A14" s="63"/>
+      <c r="B14" s="63"/>
+      <c r="C14" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
     </row>
     <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="63"/>
       <c r="C15" s="34">
         <f>ROUND(C13/$B12*100,2)</f>
         <v>0.16</v>
@@ -33980,52 +34169,36 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="60"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
+      <c r="A16" s="87"/>
+      <c r="B16" s="87"/>
+      <c r="C16" s="88"/>
+      <c r="D16" s="88"/>
+      <c r="E16" s="88"/>
+      <c r="F16" s="88"/>
     </row>
     <row r="17" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
+      <c r="A17" s="87"/>
+      <c r="B17" s="87"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
     </row>
     <row r="18" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
+      <c r="A18" s="87"/>
+      <c r="B18" s="87"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
+      <c r="E18" s="88"/>
+      <c r="F18" s="88"/>
     </row>
     <row r="19" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="60"/>
-      <c r="B19" s="60"/>
-      <c r="C19" s="34" t="e">
-        <f>ROUND(C17/$B16*100,2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D19" s="34" t="e">
-        <f>ROUND(D17/$B16*100,2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" s="34" t="e">
-        <f t="shared" ref="E19:F19" si="3">ROUND(E17/$B16*100,2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="34" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
+      <c r="A19" s="87"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
     </row>
     <row r="20" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="21" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -34054,11 +34227,14 @@
     <row r="44" ht="17.3" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="45" ht="17.3" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
-    <mergeCell ref="C16:F16"/>
-    <mergeCell ref="C18:F18"/>
+  <mergeCells count="19">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="A8:A11"/>
@@ -34071,13 +34247,6 @@
     <mergeCell ref="C10:F10"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34086,48 +34255,49 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD6B2D-C446-466B-9C71-121C80824D6F}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="21.7109375" customWidth="1"/>
     <col min="7" max="12" width="11.7109375" customWidth="1"/>
+    <col min="14" max="19" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="66" t="s">
+      <c r="B1" s="53"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="72" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="67" t="s">
+      <c r="B2" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
     </row>
-    <row r="3" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
     </row>
-    <row r="4" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>23</v>
       </c>
@@ -34144,7 +34314,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
         <v>24</v>
       </c>
@@ -34161,7 +34331,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
         <v>25</v>
       </c>
@@ -34177,8 +34347,14 @@
       <c r="E6" s="30">
         <v>11709</v>
       </c>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
     </row>
-    <row r="7" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
         <v>26</v>
       </c>
@@ -34194,15 +34370,21 @@
       <c r="E7" s="28">
         <v>12810</v>
       </c>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
     </row>
-    <row r="8" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+    <row r="8" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="31"/>
       <c r="G8" s="31"/>
       <c r="H8" s="31"/>
@@ -34210,8 +34392,14 @@
       <c r="J8" s="31"/>
       <c r="K8" s="31"/>
       <c r="L8" s="31"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
     </row>
-    <row r="9" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
@@ -34228,18 +34416,28 @@
         <v>10000</v>
       </c>
       <c r="F9" s="31"/>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="68" t="s">
+      <c r="H9" s="74" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="69"/>
-      <c r="J9" s="69"/>
-      <c r="K9" s="69"/>
-      <c r="L9" s="69"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="75"/>
+      <c r="N9" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="O9" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="84"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="84"/>
     </row>
-    <row r="10" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
         <v>24</v>
       </c>
@@ -34256,7 +34454,7 @@
         <v>9358</v>
       </c>
       <c r="F10" s="31"/>
-      <c r="G10" s="63"/>
+      <c r="G10" s="69"/>
       <c r="H10" s="33">
         <v>16</v>
       </c>
@@ -34272,8 +34470,18 @@
       <c r="L10" s="33">
         <v>256</v>
       </c>
+      <c r="N10" s="67"/>
+      <c r="O10" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="P10" s="85"/>
+      <c r="Q10" s="85"/>
+      <c r="R10" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" s="85"/>
     </row>
-    <row r="11" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
         <v>25</v>
       </c>
@@ -34308,8 +34516,21 @@
       <c r="L11" s="34">
         <v>1520</v>
       </c>
+      <c r="N11" s="41">
+        <v>3000</v>
+      </c>
+      <c r="O11" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="P11" s="86"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="82" t="e">
+        <f>100 - ROUND(O11*100 /B11,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S11" s="83"/>
     </row>
-    <row r="12" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
         <v>26</v>
       </c>
@@ -34344,19 +34565,38 @@
       <c r="L12" s="34">
         <v>4794</v>
       </c>
+      <c r="N12" s="41">
+        <v>5000</v>
+      </c>
+      <c r="O12" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="P12" s="86"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="82" t="e">
+        <f>100 - ROUND(O12*100 /C11,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S12" s="83"/>
     </row>
-    <row r="13" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
+    <row r="13" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="31"/>
       <c r="L13" s="31"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
     </row>
-    <row r="14" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
         <v>23</v>
       </c>
@@ -34373,18 +34613,28 @@
         <v>7000</v>
       </c>
       <c r="F14" s="31"/>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
+      <c r="I14" s="53"/>
+      <c r="J14" s="53"/>
+      <c r="K14" s="53"/>
       <c r="L14" s="31"/>
+      <c r="N14" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="O14" s="84" t="s">
+        <v>60</v>
+      </c>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84"/>
+      <c r="R14" s="84"/>
+      <c r="S14" s="84"/>
     </row>
-    <row r="15" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
         <v>24</v>
       </c>
@@ -34401,7 +34651,7 @@
         <v>1698</v>
       </c>
       <c r="F15" s="31"/>
-      <c r="G15" s="63"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="33">
         <v>16</v>
       </c>
@@ -34415,8 +34665,18 @@
         <v>128</v>
       </c>
       <c r="L15" s="31"/>
+      <c r="N15" s="67"/>
+      <c r="O15" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="P15" s="85"/>
+      <c r="Q15" s="85"/>
+      <c r="R15" s="85" t="s">
+        <v>61</v>
+      </c>
+      <c r="S15" s="85"/>
     </row>
-    <row r="16" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
         <v>25</v>
       </c>
@@ -34449,8 +34709,21 @@
         <v>4329</v>
       </c>
       <c r="L16" s="31"/>
+      <c r="N16" s="41">
+        <v>2000</v>
+      </c>
+      <c r="O16" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="P16" s="86"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="82" t="e">
+        <f>100 - ROUND(O16*100 /B16,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S16" s="83"/>
     </row>
-    <row r="17" spans="1:12" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
         <v>26</v>
       </c>
@@ -34483,12 +34756,31 @@
         <v>13227</v>
       </c>
       <c r="L17" s="31"/>
+      <c r="N17" s="41">
+        <v>3000</v>
+      </c>
+      <c r="O17" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="P17" s="86"/>
+      <c r="Q17" s="83"/>
+      <c r="R17" s="82" t="e">
+        <f>100 - ROUND(O17*100 /C16,2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="S17" s="83"/>
     </row>
-    <row r="18" spans="1:12" ht="17.850000000000001" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="F18" s="31"/>
       <c r="L18" s="31"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
     </row>
-    <row r="19" spans="1:12" ht="17.850000000000001" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="F19" s="31"/>
       <c r="G19" s="31"/>
       <c r="H19" s="31"/>
@@ -34496,24 +34788,48 @@
       <c r="J19" s="31"/>
       <c r="K19" s="31"/>
       <c r="L19" s="31"/>
+      <c r="N19" s="22"/>
+      <c r="O19" s="22"/>
+      <c r="P19" s="22"/>
+      <c r="Q19" s="22"/>
+      <c r="R19" s="22"/>
+      <c r="S19" s="22"/>
     </row>
-    <row r="20" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F20" s="31"/>
       <c r="L20" s="31"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="22"/>
+      <c r="P20" s="22"/>
+      <c r="Q20" s="22"/>
+      <c r="R20" s="22"/>
+      <c r="S20" s="22"/>
     </row>
-    <row r="21" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F21" s="31"/>
       <c r="L21" s="31"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
     </row>
-    <row r="22" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" s="31"/>
       <c r="L22" s="31"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
+      <c r="S22" s="22"/>
     </row>
-    <row r="23" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F23" s="31"/>
       <c r="L23" s="31"/>
     </row>
-    <row r="24" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F24" s="20"/>
       <c r="G24" s="32"/>
       <c r="H24" s="32"/>
@@ -34522,7 +34838,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="20"/>
     </row>
-    <row r="25" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F25" s="20"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
@@ -34531,7 +34847,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="20"/>
     </row>
-    <row r="26" spans="1:12" ht="17.850000000000001" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="F26" s="31"/>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
@@ -34541,7 +34857,23 @@
       <c r="L26" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="26">
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="R12:S12"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="R16:S16"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="R17:S17"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="R10:S10"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="R15:S15"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="O12:Q12"/>
     <mergeCell ref="H14:K14"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="A13:E13"/>
@@ -34566,79 +34898,92 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F84842B6-7842-488D-9BA9-218EFFDB7E51}">
   <dimension ref="A1:M38"/>
-  <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="17.850000000000001" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="21.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="1"/>
-    <col min="7" max="12" width="11.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="31" customWidth="1"/>
+    <col min="7" max="9" width="11.7109375" style="31" customWidth="1"/>
+    <col min="10" max="12" width="11.7109375" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="59" t="s">
+    <row r="1" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="70"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
     </row>
-    <row r="2" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="59"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
+    <row r="2" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="67"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="31" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="70" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="70"/>
+      <c r="F3" s="81" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="37">
+      <c r="B4" s="42">
         <v>1000</v>
       </c>
-      <c r="C4" s="37">
+      <c r="C4" s="42">
         <v>3000</v>
       </c>
-      <c r="D4" s="37">
+      <c r="D4" s="42">
         <v>7000</v>
       </c>
-      <c r="E4" s="37">
+      <c r="E4" s="42">
         <v>10000</v>
+      </c>
+      <c r="F4" s="79">
+        <f>100 - ROUND(SUM(B7:E7)/4,2)</f>
+        <v>30.090000000000003</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="72">
+      <c r="A5" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="44">
         <v>44</v>
       </c>
-      <c r="C5" s="72">
+      <c r="C5" s="44">
         <v>454</v>
       </c>
-      <c r="D5" s="72">
+      <c r="D5" s="44">
         <v>4432</v>
       </c>
-      <c r="E5" s="72">
+      <c r="E5" s="44">
         <v>12310</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
       <c r="J5" s="24"/>
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
@@ -34646,7 +34991,7 @@
     </row>
     <row r="6" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="28">
         <v>25</v>
@@ -34660,55 +35005,55 @@
       <c r="E6" s="28">
         <v>7513</v>
       </c>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
       <c r="J6" s="24"/>
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
       <c r="M6" s="24"/>
     </row>
     <row r="7" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="30">
-        <f>ROUND(100 - B5*100/B6,2)</f>
-        <v>-76</v>
-      </c>
-      <c r="C7" s="30">
-        <f t="shared" ref="C7:E7" si="0">ROUND(100 - C5*100/C6,2)</f>
-        <v>-11.27</v>
-      </c>
-      <c r="D7" s="30">
+      <c r="A7" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="78">
+        <f>ROUND(B6*100/B5,2)</f>
+        <v>56.82</v>
+      </c>
+      <c r="C7" s="78">
+        <f t="shared" ref="C7:E7" si="0">ROUND(C6*100/C5,2)</f>
+        <v>89.87</v>
+      </c>
+      <c r="D7" s="78">
         <f t="shared" si="0"/>
-        <v>-39.020000000000003</v>
-      </c>
-      <c r="E7" s="30">
+        <v>71.930000000000007</v>
+      </c>
+      <c r="E7" s="78">
         <f t="shared" si="0"/>
-        <v>-63.85</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
+        <v>61.03</v>
+      </c>
+      <c r="F7" s="79"/>
+      <c r="G7" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
       <c r="J7" s="24"/>
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
       <c r="M7" s="24"/>
     </row>
     <row r="8" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="70" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="64"/>
-      <c r="F8" s="21"/>
+      <c r="B8" s="70"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="80"/>
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
       <c r="I8" s="21"/>
@@ -34721,55 +35066,58 @@
       <c r="A9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="42">
         <v>3000</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="42">
         <v>5000</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="42">
         <v>7000</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="42">
         <v>10000</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="40"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="40"/>
-      <c r="L9" s="40"/>
+      <c r="F9" s="79">
+        <f>100 - ROUND(SUM(B12:E12)/4,2)</f>
+        <v>-8.5699999999999932</v>
+      </c>
+      <c r="G9" s="39"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="39"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="39"/>
+      <c r="L9" s="39"/>
       <c r="M9" s="24"/>
     </row>
     <row r="10" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="72">
+      <c r="A10" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="44">
         <v>169</v>
       </c>
-      <c r="C10" s="72">
+      <c r="C10" s="44">
         <v>522</v>
       </c>
-      <c r="D10" s="72">
+      <c r="D10" s="44">
         <v>1230</v>
       </c>
-      <c r="E10" s="72">
+      <c r="E10" s="44">
         <v>4092</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="38"/>
+      <c r="F10" s="79"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
       <c r="M10" s="24"/>
     </row>
     <row r="11" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="28">
         <v>188</v>
@@ -34783,58 +35131,58 @@
       <c r="E11" s="28">
         <v>4204</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="39"/>
-      <c r="K11" s="39"/>
-      <c r="L11" s="39"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="38"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="38"/>
       <c r="M11" s="24"/>
     </row>
     <row r="12" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="78">
+        <f>ROUND(B11*100/B10,2)</f>
+        <v>111.24</v>
+      </c>
+      <c r="C12" s="78">
+        <f t="shared" ref="C12:E12" si="1">ROUND(C11*100/C10,2)</f>
+        <v>107.85</v>
+      </c>
+      <c r="D12" s="78">
+        <f t="shared" si="1"/>
+        <v>112.44</v>
+      </c>
+      <c r="E12" s="78">
+        <f t="shared" si="1"/>
+        <v>102.74</v>
+      </c>
+      <c r="F12" s="79"/>
+      <c r="G12" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="79">
-        <f>ROUND(100 - B10*100/B11,2)</f>
-        <v>10.11</v>
-      </c>
-      <c r="C12" s="79">
-        <f>ROUND(100 - C10*100/C11,2)</f>
-        <v>7.28</v>
-      </c>
-      <c r="D12" s="79">
-        <f t="shared" ref="D12" si="1">ROUND(100 - D10*100/D11,2)</f>
-        <v>11.06</v>
-      </c>
-      <c r="E12" s="79">
-        <f t="shared" ref="E12" si="2">ROUND(100 - E10*100/E11,2)</f>
-        <v>2.66</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="38"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="39"/>
-      <c r="K12" s="39"/>
-      <c r="L12" s="39"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
       <c r="M12" s="24"/>
     </row>
     <row r="13" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="70" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
+      <c r="B13" s="70"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
       <c r="J13" s="24"/>
       <c r="K13" s="24"/>
       <c r="L13" s="21"/>
@@ -34844,55 +35192,58 @@
       <c r="A14" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="42">
         <v>2000</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="42">
         <v>3000</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="42">
         <v>5000</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="42">
         <v>7000</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
+      <c r="F14" s="79">
+        <f>100 - ROUND(SUM(B17:E17)/4,2)</f>
+        <v>-36.300000000000011</v>
+      </c>
+      <c r="G14" s="39"/>
+      <c r="H14" s="40"/>
+      <c r="I14" s="40"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="40"/>
       <c r="L14" s="21"/>
       <c r="M14" s="24"/>
     </row>
     <row r="15" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="72">
+      <c r="A15" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="44">
         <v>1402</v>
       </c>
-      <c r="C15" s="72">
+      <c r="C15" s="44">
         <v>4601</v>
       </c>
-      <c r="D15" s="72">
+      <c r="D15" s="44">
         <v>20947</v>
       </c>
-      <c r="E15" s="72">
+      <c r="E15" s="44">
         <v>60964</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="38"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
       <c r="L15" s="21"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B16" s="28">
         <v>2260</v>
@@ -34906,60 +35257,72 @@
       <c r="E16" s="28">
         <v>68131</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
+      <c r="F16" s="79"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
       <c r="L16" s="21"/>
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="79">
-        <f>ROUND(100 - B15*100/B16,2)</f>
-        <v>37.96</v>
-      </c>
-      <c r="C17" s="79">
-        <f t="shared" ref="C17" si="3">ROUND(100 - C15*100/C16,2)</f>
-        <v>31.03</v>
-      </c>
-      <c r="D17" s="79">
-        <f t="shared" ref="D17" si="4">ROUND(100 - D15*100/D16,2)</f>
-        <v>21.41</v>
-      </c>
-      <c r="E17" s="79">
-        <f t="shared" ref="E17" si="5">ROUND(100 - E15*100/E16,2)</f>
-        <v>10.52</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="G17" s="38"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
+      <c r="A17" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="78">
+        <f>ROUND(B16*100/B15,2)</f>
+        <v>161.19999999999999</v>
+      </c>
+      <c r="C17" s="78">
+        <f t="shared" ref="C17:E17" si="2">ROUND(C16*100/C15,2)</f>
+        <v>144.99</v>
+      </c>
+      <c r="D17" s="78">
+        <f t="shared" si="2"/>
+        <v>127.24</v>
+      </c>
+      <c r="E17" s="78">
+        <f t="shared" si="2"/>
+        <v>111.76</v>
+      </c>
+      <c r="F17" s="79"/>
+      <c r="G17" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
       <c r="L17" s="21"/>
       <c r="M17" s="24"/>
     </row>
-    <row r="18" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="F18" s="21"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
       <c r="J18" s="24"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21"/>
       <c r="M18" s="24"/>
     </row>
-    <row r="19" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="50"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -34967,43 +35330,111 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="21"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
+      <c r="A20" s="67" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="67"/>
+      <c r="C20" s="67"/>
+      <c r="D20" s="76" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="76"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
       <c r="J20" s="24"/>
       <c r="K20" s="24"/>
       <c r="L20" s="21"/>
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="31"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="76"/>
+      <c r="E21" s="76"/>
+      <c r="F21" s="76"/>
+      <c r="G21" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="21"/>
       <c r="L21" s="31"/>
     </row>
     <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F22" s="31"/>
+      <c r="A22" s="70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="81" t="s">
+        <v>56</v>
+      </c>
       <c r="L22" s="31"/>
     </row>
     <row r="23" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="31"/>
+      <c r="A23" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="42">
+        <v>1000</v>
+      </c>
+      <c r="C23" s="42">
+        <v>3000</v>
+      </c>
+      <c r="D23" s="42">
+        <v>7000</v>
+      </c>
+      <c r="E23" s="42">
+        <v>10000</v>
+      </c>
+      <c r="F23" s="79">
+        <f>100 - ROUND(SUM(B26:E26)/4,2)</f>
+        <v>33.950000000000003</v>
+      </c>
       <c r="L23" s="31"/>
     </row>
     <row r="24" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F24" s="20"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
+      <c r="A24" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="44">
+        <v>44</v>
+      </c>
+      <c r="C24" s="44">
+        <v>453</v>
+      </c>
+      <c r="D24" s="44">
+        <v>4553</v>
+      </c>
+      <c r="E24" s="44">
+        <v>11513</v>
+      </c>
+      <c r="F24" s="79"/>
       <c r="I24" s="32"/>
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
       <c r="L24" s="20"/>
     </row>
     <row r="25" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
+      <c r="A25" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="28">
+        <v>23</v>
+      </c>
+      <c r="C25" s="28">
+        <v>361</v>
+      </c>
+      <c r="D25" s="28">
+        <v>2745</v>
+      </c>
+      <c r="E25" s="28">
+        <v>8285</v>
+      </c>
+      <c r="F25" s="79"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
@@ -35011,111 +35442,261 @@
       <c r="K25" s="32"/>
       <c r="L25" s="20"/>
     </row>
-    <row r="26" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="78">
+        <f>ROUND(B25*100/B24,2)</f>
+        <v>52.27</v>
+      </c>
+      <c r="C26" s="78">
+        <f t="shared" ref="C26:E26" si="3">ROUND(C25*100/C24,2)</f>
+        <v>79.69</v>
+      </c>
+      <c r="D26" s="78">
+        <f t="shared" si="3"/>
+        <v>60.29</v>
+      </c>
+      <c r="E26" s="78">
+        <f t="shared" si="3"/>
+        <v>71.959999999999994</v>
+      </c>
+      <c r="F26" s="79"/>
+      <c r="G26" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H26" s="32"/>
       <c r="J26" s="31"/>
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
     </row>
-    <row r="27" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="A27" s="73"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="74"/>
-      <c r="D27" s="74"/>
-      <c r="E27" s="74"/>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="70" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="80"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="42">
+        <v>3000</v>
+      </c>
+      <c r="C28" s="42">
+        <v>5000</v>
+      </c>
+      <c r="D28" s="42">
+        <v>7000</v>
+      </c>
+      <c r="E28" s="42">
+        <v>10000</v>
+      </c>
+      <c r="F28" s="79">
+        <f>100 - ROUND(SUM(B31:E31)/4,2)</f>
+        <v>27.060000000000002</v>
+      </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="44">
+        <v>167</v>
+      </c>
+      <c r="C29" s="44">
+        <v>513</v>
+      </c>
+      <c r="D29" s="44">
+        <v>1319</v>
+      </c>
+      <c r="E29" s="44">
+        <v>3403</v>
+      </c>
+      <c r="F29" s="79"/>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="28">
+        <v>137</v>
+      </c>
+      <c r="C30" s="28">
+        <v>421</v>
+      </c>
+      <c r="D30" s="28">
+        <v>878</v>
+      </c>
+      <c r="E30" s="28">
+        <v>2079</v>
+      </c>
+      <c r="F30" s="79"/>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="78">
+        <f>ROUND(B30*100/B29,2)</f>
+        <v>82.04</v>
+      </c>
+      <c r="C31" s="78">
+        <f t="shared" ref="C31:E31" si="4">ROUND(C30*100/C29,2)</f>
+        <v>82.07</v>
+      </c>
+      <c r="D31" s="78">
+        <f t="shared" si="4"/>
+        <v>66.569999999999993</v>
+      </c>
+      <c r="E31" s="78">
+        <f t="shared" si="4"/>
+        <v>61.09</v>
+      </c>
+      <c r="F31" s="79"/>
+      <c r="G31" s="21" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="32" spans="1:13" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="A32" s="73"/>
-      <c r="B32" s="74"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="74"/>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="70"/>
+      <c r="F32" s="80"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="42">
+        <v>2000</v>
+      </c>
+      <c r="C33" s="42">
+        <v>3000</v>
+      </c>
+      <c r="D33" s="42">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="42">
+        <v>7000</v>
+      </c>
+      <c r="F33" s="79">
+        <f>100 - ROUND(SUM(B36:E36)/4,2)</f>
+        <v>-38.069999999999993</v>
+      </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="44">
+        <v>1402</v>
+      </c>
+      <c r="C34" s="44">
+        <v>4607</v>
+      </c>
+      <c r="D34" s="44">
+        <v>20892</v>
+      </c>
+      <c r="E34" s="44">
+        <v>57466</v>
+      </c>
+      <c r="F34" s="79"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="28">
+        <v>2248</v>
+      </c>
+      <c r="C35" s="28">
+        <v>6697</v>
+      </c>
+      <c r="D35" s="28">
+        <v>26675</v>
+      </c>
+      <c r="E35" s="28">
+        <v>68314</v>
+      </c>
+      <c r="F35" s="79"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="19"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="78">
+        <f>ROUND(B35*100/B34,2)</f>
+        <v>160.34</v>
+      </c>
+      <c r="C36" s="78">
+        <f t="shared" ref="C36:E36" si="5">ROUND(C35*100/C34,2)</f>
+        <v>145.37</v>
+      </c>
+      <c r="D36" s="78">
+        <f t="shared" si="5"/>
+        <v>127.68</v>
+      </c>
+      <c r="E36" s="78">
+        <f t="shared" si="5"/>
+        <v>118.88</v>
+      </c>
+      <c r="F36" s="79"/>
+      <c r="G36" s="31" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="19"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="45"/>
+      <c r="D37" s="45"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="50"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="45"/>
+      <c r="D38" s="45"/>
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="20">
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="B18:F19"/>
+    <mergeCell ref="B37:F38"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A32:E32"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E2"/>
+    <mergeCell ref="D1:F2"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="F9:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/DecompositionLU/docs/version_3.2_statistics.xlsx
+++ b/DecompositionLU/docs/version_3.2_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8DFC89-A5E3-4476-ADF2-AD0ABCC5EEB6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6257DEBE-03AA-477D-BDCE-221F4930C904}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Таблица" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
   <si>
     <t>Замеры версии 3.2</t>
   </si>
@@ -857,74 +857,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -950,19 +893,64 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -987,6 +975,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -30002,25 +30002,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DD6B2D-C446-466B-9C71-121C80824D6F}">
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="66.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="5" width="21.7109375" customWidth="1"/>
-    <col min="7" max="12" width="11.7109375" customWidth="1"/>
-    <col min="14" max="19" width="11.7109375" customWidth="1"/>
+    <col min="7" max="19" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="78" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="78" t="s">
+      <c r="E1" s="59" t="s">
         <v>19</v>
       </c>
     </row>
@@ -30028,21 +30027,21 @@
       <c r="A2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="79"/>
-      <c r="D2" s="79"/>
-      <c r="E2" s="79"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
     </row>
     <row r="3" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
     </row>
     <row r="4" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
@@ -30094,9 +30093,6 @@
       <c r="E6" s="30">
         <v>11709</v>
       </c>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
       <c r="Q6" s="22"/>
       <c r="R6" s="22"/>
       <c r="S6" s="22"/>
@@ -30117,31 +30113,19 @@
       <c r="E7" s="28">
         <v>12810</v>
       </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
       <c r="R7" s="22"/>
       <c r="S7" s="22"/>
     </row>
     <row r="8" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="31"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
       <c r="R8" s="22"/>
       <c r="S8" s="22"/>
@@ -30163,26 +30147,23 @@
         <v>10000</v>
       </c>
       <c r="F9" s="31"/>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="51" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="61" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="81"/>
-      <c r="J9" s="81"/>
-      <c r="K9" s="81"/>
-      <c r="L9" s="81"/>
-      <c r="N9" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="O9" s="83" t="s">
+      <c r="I9" s="62"/>
+      <c r="J9" s="62"/>
+      <c r="K9" s="62"/>
+      <c r="L9" s="62"/>
+      <c r="M9" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
     </row>
     <row r="10" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
@@ -30201,7 +30182,7 @@
         <v>9358</v>
       </c>
       <c r="F10" s="31"/>
-      <c r="G10" s="75"/>
+      <c r="G10" s="51"/>
       <c r="H10" s="33">
         <v>16</v>
       </c>
@@ -30217,16 +30198,15 @@
       <c r="L10" s="33">
         <v>256</v>
       </c>
-      <c r="N10" s="73"/>
-      <c r="O10" s="82" t="s">
+      <c r="M10" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="82" t="s">
+      <c r="N10" s="91"/>
+      <c r="O10" s="91"/>
+      <c r="P10" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="S10" s="82"/>
+      <c r="Q10" s="91"/>
     </row>
     <row r="11" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
@@ -30245,8 +30225,8 @@
         <v>3658</v>
       </c>
       <c r="F11" s="31"/>
-      <c r="G11" s="33">
-        <v>5000</v>
+      <c r="G11" s="41">
+        <v>3000</v>
       </c>
       <c r="H11" s="34">
         <v>1776</v>
@@ -30263,19 +30243,16 @@
       <c r="L11" s="34">
         <v>1520</v>
       </c>
-      <c r="N11" s="41">
-        <v>3000</v>
-      </c>
-      <c r="O11" s="84" t="s">
+      <c r="M11" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="86"/>
-      <c r="R11" s="84" t="e">
-        <f>100 - ROUND(O11*100 /B11,2)</f>
+      <c r="N11" s="93"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="92" t="e">
+        <f>100 - ROUND(M11*100 /B11,2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S11" s="86"/>
+      <c r="Q11" s="94"/>
     </row>
     <row r="12" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
@@ -30294,8 +30271,8 @@
         <v>12974</v>
       </c>
       <c r="F12" s="31"/>
-      <c r="G12" s="33">
-        <v>10000</v>
+      <c r="G12" s="41">
+        <v>5000</v>
       </c>
       <c r="H12" s="34">
         <v>10592</v>
@@ -30312,36 +30289,26 @@
       <c r="L12" s="34">
         <v>4794</v>
       </c>
-      <c r="N12" s="41">
-        <v>5000</v>
-      </c>
-      <c r="O12" s="84" t="s">
+      <c r="M12" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="86"/>
-      <c r="R12" s="84" t="e">
-        <f>100 - ROUND(O12*100 /C11,2)</f>
+      <c r="N12" s="93"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="92" t="e">
+        <f>100 - ROUND(M12*100 /C11,2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S12" s="86"/>
+      <c r="Q12" s="94"/>
     </row>
     <row r="13" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="57" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
       <c r="F13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
     </row>
     <row r="14" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
@@ -30360,26 +30327,22 @@
         <v>7000</v>
       </c>
       <c r="F14" s="31"/>
-      <c r="G14" s="74" t="s">
+      <c r="G14" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="59"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="59"/>
-      <c r="L14" s="31"/>
-      <c r="N14" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="O14" s="83" t="s">
+      <c r="I14" s="54"/>
+      <c r="J14" s="54"/>
+      <c r="K14" s="54"/>
+      <c r="L14" s="52" t="s">
         <v>54</v>
       </c>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="83"/>
-      <c r="S14" s="83"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
+      <c r="O14" s="52"/>
+      <c r="P14" s="52"/>
     </row>
     <row r="15" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
@@ -30398,7 +30361,7 @@
         <v>1698</v>
       </c>
       <c r="F15" s="31"/>
-      <c r="G15" s="75"/>
+      <c r="G15" s="56"/>
       <c r="H15" s="33">
         <v>16</v>
       </c>
@@ -30411,17 +30374,15 @@
       <c r="K15" s="33">
         <v>128</v>
       </c>
-      <c r="L15" s="31"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="82" t="s">
+      <c r="L15" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="82" t="s">
+      <c r="M15" s="91"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="91" t="s">
         <v>55</v>
       </c>
-      <c r="S15" s="82"/>
+      <c r="P15" s="91"/>
     </row>
     <row r="16" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
@@ -30455,20 +30416,16 @@
       <c r="K16" s="34">
         <v>4329</v>
       </c>
-      <c r="L16" s="31"/>
-      <c r="N16" s="41">
-        <v>2000</v>
-      </c>
-      <c r="O16" s="84" t="s">
+      <c r="L16" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="85"/>
-      <c r="Q16" s="86"/>
-      <c r="R16" s="84" t="e">
-        <f>100 - ROUND(O16*100 /B16,2)</f>
+      <c r="M16" s="93"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="92" t="e">
+        <f>100 - ROUND(L16*100 /B16,2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S16" s="86"/>
+      <c r="P16" s="94"/>
     </row>
     <row r="17" spans="1:19" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
@@ -30502,125 +30459,48 @@
       <c r="K17" s="34">
         <v>13227</v>
       </c>
-      <c r="L17" s="31"/>
-      <c r="N17" s="41">
-        <v>3000</v>
-      </c>
-      <c r="O17" s="84" t="s">
+      <c r="L17" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="P17" s="85"/>
-      <c r="Q17" s="86"/>
-      <c r="R17" s="84" t="e">
-        <f>100 - ROUND(O17*100 /C16,2)</f>
+      <c r="M17" s="93"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="92" t="e">
+        <f>100 - ROUND(L17*100 /C16,2)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="S17" s="86"/>
+      <c r="P17" s="94"/>
     </row>
     <row r="18" spans="1:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
       <c r="F18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
       <c r="R18" s="22"/>
       <c r="S18" s="22"/>
     </row>
-    <row r="19" spans="1:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="Q19" s="22"/>
       <c r="R19" s="22"/>
       <c r="S19" s="22"/>
     </row>
     <row r="20" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
       <c r="Q20" s="22"/>
       <c r="R20" s="22"/>
       <c r="S20" s="22"/>
     </row>
     <row r="21" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
       <c r="Q21" s="22"/>
       <c r="R21" s="22"/>
       <c r="S21" s="22"/>
     </row>
     <row r="22" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
       <c r="Q22" s="22"/>
       <c r="R22" s="22"/>
       <c r="S22" s="22"/>
     </row>
-    <row r="23" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F23" s="31"/>
-      <c r="L23" s="31"/>
-    </row>
-    <row r="24" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F24" s="20"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="20"/>
-    </row>
-    <row r="25" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F25" s="20"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="20"/>
-    </row>
-    <row r="26" spans="1:19" ht="17.850000000000001" x14ac:dyDescent="0.25">
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-    </row>
+    <row r="23" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="R16:S16"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="R17:S17"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="R10:S10"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="R15:S15"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="O12:Q12"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="R12:S12"/>
+  <mergeCells count="24">
     <mergeCell ref="H14:K14"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="A13:E13"/>
@@ -30629,8 +30509,22 @@
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A8:E8"/>
+    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:P17"/>
     <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:L9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="M9:Q9"/>
+    <mergeCell ref="L14:P14"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E1" location="Графики!A24" display="Соотв. графики" xr:uid="{D9DD65C5-B7A9-47BB-938E-15CD97470244}"/>
@@ -30654,30 +30548,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="60" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="61"/>
-      <c r="T1" s="62"/>
+      <c r="P1" s="64"/>
+      <c r="Q1" s="64"/>
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="65"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
@@ -30689,15 +30583,15 @@
       <c r="AC1" s="1"/>
     </row>
     <row r="2" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="65"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="69"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -30724,7 +30618,7 @@
       <c r="AC2" s="1"/>
     </row>
     <row r="3" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="55"/>
+      <c r="A3" s="66"/>
       <c r="B3" s="3" t="s">
         <v>4</v>
       </c>
@@ -30763,7 +30657,7 @@
       <c r="AC3" s="1"/>
     </row>
     <row r="4" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="55"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="4">
         <v>1</v>
       </c>
@@ -30802,7 +30696,7 @@
       <c r="AC4" s="1"/>
     </row>
     <row r="5" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="55"/>
+      <c r="A5" s="66"/>
       <c r="B5" s="4">
         <v>2</v>
       </c>
@@ -30841,7 +30735,7 @@
       <c r="AC5" s="1"/>
     </row>
     <row r="6" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="55"/>
+      <c r="A6" s="66"/>
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -30880,7 +30774,7 @@
       <c r="AC6" s="1"/>
     </row>
     <row r="7" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="55"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="4">
         <v>6</v>
       </c>
@@ -30919,7 +30813,7 @@
       <c r="AC7" s="1"/>
     </row>
     <row r="8" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="55"/>
+      <c r="A8" s="66"/>
       <c r="B8" s="4">
         <v>8</v>
       </c>
@@ -30958,7 +30852,7 @@
       <c r="AC8" s="1"/>
     </row>
     <row r="9" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="55"/>
+      <c r="A9" s="66"/>
       <c r="B9" s="4">
         <v>10</v>
       </c>
@@ -30997,7 +30891,7 @@
       <c r="AC9" s="1"/>
     </row>
     <row r="10" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="55"/>
+      <c r="A10" s="66"/>
       <c r="B10" s="4">
         <v>12</v>
       </c>
@@ -31036,7 +30930,7 @@
       <c r="AC10" s="1"/>
     </row>
     <row r="11" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
+      <c r="A11" s="66"/>
       <c r="B11" s="4">
         <v>16</v>
       </c>
@@ -31075,13 +30969,13 @@
       <c r="AC11" s="1"/>
     </row>
     <row r="12" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
-      <c r="B12" s="63" t="s">
+      <c r="A12" s="66"/>
+      <c r="B12" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="65"/>
+      <c r="C12" s="68"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="69"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -31108,7 +31002,7 @@
       <c r="AC12" s="1"/>
     </row>
     <row r="13" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
+      <c r="A13" s="66"/>
       <c r="B13" s="3" t="s">
         <v>4</v>
       </c>
@@ -31147,7 +31041,7 @@
       <c r="AC13" s="1"/>
     </row>
     <row r="14" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="55"/>
+      <c r="A14" s="66"/>
       <c r="B14" s="3">
         <v>1</v>
       </c>
@@ -31189,7 +31083,7 @@
       <c r="AC14" s="1"/>
     </row>
     <row r="15" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="55"/>
+      <c r="A15" s="66"/>
       <c r="B15" s="3">
         <v>2</v>
       </c>
@@ -31231,7 +31125,7 @@
       <c r="AC15" s="1"/>
     </row>
     <row r="16" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="55"/>
+      <c r="A16" s="66"/>
       <c r="B16" s="3">
         <v>4</v>
       </c>
@@ -31273,7 +31167,7 @@
       <c r="AC16" s="1"/>
     </row>
     <row r="17" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="55"/>
+      <c r="A17" s="66"/>
       <c r="B17" s="3">
         <v>6</v>
       </c>
@@ -31315,7 +31209,7 @@
       <c r="AC17" s="1"/>
     </row>
     <row r="18" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="55"/>
+      <c r="A18" s="66"/>
       <c r="B18" s="3">
         <v>8</v>
       </c>
@@ -31357,7 +31251,7 @@
       <c r="AC18" s="1"/>
     </row>
     <row r="19" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="55"/>
+      <c r="A19" s="66"/>
       <c r="B19" s="3">
         <v>10</v>
       </c>
@@ -31399,7 +31293,7 @@
       <c r="AC19" s="1"/>
     </row>
     <row r="20" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="55"/>
+      <c r="A20" s="66"/>
       <c r="B20" s="3">
         <v>12</v>
       </c>
@@ -31441,7 +31335,7 @@
       <c r="AC20" s="1"/>
     </row>
     <row r="21" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="55"/>
+      <c r="A21" s="66"/>
       <c r="B21" s="3">
         <v>16</v>
       </c>
@@ -31483,13 +31377,13 @@
       <c r="AC21" s="1"/>
     </row>
     <row r="22" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="55"/>
-      <c r="B22" s="63" t="s">
+      <c r="A22" s="66"/>
+      <c r="B22" s="67" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="65"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="69"/>
       <c r="F22" s="7"/>
       <c r="G22" s="8"/>
       <c r="H22" s="8"/>
@@ -31516,7 +31410,7 @@
       <c r="AC22" s="1"/>
     </row>
     <row r="23" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="55"/>
+      <c r="A23" s="66"/>
       <c r="B23" s="3" t="s">
         <v>4</v>
       </c>
@@ -31555,7 +31449,7 @@
       <c r="AC23" s="1"/>
     </row>
     <row r="24" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
+      <c r="A24" s="66"/>
       <c r="B24" s="3">
         <v>1</v>
       </c>
@@ -31597,7 +31491,7 @@
       <c r="AC24" s="1"/>
     </row>
     <row r="25" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
+      <c r="A25" s="66"/>
       <c r="B25" s="3">
         <v>2</v>
       </c>
@@ -31639,7 +31533,7 @@
       <c r="AC25" s="1"/>
     </row>
     <row r="26" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
+      <c r="A26" s="66"/>
       <c r="B26" s="3">
         <v>4</v>
       </c>
@@ -31681,7 +31575,7 @@
       <c r="AC26" s="1"/>
     </row>
     <row r="27" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
+      <c r="A27" s="66"/>
       <c r="B27" s="3">
         <v>6</v>
       </c>
@@ -31723,7 +31617,7 @@
       <c r="AC27" s="1"/>
     </row>
     <row r="28" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="55"/>
+      <c r="A28" s="66"/>
       <c r="B28" s="3">
         <v>8</v>
       </c>
@@ -31765,7 +31659,7 @@
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="55"/>
+      <c r="A29" s="66"/>
       <c r="B29" s="3">
         <v>10</v>
       </c>
@@ -31807,7 +31701,7 @@
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
+      <c r="A30" s="66"/>
       <c r="B30" s="3">
         <v>12</v>
       </c>
@@ -31849,7 +31743,7 @@
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
+      <c r="A31" s="66"/>
       <c r="B31" s="3">
         <v>16</v>
       </c>
@@ -31891,30 +31785,30 @@
       <c r="AC31" s="1"/>
     </row>
     <row r="32" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="55"/>
+      <c r="A32" s="66"/>
       <c r="B32" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="66" t="s">
+      <c r="C32" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="67"/>
-      <c r="E32" s="67"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="67"/>
-      <c r="H32" s="67"/>
-      <c r="I32" s="67"/>
-      <c r="J32" s="67"/>
-      <c r="K32" s="67"/>
-      <c r="L32" s="67"/>
-      <c r="M32" s="67"/>
-      <c r="N32" s="67"/>
-      <c r="O32" s="67"/>
-      <c r="P32" s="67"/>
-      <c r="Q32" s="67"/>
-      <c r="R32" s="67"/>
-      <c r="S32" s="67"/>
-      <c r="T32" s="68"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="71"/>
+      <c r="S32" s="71"/>
+      <c r="T32" s="72"/>
       <c r="U32" s="1"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
@@ -31926,15 +31820,15 @@
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="52" t="s">
+      <c r="A33" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="B33" s="54" t="s">
+      <c r="B33" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="C33" s="54"/>
-      <c r="D33" s="54"/>
-      <c r="E33" s="54"/>
+      <c r="C33" s="76"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="76"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -31961,7 +31855,7 @@
       <c r="AC33" s="19"/>
     </row>
     <row r="34" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="53"/>
+      <c r="A34" s="75"/>
       <c r="B34" s="3" t="s">
         <v>4</v>
       </c>
@@ -32000,7 +31894,7 @@
       <c r="AC34" s="19"/>
     </row>
     <row r="35" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="53"/>
+      <c r="A35" s="75"/>
       <c r="B35" s="4">
         <v>1</v>
       </c>
@@ -32039,7 +31933,7 @@
       <c r="AC35" s="19"/>
     </row>
     <row r="36" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="53"/>
+      <c r="A36" s="75"/>
       <c r="B36" s="4">
         <v>2</v>
       </c>
@@ -32078,7 +31972,7 @@
       <c r="AC36" s="19"/>
     </row>
     <row r="37" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="53"/>
+      <c r="A37" s="75"/>
       <c r="B37" s="4">
         <v>4</v>
       </c>
@@ -32117,7 +32011,7 @@
       <c r="AC37" s="19"/>
     </row>
     <row r="38" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="53"/>
+      <c r="A38" s="75"/>
       <c r="B38" s="4">
         <v>6</v>
       </c>
@@ -32156,7 +32050,7 @@
       <c r="AC38" s="19"/>
     </row>
     <row r="39" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="53"/>
+      <c r="A39" s="75"/>
       <c r="B39" s="4">
         <v>8</v>
       </c>
@@ -32195,7 +32089,7 @@
       <c r="AC39" s="19"/>
     </row>
     <row r="40" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="53"/>
+      <c r="A40" s="75"/>
       <c r="B40" s="4">
         <v>10</v>
       </c>
@@ -32234,7 +32128,7 @@
       <c r="AC40" s="19"/>
     </row>
     <row r="41" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="53"/>
+      <c r="A41" s="75"/>
       <c r="B41" s="4">
         <v>12</v>
       </c>
@@ -32273,7 +32167,7 @@
       <c r="AC41" s="19"/>
     </row>
     <row r="42" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="53"/>
+      <c r="A42" s="75"/>
       <c r="B42" s="4">
         <v>14</v>
       </c>
@@ -32312,7 +32206,7 @@
       <c r="AC42" s="19"/>
     </row>
     <row r="43" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="53"/>
+      <c r="A43" s="75"/>
       <c r="B43" s="4">
         <v>16</v>
       </c>
@@ -32351,7 +32245,7 @@
       <c r="AC43" s="19"/>
     </row>
     <row r="44" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="53"/>
+      <c r="A44" s="75"/>
       <c r="B44" s="4">
         <v>18</v>
       </c>
@@ -32390,7 +32284,7 @@
       <c r="AC44" s="19"/>
     </row>
     <row r="45" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="53"/>
+      <c r="A45" s="75"/>
       <c r="B45" s="4">
         <v>20</v>
       </c>
@@ -32429,7 +32323,7 @@
       <c r="AC45" s="19"/>
     </row>
     <row r="46" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="53"/>
+      <c r="A46" s="75"/>
       <c r="B46" s="10">
         <v>40</v>
       </c>
@@ -32468,13 +32362,13 @@
       <c r="AC46" s="19"/>
     </row>
     <row r="47" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="53"/>
-      <c r="B47" s="54" t="s">
+      <c r="A47" s="75"/>
+      <c r="B47" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="54"/>
-      <c r="D47" s="54"/>
-      <c r="E47" s="54"/>
+      <c r="C47" s="76"/>
+      <c r="D47" s="76"/>
+      <c r="E47" s="76"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -32501,7 +32395,7 @@
       <c r="AC47" s="19"/>
     </row>
     <row r="48" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="53"/>
+      <c r="A48" s="75"/>
       <c r="B48" s="3" t="s">
         <v>4</v>
       </c>
@@ -32540,7 +32434,7 @@
       <c r="AC48" s="20"/>
     </row>
     <row r="49" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="53"/>
+      <c r="A49" s="75"/>
       <c r="B49" s="4">
         <v>1</v>
       </c>
@@ -32582,7 +32476,7 @@
       <c r="AC49" s="20"/>
     </row>
     <row r="50" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="53"/>
+      <c r="A50" s="75"/>
       <c r="B50" s="4">
         <v>2</v>
       </c>
@@ -32624,7 +32518,7 @@
       <c r="AC50" s="20"/>
     </row>
     <row r="51" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="53"/>
+      <c r="A51" s="75"/>
       <c r="B51" s="4">
         <v>4</v>
       </c>
@@ -32666,7 +32560,7 @@
       <c r="AC51" s="20"/>
     </row>
     <row r="52" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="53"/>
+      <c r="A52" s="75"/>
       <c r="B52" s="4">
         <v>6</v>
       </c>
@@ -32708,7 +32602,7 @@
       <c r="AC52" s="20"/>
     </row>
     <row r="53" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="53"/>
+      <c r="A53" s="75"/>
       <c r="B53" s="13">
         <v>8</v>
       </c>
@@ -32750,7 +32644,7 @@
       <c r="AC53" s="20"/>
     </row>
     <row r="54" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="53"/>
+      <c r="A54" s="75"/>
       <c r="B54" s="4">
         <v>10</v>
       </c>
@@ -32792,7 +32686,7 @@
       <c r="AC54" s="20"/>
     </row>
     <row r="55" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="53"/>
+      <c r="A55" s="75"/>
       <c r="B55" s="4">
         <v>12</v>
       </c>
@@ -32834,7 +32728,7 @@
       <c r="AC55" s="20"/>
     </row>
     <row r="56" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="53"/>
+      <c r="A56" s="75"/>
       <c r="B56" s="4">
         <v>14</v>
       </c>
@@ -32876,7 +32770,7 @@
       <c r="AC56" s="20"/>
     </row>
     <row r="57" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="53"/>
+      <c r="A57" s="75"/>
       <c r="B57" s="4">
         <v>16</v>
       </c>
@@ -32918,7 +32812,7 @@
       <c r="AC57" s="19"/>
     </row>
     <row r="58" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="53"/>
+      <c r="A58" s="75"/>
       <c r="B58" s="4">
         <v>18</v>
       </c>
@@ -32960,7 +32854,7 @@
       <c r="AC58" s="20"/>
     </row>
     <row r="59" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="53"/>
+      <c r="A59" s="75"/>
       <c r="B59" s="4">
         <v>20</v>
       </c>
@@ -33002,7 +32896,7 @@
       <c r="AC59" s="20"/>
     </row>
     <row r="60" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="53"/>
+      <c r="A60" s="75"/>
       <c r="B60" s="10">
         <v>40</v>
       </c>
@@ -33044,13 +32938,13 @@
       <c r="AC60" s="20"/>
     </row>
     <row r="61" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="53"/>
-      <c r="B61" s="54" t="s">
+      <c r="A61" s="75"/>
+      <c r="B61" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C61" s="54"/>
-      <c r="D61" s="54"/>
-      <c r="E61" s="54"/>
+      <c r="C61" s="76"/>
+      <c r="D61" s="76"/>
+      <c r="E61" s="76"/>
       <c r="F61" s="8"/>
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
@@ -33077,7 +32971,7 @@
       <c r="AC61" s="20"/>
     </row>
     <row r="62" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="53"/>
+      <c r="A62" s="75"/>
       <c r="B62" s="3" t="s">
         <v>4</v>
       </c>
@@ -33116,7 +33010,7 @@
       <c r="AC62" s="20"/>
     </row>
     <row r="63" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="53"/>
+      <c r="A63" s="75"/>
       <c r="B63" s="4">
         <v>1</v>
       </c>
@@ -33158,7 +33052,7 @@
       <c r="AC63" s="20"/>
     </row>
     <row r="64" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="53"/>
+      <c r="A64" s="75"/>
       <c r="B64" s="4">
         <v>2</v>
       </c>
@@ -33200,7 +33094,7 @@
       <c r="AC64" s="20"/>
     </row>
     <row r="65" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="53"/>
+      <c r="A65" s="75"/>
       <c r="B65" s="4">
         <v>4</v>
       </c>
@@ -33242,7 +33136,7 @@
       <c r="AC65" s="20"/>
     </row>
     <row r="66" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="53"/>
+      <c r="A66" s="75"/>
       <c r="B66" s="4">
         <v>6</v>
       </c>
@@ -33284,7 +33178,7 @@
       <c r="AC66" s="20"/>
     </row>
     <row r="67" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="53"/>
+      <c r="A67" s="75"/>
       <c r="B67" s="15">
         <v>8</v>
       </c>
@@ -33326,7 +33220,7 @@
       <c r="AC67" s="20"/>
     </row>
     <row r="68" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="53"/>
+      <c r="A68" s="75"/>
       <c r="B68" s="4">
         <v>10</v>
       </c>
@@ -33368,7 +33262,7 @@
       <c r="AC68" s="20"/>
     </row>
     <row r="69" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="53"/>
+      <c r="A69" s="75"/>
       <c r="B69" s="4">
         <v>12</v>
       </c>
@@ -33410,7 +33304,7 @@
       <c r="AC69" s="19"/>
     </row>
     <row r="70" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="53"/>
+      <c r="A70" s="75"/>
       <c r="B70" s="4">
         <v>14</v>
       </c>
@@ -33452,7 +33346,7 @@
       <c r="AC70" s="19"/>
     </row>
     <row r="71" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="53"/>
+      <c r="A71" s="75"/>
       <c r="B71" s="4">
         <v>16</v>
       </c>
@@ -33494,7 +33388,7 @@
       <c r="AC71" s="20"/>
     </row>
     <row r="72" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="53"/>
+      <c r="A72" s="75"/>
       <c r="B72" s="4">
         <v>18</v>
       </c>
@@ -33537,7 +33431,7 @@
       <c r="AD72" s="22"/>
     </row>
     <row r="73" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="53"/>
+      <c r="A73" s="75"/>
       <c r="B73" s="4">
         <v>20</v>
       </c>
@@ -33580,7 +33474,7 @@
       <c r="AD73" s="22"/>
     </row>
     <row r="74" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="53"/>
+      <c r="A74" s="75"/>
       <c r="B74" s="10">
         <v>40</v>
       </c>
@@ -33623,51 +33517,51 @@
       <c r="AD74" s="22"/>
     </row>
     <row r="75" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="53"/>
+      <c r="A75" s="75"/>
       <c r="B75" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="57" t="s">
+      <c r="C75" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="D75" s="57"/>
-      <c r="E75" s="57"/>
-      <c r="F75" s="57"/>
-      <c r="G75" s="57"/>
-      <c r="H75" s="57"/>
-      <c r="I75" s="57"/>
-      <c r="J75" s="57"/>
-      <c r="K75" s="57"/>
-      <c r="L75" s="57"/>
-      <c r="M75" s="57"/>
-      <c r="N75" s="57"/>
-      <c r="O75" s="57"/>
-      <c r="P75" s="57"/>
-      <c r="Q75" s="57"/>
-      <c r="R75" s="57"/>
-      <c r="S75" s="57"/>
-      <c r="T75" s="57"/>
-      <c r="U75" s="57"/>
-      <c r="V75" s="57"/>
-      <c r="W75" s="57"/>
-      <c r="X75" s="57"/>
-      <c r="Y75" s="57"/>
-      <c r="Z75" s="57"/>
-      <c r="AA75" s="57"/>
+      <c r="D75" s="78"/>
+      <c r="E75" s="78"/>
+      <c r="F75" s="78"/>
+      <c r="G75" s="78"/>
+      <c r="H75" s="78"/>
+      <c r="I75" s="78"/>
+      <c r="J75" s="78"/>
+      <c r="K75" s="78"/>
+      <c r="L75" s="78"/>
+      <c r="M75" s="78"/>
+      <c r="N75" s="78"/>
+      <c r="O75" s="78"/>
+      <c r="P75" s="78"/>
+      <c r="Q75" s="78"/>
+      <c r="R75" s="78"/>
+      <c r="S75" s="78"/>
+      <c r="T75" s="78"/>
+      <c r="U75" s="78"/>
+      <c r="V75" s="78"/>
+      <c r="W75" s="78"/>
+      <c r="X75" s="78"/>
+      <c r="Y75" s="78"/>
+      <c r="Z75" s="78"/>
+      <c r="AA75" s="78"/>
       <c r="AB75" s="23"/>
       <c r="AC75" s="23"/>
       <c r="AD75" s="22"/>
     </row>
     <row r="76" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="55" t="s">
+      <c r="A76" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B76" s="54" t="s">
+      <c r="B76" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="C76" s="54"/>
-      <c r="D76" s="54"/>
-      <c r="E76" s="54"/>
+      <c r="C76" s="76"/>
+      <c r="D76" s="76"/>
+      <c r="E76" s="76"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -33695,7 +33589,7 @@
       <c r="AD76" s="22"/>
     </row>
     <row r="77" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="55"/>
+      <c r="A77" s="66"/>
       <c r="B77" s="3" t="s">
         <v>4</v>
       </c>
@@ -33735,7 +33629,7 @@
       <c r="AD77" s="22"/>
     </row>
     <row r="78" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="55"/>
+      <c r="A78" s="66"/>
       <c r="B78" s="4">
         <v>1</v>
       </c>
@@ -33775,7 +33669,7 @@
       <c r="AD78" s="22"/>
     </row>
     <row r="79" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="55"/>
+      <c r="A79" s="66"/>
       <c r="B79" s="4">
         <v>2</v>
       </c>
@@ -33814,7 +33708,7 @@
       <c r="AC79" s="1"/>
     </row>
     <row r="80" spans="1:30" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="55"/>
+      <c r="A80" s="66"/>
       <c r="B80" s="4">
         <v>4</v>
       </c>
@@ -33853,7 +33747,7 @@
       <c r="AC80" s="1"/>
     </row>
     <row r="81" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="55"/>
+      <c r="A81" s="66"/>
       <c r="B81" s="4">
         <v>6</v>
       </c>
@@ -33892,7 +33786,7 @@
       <c r="AC81" s="1"/>
     </row>
     <row r="82" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="55"/>
+      <c r="A82" s="66"/>
       <c r="B82" s="4">
         <v>8</v>
       </c>
@@ -33931,13 +33825,13 @@
       <c r="AC82" s="1"/>
     </row>
     <row r="83" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="55"/>
-      <c r="B83" s="54" t="s">
+      <c r="A83" s="66"/>
+      <c r="B83" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C83" s="54"/>
-      <c r="D83" s="54"/>
-      <c r="E83" s="54"/>
+      <c r="C83" s="76"/>
+      <c r="D83" s="76"/>
+      <c r="E83" s="76"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -33964,7 +33858,7 @@
       <c r="AC83" s="1"/>
     </row>
     <row r="84" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="55"/>
+      <c r="A84" s="66"/>
       <c r="B84" s="3" t="s">
         <v>4</v>
       </c>
@@ -34003,7 +33897,7 @@
       <c r="AC84" s="1"/>
     </row>
     <row r="85" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="55"/>
+      <c r="A85" s="66"/>
       <c r="B85" s="3">
         <v>1</v>
       </c>
@@ -34045,7 +33939,7 @@
       <c r="AC85" s="1"/>
     </row>
     <row r="86" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="55"/>
+      <c r="A86" s="66"/>
       <c r="B86" s="3">
         <v>2</v>
       </c>
@@ -34087,7 +33981,7 @@
       <c r="AC86" s="1"/>
     </row>
     <row r="87" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="55"/>
+      <c r="A87" s="66"/>
       <c r="B87" s="3">
         <v>4</v>
       </c>
@@ -34129,7 +34023,7 @@
       <c r="AC87" s="1"/>
     </row>
     <row r="88" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="55"/>
+      <c r="A88" s="66"/>
       <c r="B88" s="3">
         <v>6</v>
       </c>
@@ -34171,7 +34065,7 @@
       <c r="AC88" s="1"/>
     </row>
     <row r="89" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="55"/>
+      <c r="A89" s="66"/>
       <c r="B89" s="17">
         <v>8</v>
       </c>
@@ -34213,13 +34107,13 @@
       <c r="AC89" s="1"/>
     </row>
     <row r="90" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="55"/>
-      <c r="B90" s="54" t="s">
+      <c r="A90" s="66"/>
+      <c r="B90" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="54"/>
-      <c r="D90" s="54"/>
-      <c r="E90" s="54"/>
+      <c r="C90" s="76"/>
+      <c r="D90" s="76"/>
+      <c r="E90" s="76"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="8"/>
@@ -34246,7 +34140,7 @@
       <c r="AC90" s="1"/>
     </row>
     <row r="91" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="55"/>
+      <c r="A91" s="66"/>
       <c r="B91" s="3" t="s">
         <v>4</v>
       </c>
@@ -34285,7 +34179,7 @@
       <c r="AC91" s="1"/>
     </row>
     <row r="92" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="55"/>
+      <c r="A92" s="66"/>
       <c r="B92" s="3">
         <v>1</v>
       </c>
@@ -34327,7 +34221,7 @@
       <c r="AC92" s="1"/>
     </row>
     <row r="93" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="55"/>
+      <c r="A93" s="66"/>
       <c r="B93" s="3">
         <v>2</v>
       </c>
@@ -34369,7 +34263,7 @@
       <c r="AC93" s="1"/>
     </row>
     <row r="94" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="55"/>
+      <c r="A94" s="66"/>
       <c r="B94" s="3">
         <v>4</v>
       </c>
@@ -34411,7 +34305,7 @@
       <c r="AC94" s="1"/>
     </row>
     <row r="95" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="55"/>
+      <c r="A95" s="66"/>
       <c r="B95" s="3">
         <v>6</v>
       </c>
@@ -34453,7 +34347,7 @@
       <c r="AC95" s="1"/>
     </row>
     <row r="96" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="55"/>
+      <c r="A96" s="66"/>
       <c r="B96" s="18">
         <v>8</v>
       </c>
@@ -34495,13 +34389,13 @@
       <c r="AC96" s="1"/>
     </row>
     <row r="97" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="55"/>
-      <c r="B97" s="56" t="s">
+      <c r="A97" s="66"/>
+      <c r="B97" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="C97" s="56"/>
-      <c r="D97" s="56"/>
-      <c r="E97" s="56"/>
+      <c r="C97" s="77"/>
+      <c r="D97" s="77"/>
+      <c r="E97" s="77"/>
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="8"/>
@@ -34528,13 +34422,13 @@
       <c r="AC97" s="1"/>
     </row>
     <row r="98" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="55"/>
-      <c r="B98" s="51" t="s">
+      <c r="A98" s="66"/>
+      <c r="B98" s="73" t="s">
         <v>30</v>
       </c>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
+      <c r="C98" s="73"/>
+      <c r="D98" s="73"/>
+      <c r="E98" s="73"/>
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="8"/>
@@ -34561,11 +34455,11 @@
       <c r="AC98" s="1"/>
     </row>
     <row r="99" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="55"/>
-      <c r="B99" s="51"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
+      <c r="A99" s="66"/>
+      <c r="B99" s="73"/>
+      <c r="C99" s="73"/>
+      <c r="D99" s="73"/>
+      <c r="E99" s="73"/>
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="8"/>
@@ -34592,11 +34486,11 @@
       <c r="AC99" s="1"/>
     </row>
     <row r="100" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="55"/>
-      <c r="B100" s="51"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
+      <c r="A100" s="66"/>
+      <c r="B100" s="73"/>
+      <c r="C100" s="73"/>
+      <c r="D100" s="73"/>
+      <c r="E100" s="73"/>
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="8"/>
@@ -34623,11 +34517,11 @@
       <c r="AC100" s="1"/>
     </row>
     <row r="101" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="55"/>
-      <c r="B101" s="51"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
+      <c r="A101" s="66"/>
+      <c r="B101" s="73"/>
+      <c r="C101" s="73"/>
+      <c r="D101" s="73"/>
+      <c r="E101" s="73"/>
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="8"/>
@@ -34654,11 +34548,11 @@
       <c r="AC101" s="1"/>
     </row>
     <row r="102" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="55"/>
-      <c r="B102" s="51"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
+      <c r="A102" s="66"/>
+      <c r="B102" s="73"/>
+      <c r="C102" s="73"/>
+      <c r="D102" s="73"/>
+      <c r="E102" s="73"/>
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="8"/>
@@ -34685,11 +34579,11 @@
       <c r="AC102" s="1"/>
     </row>
     <row r="103" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="55"/>
-      <c r="B103" s="51"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
+      <c r="A103" s="66"/>
+      <c r="B103" s="73"/>
+      <c r="C103" s="73"/>
+      <c r="D103" s="73"/>
+      <c r="E103" s="73"/>
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="8"/>
@@ -34716,11 +34610,11 @@
       <c r="AC103" s="1"/>
     </row>
     <row r="104" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="55"/>
-      <c r="B104" s="51"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
+      <c r="A104" s="66"/>
+      <c r="B104" s="73"/>
+      <c r="C104" s="73"/>
+      <c r="D104" s="73"/>
+      <c r="E104" s="73"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -34747,11 +34641,11 @@
       <c r="AC104" s="1"/>
     </row>
     <row r="105" spans="1:29" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="55"/>
-      <c r="B105" s="51"/>
-      <c r="C105" s="51"/>
-      <c r="D105" s="51"/>
-      <c r="E105" s="51"/>
+      <c r="A105" s="66"/>
+      <c r="B105" s="73"/>
+      <c r="C105" s="73"/>
+      <c r="D105" s="73"/>
+      <c r="E105" s="73"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -34779,13 +34673,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:T1"/>
-    <mergeCell ref="A2:A32"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="C32:T32"/>
     <mergeCell ref="B98:E105"/>
     <mergeCell ref="A33:A75"/>
     <mergeCell ref="B33:E33"/>
@@ -34797,6 +34684,13 @@
     <mergeCell ref="B90:E90"/>
     <mergeCell ref="B97:E97"/>
     <mergeCell ref="C75:AA75"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="O1:T1"/>
+    <mergeCell ref="A2:A32"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C32:T32"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="O1" location="Таблица!A44" display="Соотв. таблица" xr:uid="{83FF44B0-CA98-46DE-9446-E04E222E13B0}"/>
@@ -34821,60 +34715,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="51" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="80" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="80" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
+      <c r="A3" s="79"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="69">
+      <c r="A4" s="81">
         <v>3000</v>
       </c>
-      <c r="B4" s="69">
+      <c r="B4" s="81">
         <v>4613</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
     </row>
     <row r="5" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="69"/>
-      <c r="B5" s="69"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="34">
         <v>16.673999999999999</v>
       </c>
@@ -34889,18 +34783,18 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="70" t="s">
+      <c r="A6" s="81"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="70"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70"/>
+      <c r="D6" s="80"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
     </row>
     <row r="7" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="69"/>
-      <c r="B7" s="69"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="81"/>
       <c r="C7" s="34">
         <f>ROUND(C5/$B4*100,2)</f>
         <v>0.36</v>
@@ -34919,22 +34813,22 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="69">
+      <c r="A8" s="81">
         <v>5000</v>
       </c>
-      <c r="B8" s="69">
+      <c r="B8" s="81">
         <v>21014</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="D8" s="82"/>
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="69"/>
-      <c r="B9" s="69"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="34">
         <v>25.027000000000001</v>
       </c>
@@ -34949,18 +34843,18 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="69"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="70" t="s">
+      <c r="A10" s="81"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-      <c r="F10" s="70"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
     </row>
     <row r="11" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="69"/>
-      <c r="B11" s="69"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="81"/>
       <c r="C11" s="34">
         <f>ROUND(C9/$B8*100,2)</f>
         <v>0.12</v>
@@ -34979,22 +34873,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="69">
+      <c r="A12" s="81">
         <v>7000</v>
       </c>
-      <c r="B12" s="69">
+      <c r="B12" s="81">
         <v>57613</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
     </row>
     <row r="13" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="69"/>
-      <c r="B13" s="69"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="34">
         <v>90.486000000000004</v>
       </c>
@@ -35009,18 +34903,18 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="70" t="s">
+      <c r="A14" s="81"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
     </row>
     <row r="15" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="34">
         <f>ROUND(C13/$B12*100,2)</f>
         <v>0.16</v>
@@ -35098,6 +34992,14 @@
     <row r="45" ht="17.3" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="B2:B3"/>
@@ -35109,14 +35011,6 @@
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -35137,36 +35031,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="88" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="84" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
     </row>
     <row r="2" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="73"/>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
+      <c r="A2" s="51"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="84"/>
+      <c r="E2" s="84"/>
+      <c r="F2" s="84"/>
       <c r="G2" s="31" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="76" t="s">
+      <c r="A3" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="76"/>
-      <c r="C3" s="76"/>
-      <c r="D3" s="76"/>
-      <c r="E3" s="76"/>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
       <c r="F3" s="48" t="s">
         <v>50</v>
       </c>
@@ -35187,7 +35081,7 @@
       <c r="E4" s="44">
         <v>10000</v>
       </c>
-      <c r="F4" s="87">
+      <c r="F4" s="83">
         <f>ROUND(SUM(B7:E7)/4,2)</f>
         <v>69.91</v>
       </c>
@@ -35208,7 +35102,7 @@
       <c r="E5" s="43">
         <v>12310</v>
       </c>
-      <c r="F5" s="87"/>
+      <c r="F5" s="83"/>
       <c r="G5" s="21"/>
       <c r="H5" s="21"/>
       <c r="I5" s="21"/>
@@ -35233,7 +35127,7 @@
       <c r="E6" s="28">
         <v>7513</v>
       </c>
-      <c r="F6" s="87"/>
+      <c r="F6" s="83"/>
       <c r="G6" s="21"/>
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
@@ -35262,7 +35156,7 @@
         <f t="shared" si="0"/>
         <v>61.03</v>
       </c>
-      <c r="F7" s="87"/>
+      <c r="F7" s="83"/>
       <c r="G7" s="21" t="s">
         <v>44</v>
       </c>
@@ -35274,13 +35168,13 @@
       <c r="M7" s="24"/>
     </row>
     <row r="8" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="76"/>
+      <c r="B8" s="57"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
       <c r="F8" s="47"/>
       <c r="G8" s="21"/>
       <c r="H8" s="21"/>
@@ -35306,7 +35200,7 @@
       <c r="E9" s="44">
         <v>10000</v>
       </c>
-      <c r="F9" s="87">
+      <c r="F9" s="83">
         <f xml:space="preserve"> ROUND(SUM(B12:E12)/4,2)</f>
         <v>108.57</v>
       </c>
@@ -35334,7 +35228,7 @@
       <c r="E10" s="43">
         <v>4092</v>
       </c>
-      <c r="F10" s="87"/>
+      <c r="F10" s="83"/>
       <c r="G10" s="39"/>
       <c r="H10" s="37"/>
       <c r="I10" s="37"/>
@@ -35359,7 +35253,7 @@
       <c r="E11" s="28">
         <v>4204</v>
       </c>
-      <c r="F11" s="87"/>
+      <c r="F11" s="83"/>
       <c r="G11" s="37"/>
       <c r="H11" s="38"/>
       <c r="I11" s="38"/>
@@ -35388,7 +35282,7 @@
         <f t="shared" si="1"/>
         <v>102.74</v>
       </c>
-      <c r="F12" s="87"/>
+      <c r="F12" s="83"/>
       <c r="G12" s="21" t="s">
         <v>42</v>
       </c>
@@ -35400,13 +35294,13 @@
       <c r="M12" s="24"/>
     </row>
     <row r="13" spans="1:13" ht="17.3" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="76" t="s">
+      <c r="A13" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="76"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="76"/>
-      <c r="E13" s="76"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
       <c r="F13" s="47"/>
       <c r="G13" s="21"/>
       <c r="H13" s="21"/>
@@ -35432,7 +35326,7 @@
       <c r="E14" s="44">
         <v>7000</v>
       </c>
-      <c r="F14" s="87">
+      <c r="F14" s="83">
         <f>ROUND(SUM(B17:E17)/4,2)</f>
         <v>136.30000000000001</v>
       </c>
@@ -35460,7 +35354,7 @@
       <c r="E15" s="43">
         <v>60964</v>
       </c>
-      <c r="F15" s="87"/>
+      <c r="F15" s="83"/>
       <c r="G15" s="39"/>
       <c r="H15" s="37"/>
       <c r="I15" s="37"/>
@@ -35485,7 +35379,7 @@
       <c r="E16" s="28">
         <v>68131</v>
       </c>
-      <c r="F16" s="87"/>
+      <c r="F16" s="83"/>
       <c r="G16" s="37"/>
       <c r="H16" s="38"/>
       <c r="I16" s="38"/>
@@ -35514,7 +35408,7 @@
         <f t="shared" si="2"/>
         <v>111.76</v>
       </c>
-      <c r="F17" s="87"/>
+      <c r="F17" s="83"/>
       <c r="G17" s="21" t="s">
         <v>43</v>
       </c>
@@ -35526,16 +35420,16 @@
       <c r="M17" s="24"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
       <c r="G18" s="21"/>
       <c r="H18" s="21"/>
       <c r="I18" s="21"/>
@@ -35545,12 +35439,12 @@
       <c r="M18" s="24"/>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="56"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="73"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
       <c r="K19" s="21"/>
@@ -35558,14 +35452,14 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="73"/>
-      <c r="C20" s="73"/>
-      <c r="D20" s="73"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
       <c r="G20" s="21"/>
       <c r="H20" s="21"/>
       <c r="I20" s="21"/>
@@ -35575,12 +35469,12 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="73"/>
-      <c r="B21" s="73"/>
-      <c r="C21" s="73"/>
-      <c r="D21" s="73"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
+      <c r="A21" s="51"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
       <c r="G21" s="31" t="s">
         <v>46</v>
       </c>
@@ -35588,13 +35482,13 @@
       <c r="L21" s="31"/>
     </row>
     <row r="22" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="76" t="s">
+      <c r="A22" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
       <c r="F22" s="48" t="s">
         <v>50</v>
       </c>
@@ -35616,7 +35510,7 @@
       <c r="E23" s="44">
         <v>10000</v>
       </c>
-      <c r="F23" s="87">
+      <c r="F23" s="83">
         <f>ROUND(SUM(B26:E26)/4,2)</f>
         <v>66.05</v>
       </c>
@@ -35638,7 +35532,7 @@
       <c r="E24" s="43">
         <v>11513</v>
       </c>
-      <c r="F24" s="87"/>
+      <c r="F24" s="83"/>
       <c r="I24" s="32"/>
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
@@ -35660,7 +35554,7 @@
       <c r="E25" s="28">
         <v>8285</v>
       </c>
-      <c r="F25" s="87"/>
+      <c r="F25" s="83"/>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
@@ -35688,7 +35582,7 @@
         <f t="shared" si="3"/>
         <v>71.959999999999994</v>
       </c>
-      <c r="F26" s="87"/>
+      <c r="F26" s="83"/>
       <c r="G26" s="20" t="s">
         <v>47</v>
       </c>
@@ -35698,13 +35592,13 @@
       <c r="L26" s="31"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="76" t="s">
+      <c r="A27" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
       <c r="F27" s="47"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -35723,7 +35617,7 @@
       <c r="E28" s="44">
         <v>10000</v>
       </c>
-      <c r="F28" s="87">
+      <c r="F28" s="83">
         <f>ROUND(SUM(B31:E31)/4,2)</f>
         <v>72.94</v>
       </c>
@@ -35744,7 +35638,7 @@
       <c r="E29" s="43">
         <v>3403</v>
       </c>
-      <c r="F29" s="87"/>
+      <c r="F29" s="83"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
@@ -35762,7 +35656,7 @@
       <c r="E30" s="28">
         <v>2079</v>
       </c>
-      <c r="F30" s="87"/>
+      <c r="F30" s="83"/>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="45" t="s">
@@ -35784,19 +35678,19 @@
         <f t="shared" si="4"/>
         <v>61.09</v>
       </c>
-      <c r="F31" s="87"/>
+      <c r="F31" s="83"/>
       <c r="G31" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="76"/>
-      <c r="C32" s="76"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="76"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
       <c r="F32" s="47"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -35815,7 +35709,7 @@
       <c r="E33" s="44">
         <v>7000</v>
       </c>
-      <c r="F33" s="87">
+      <c r="F33" s="83">
         <f>ROUND(SUM(B36:E36)/4,2)</f>
         <v>138.07</v>
       </c>
@@ -35836,7 +35730,7 @@
       <c r="E34" s="43">
         <v>57466</v>
       </c>
-      <c r="F34" s="87"/>
+      <c r="F34" s="83"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
@@ -35854,7 +35748,7 @@
       <c r="E35" s="28">
         <v>68314</v>
       </c>
-      <c r="F35" s="87"/>
+      <c r="F35" s="83"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="45" t="s">
@@ -35876,67 +35770,67 @@
         <f t="shared" si="5"/>
         <v>118.88</v>
       </c>
-      <c r="F36" s="87"/>
+      <c r="F36" s="83"/>
       <c r="G36" s="31" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="51" t="s">
+      <c r="B37" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
+      <c r="C37" s="73"/>
+      <c r="D37" s="73"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="56"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51"/>
-      <c r="E38" s="51"/>
-      <c r="F38" s="51"/>
+      <c r="A38" s="77"/>
+      <c r="B38" s="73"/>
+      <c r="C38" s="73"/>
+      <c r="D38" s="73"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
     </row>
     <row r="39" spans="1:7" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="73" t="s">
+      <c r="A39" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="B39" s="73"/>
-      <c r="C39" s="73"/>
-      <c r="D39" s="88" t="s">
+      <c r="B39" s="51"/>
+      <c r="C39" s="51"/>
+      <c r="D39" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="88"/>
-      <c r="F39" s="88"/>
+      <c r="E39" s="84"/>
+      <c r="F39" s="84"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="73"/>
-      <c r="B40" s="73"/>
-      <c r="C40" s="73"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="88"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="51"/>
+      <c r="D40" s="84"/>
+      <c r="E40" s="84"/>
+      <c r="F40" s="84"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="73"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="73"/>
-      <c r="D41" s="88"/>
-      <c r="E41" s="88"/>
-      <c r="F41" s="88"/>
+      <c r="A41" s="51"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="76" t="s">
+      <c r="A42" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
       <c r="F42" s="48" t="s">
         <v>50</v>
       </c>
@@ -35957,7 +35851,7 @@
       <c r="E43" s="44">
         <v>10000</v>
       </c>
-      <c r="F43" s="87">
+      <c r="F43" s="83">
         <f>ROUND(SUM(B46:E46)/4,2)</f>
         <v>35.549999999999997</v>
       </c>
@@ -35978,7 +35872,7 @@
       <c r="E44" s="43">
         <v>11814</v>
       </c>
-      <c r="F44" s="87"/>
+      <c r="F44" s="83"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
@@ -35996,7 +35890,7 @@
       <c r="E45" s="28">
         <v>5295</v>
       </c>
-      <c r="F45" s="87"/>
+      <c r="F45" s="83"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="45" t="s">
@@ -36018,16 +35912,16 @@
         <f t="shared" si="6"/>
         <v>44.82</v>
       </c>
-      <c r="F46" s="87"/>
+      <c r="F46" s="83"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="76" t="s">
+      <c r="A47" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="B47" s="76"/>
-      <c r="C47" s="76"/>
-      <c r="D47" s="76"/>
-      <c r="E47" s="76"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
       <c r="F47" s="47"/>
       <c r="G47" s="31" t="s">
         <v>61</v>
@@ -36049,7 +35943,7 @@
       <c r="E48" s="44">
         <v>10000</v>
       </c>
-      <c r="F48" s="87">
+      <c r="F48" s="83">
         <f>ROUND(SUM(B51:E51)/4,2)</f>
         <v>39.020000000000003</v>
       </c>
@@ -36070,7 +35964,7 @@
       <c r="E49" s="43">
         <v>3802</v>
       </c>
-      <c r="F49" s="87"/>
+      <c r="F49" s="83"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
@@ -36088,7 +35982,7 @@
       <c r="E50" s="28">
         <v>1333</v>
       </c>
-      <c r="F50" s="87"/>
+      <c r="F50" s="83"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="45" t="s">
@@ -36110,63 +36004,75 @@
         <f t="shared" si="7"/>
         <v>35.06</v>
       </c>
-      <c r="F51" s="87"/>
+      <c r="F51" s="83"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="76" t="s">
+      <c r="A52" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B52" s="76"/>
-      <c r="C52" s="76"/>
-      <c r="D52" s="76"/>
-      <c r="E52" s="76"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
       <c r="F52" s="47"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="89" t="s">
+      <c r="A53" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="B53" s="90"/>
-      <c r="C53" s="90"/>
-      <c r="D53" s="90"/>
-      <c r="E53" s="90"/>
-      <c r="F53" s="91"/>
+      <c r="B53" s="86"/>
+      <c r="C53" s="86"/>
+      <c r="D53" s="86"/>
+      <c r="E53" s="86"/>
+      <c r="F53" s="87"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="92"/>
-      <c r="B54" s="93"/>
-      <c r="C54" s="93"/>
-      <c r="D54" s="93"/>
-      <c r="E54" s="93"/>
-      <c r="F54" s="94"/>
+      <c r="A54" s="88"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="89"/>
+      <c r="D54" s="89"/>
+      <c r="E54" s="89"/>
+      <c r="F54" s="90"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="56" t="s">
+      <c r="A55" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B55" s="51" t="s">
+      <c r="B55" s="73" t="s">
         <v>67</v>
       </c>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="51"/>
+      <c r="C55" s="73"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="56"/>
-      <c r="B56" s="51"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="51"/>
+      <c r="A56" s="77"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="F28:F31"/>
-    <mergeCell ref="F33:F36"/>
-    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="F48:F51"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:F56"/>
+    <mergeCell ref="A53:F54"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F43:F46"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A39:C41"/>
+    <mergeCell ref="D39:F41"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:F2"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="F9:F12"/>
     <mergeCell ref="A37:A38"/>
     <mergeCell ref="B18:F19"/>
     <mergeCell ref="B37:F38"/>
@@ -36174,23 +36080,11 @@
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A20:F21"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:F2"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="F9:F12"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F43:F46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A39:C41"/>
-    <mergeCell ref="D39:F41"/>
-    <mergeCell ref="F48:F51"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A55:A56"/>
-    <mergeCell ref="B55:F56"/>
-    <mergeCell ref="A53:F54"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="F28:F31"/>
+    <mergeCell ref="F33:F36"/>
+    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/DecompositionLU/docs/version_3.2_statistics.xlsx
+++ b/DecompositionLU/docs/version_3.2_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maxim\source\repos\practice\SECOND_COURSE\FOR_ITLAB\ArchBenchs\DecompositionLU\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2018FAC-222F-4FE2-B106-9B3E02C176BC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAAC7CE-5A6B-4BF5-A722-B8F99D0D9B66}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="79">
   <si>
     <t>Замеры версии 3.2</t>
   </si>
@@ -388,12 +388,36 @@
   <si>
     <t>Сравнение блочного алгоритма и mkl (функция LAPACKE_dgetrf)</t>
   </si>
+  <si>
+    <t>Время (сек)</t>
+  </si>
+  <si>
+    <t>Потоки</t>
+  </si>
+  <si>
+    <t>Eigen 5.0.0</t>
+  </si>
+  <si>
+    <t>Intel MKL 2023.0.0</t>
+  </si>
+  <si>
+    <t>x86</t>
+  </si>
+  <si>
+    <t>RISC-V</t>
+  </si>
+  <si>
+    <t>Тест. Функция</t>
+  </si>
+  <si>
+    <t>Отношение ко времени тест. функции (%)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -501,6 +525,22 @@
     </font>
     <font>
       <sz val="20"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="GOST Common"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="GOST Common"/>
       <family val="2"/>
@@ -746,7 +786,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -992,6 +1032,37 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2683,16 +2754,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.000378787878788</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.0420972062763108</c:v>
+                  <c:v>4.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.7937465715852987</c:v>
+                  <c:v>5.79</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.5174377224199285</c:v>
+                  <c:v>7.52</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3137,16 +3208,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.000189393939394</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0105243015690777</c:v>
+                  <c:v>1.01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.96562442859754982</c:v>
+                  <c:v>0.97</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.93967971530249106</c:v>
+                  <c:v>0.94</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4299,16 +4370,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.050031234028054</c:v>
+                  <c:v>2.0499999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.1636678200692039</c:v>
+                  <c:v>4.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.0487600536193034</c:v>
+                  <c:v>6.05</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.817020355132092</c:v>
+                  <c:v>7.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4743,16 +4814,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.025015617014027</c:v>
+                  <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.040916955017301</c:v>
+                  <c:v>1.04</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0081266756032172</c:v>
+                  <c:v>1.01</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.9771275443915115</c:v>
+                  <c:v>0.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5325,12 +5396,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5338,12 +5406,18 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU" baseline="0">
+              <a:rPr lang="ru-RU" sz="1600" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000"/>
+                </a:solidFill>
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:t>Ускорение</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" baseline="0">
+            <a:endParaRPr lang="en-US" sz="1600" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
               <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:endParaRPr>
           </a:p>
@@ -5362,12 +5436,9 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5387,6 +5458,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Целевое значение</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -5477,6 +5551,9 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>Результаты измерений</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -5501,6 +5578,165 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.416129318403606E-3"/>
+                  <c:y val="2.7975619357869849E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-3545-4A2F-83DA-F59F9BF5313D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.4161293184035808E-3"/>
+                  <c:y val="3.1972136408994115E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-3545-4A2F-83DA-F59F9BF5313D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.0832258636807162E-2"/>
+                  <c:y val="3.996517051124264E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-3545-4A2F-83DA-F59F9BF5313D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.3540323296009052E-2"/>
+                  <c:y val="2.7975619357869776E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-3545-4A2F-83DA-F59F9BF5313D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.0832258636807261E-2"/>
+                  <c:y val="2.7975619357869849E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-3545-4A2F-83DA-F59F9BF5313D}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="800080"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Графики!$B$85:$B$89</c:f>
@@ -5535,16 +5771,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.050031234028054</c:v>
+                  <c:v>2.0499999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.1636678200692039</c:v>
+                  <c:v>4.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.0487600536193034</c:v>
+                  <c:v>6.05</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.817020355132092</c:v>
+                  <c:v>7.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5674,10 +5910,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5699,6 +5932,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -6448,16 +6712,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0362494586401039</c:v>
+                  <c:v>1.04</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0571397914615366</c:v>
+                  <c:v>1.06</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0257149856084267</c:v>
+                  <c:v>1.03</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0036974447480704</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8664,7 +8928,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -8677,12 +8941,18 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU" baseline="0">
+              <a:rPr lang="ru-RU" sz="1600" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
                 <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:t>Ускорение</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US" baseline="0">
+            <a:endParaRPr lang="en-US" sz="1600" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
               <a:latin typeface="GOST Common" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:endParaRPr>
           </a:p>
@@ -8701,7 +8971,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -8719,7 +8989,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.4850806587339424E-2"/>
+          <c:y val="0.10815500486112276"/>
+          <c:w val="0.89305011063120499"/>
+          <c:h val="0.73859076680020785"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -8855,6 +9135,9 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:v>Результаты измерений</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
@@ -8879,6 +9162,237 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-2.7055965797850605E-3"/>
+                  <c:y val="1.3305228221331948E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.4111931595701209E-3"/>
+                  <c:y val="1.6631535276664933E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.4059806321166328E-3"/>
+                  <c:y val="2.3284149387330907E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.108970948175049E-3"/>
+                  <c:y val="3.3263070553329867E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-8.1089072926267738E-3"/>
+                  <c:y val="1.3305228221331948E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.3514951580291682E-2"/>
+                  <c:y val="3.3263070553329867E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.0817273380721752E-2"/>
+                  <c:y val="1.3305228221331948E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.3522869960506811E-2"/>
+                  <c:y val="1.9957842331997922E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-81E6-47B7-B7E5-348F3FE15B17}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="C00000"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ru-RU"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Графики!$B$49:$B$59</c:f>
@@ -8931,34 +9445,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.0261800000000001</c:v>
+                  <c:v>2.0299999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.9546399999999999</c:v>
+                  <c:v>3.95</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.74735</c:v>
+                  <c:v>5.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.9925699999999997</c:v>
+                  <c:v>6.99</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>8.5714199999999998</c:v>
+                  <c:v>8.57</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.373279999999999</c:v>
+                  <c:v>10.37</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>11.12982</c:v>
+                  <c:v>11.13</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.506640000000001</c:v>
+                  <c:v>12.51</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.94553</c:v>
+                  <c:v>12.95</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>14.072699999999999</c:v>
+                  <c:v>14.07</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9026,10 +9540,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -9089,10 +9600,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -9115,6 +9623,37 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -9871,34 +10410,34 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.01309</c:v>
+                  <c:v>1.0149999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.98865999999999998</c:v>
+                  <c:v>0.98750000000000004</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.95789000000000002</c:v>
+                  <c:v>0.95833000000000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.87407000000000001</c:v>
+                  <c:v>0.87375000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.85714000000000001</c:v>
+                  <c:v>0.85699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.86443999999999999</c:v>
+                  <c:v>0.86416999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.79498999999999997</c:v>
+                  <c:v>0.79500000000000004</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.78166999999999998</c:v>
+                  <c:v>0.78188000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.71919999999999995</c:v>
+                  <c:v>0.71943999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.70364000000000004</c:v>
+                  <c:v>0.70350000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -28953,16 +29492,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>244444</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>262550</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>199176</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>208229</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>246708</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>261490</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>253498</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>126749</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -29181,16 +29720,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>391560</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>4526</xdr:rowOff>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>263805</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>149382</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>851025</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>253497</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>322405</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>164974</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -32441,8 +32980,8 @@
         <v>1.9917400000000001</v>
       </c>
       <c r="E50" s="5">
-        <f t="shared" ref="E50:E55" si="3">ROUND(E$35/E36,5)</f>
-        <v>2.0261800000000001</v>
+        <f>ROUND(E$35/E36,2)</f>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8"/>
@@ -32483,8 +33022,8 @@
         <v>3.7831700000000001</v>
       </c>
       <c r="E51" s="5">
-        <f t="shared" si="3"/>
-        <v>3.9546399999999999</v>
+        <f t="shared" ref="E51:E60" si="3">ROUND(E$35/E37,2)</f>
+        <v>3.95</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8"/>
@@ -32526,7 +33065,7 @@
       </c>
       <c r="E52" s="5">
         <f t="shared" si="3"/>
-        <v>5.74735</v>
+        <v>5.75</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8"/>
@@ -32566,9 +33105,9 @@
         <f>ROUND(D35/D39,5)</f>
         <v>6.7245600000000003</v>
       </c>
-      <c r="E53" s="14">
+      <c r="E53" s="5">
         <f t="shared" si="3"/>
-        <v>6.9925699999999997</v>
+        <v>6.99</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8"/>
@@ -32610,7 +33149,7 @@
       </c>
       <c r="E54" s="5">
         <f t="shared" si="3"/>
-        <v>8.5714199999999998</v>
+        <v>8.57</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8"/>
@@ -32652,7 +33191,7 @@
       </c>
       <c r="E55" s="5">
         <f t="shared" si="3"/>
-        <v>10.373279999999999</v>
+        <v>10.37</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8"/>
@@ -32689,12 +33228,12 @@
         <v>9.9085900000000002</v>
       </c>
       <c r="D56" s="5">
-        <f t="shared" ref="D56:E60" si="4">ROUND(D$35/D42,5)</f>
+        <f t="shared" ref="D56:D60" si="4">ROUND(D$35/D42,5)</f>
         <v>10.163349999999999</v>
       </c>
       <c r="E56" s="5">
-        <f t="shared" si="4"/>
-        <v>11.12982</v>
+        <f t="shared" si="3"/>
+        <v>11.13</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8"/>
@@ -32735,8 +33274,8 @@
         <v>10.827249999999999</v>
       </c>
       <c r="E57" s="5">
-        <f t="shared" si="4"/>
-        <v>12.506640000000001</v>
+        <f t="shared" si="3"/>
+        <v>12.51</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -32777,8 +33316,8 @@
         <v>11.587109999999999</v>
       </c>
       <c r="E58" s="5">
-        <f t="shared" si="4"/>
-        <v>12.94553</v>
+        <f t="shared" si="3"/>
+        <v>12.95</v>
       </c>
       <c r="F58" s="8"/>
       <c r="G58" s="8"/>
@@ -32819,8 +33358,8 @@
         <v>12.16165</v>
       </c>
       <c r="E59" s="5">
-        <f t="shared" si="4"/>
-        <v>14.072699999999999</v>
+        <f t="shared" si="3"/>
+        <v>14.07</v>
       </c>
       <c r="F59" s="8"/>
       <c r="G59" s="8"/>
@@ -32860,9 +33399,9 @@
         <f t="shared" si="4"/>
         <v>11.54612</v>
       </c>
-      <c r="E60" s="11">
-        <f t="shared" si="4"/>
-        <v>13.635910000000001</v>
+      <c r="E60" s="5">
+        <f t="shared" si="3"/>
+        <v>13.64</v>
       </c>
       <c r="F60" s="8"/>
       <c r="G60" s="8"/>
@@ -33018,7 +33557,7 @@
       </c>
       <c r="E64" s="5">
         <f t="shared" si="5"/>
-        <v>1.01309</v>
+        <v>1.0149999999999999</v>
       </c>
       <c r="F64" s="8"/>
       <c r="G64" s="8"/>
@@ -33060,7 +33599,7 @@
       </c>
       <c r="E65" s="5">
         <f t="shared" si="5"/>
-        <v>0.98865999999999998</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="F65" s="8"/>
       <c r="G65" s="8"/>
@@ -33102,7 +33641,7 @@
       </c>
       <c r="E66" s="5">
         <f t="shared" si="5"/>
-        <v>0.95789000000000002</v>
+        <v>0.95833000000000002</v>
       </c>
       <c r="F66" s="8"/>
       <c r="G66" s="8"/>
@@ -33144,7 +33683,7 @@
       </c>
       <c r="E67" s="14">
         <f t="shared" si="5"/>
-        <v>0.87407000000000001</v>
+        <v>0.87375000000000003</v>
       </c>
       <c r="F67" s="8"/>
       <c r="G67" s="8"/>
@@ -33186,7 +33725,7 @@
       </c>
       <c r="E68" s="5">
         <f t="shared" si="5"/>
-        <v>0.85714000000000001</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
@@ -33228,7 +33767,7 @@
       </c>
       <c r="E69" s="5">
         <f t="shared" si="5"/>
-        <v>0.86443999999999999</v>
+        <v>0.86416999999999999</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -33270,7 +33809,7 @@
       </c>
       <c r="E70" s="5">
         <f t="shared" si="5"/>
-        <v>0.79498999999999997</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
@@ -33312,7 +33851,7 @@
       </c>
       <c r="E71" s="5">
         <f t="shared" si="5"/>
-        <v>0.78166999999999998</v>
+        <v>0.78188000000000002</v>
       </c>
       <c r="F71" s="8"/>
       <c r="G71" s="8"/>
@@ -33354,7 +33893,7 @@
       </c>
       <c r="E72" s="5">
         <f t="shared" si="5"/>
-        <v>0.71919999999999995</v>
+        <v>0.71943999999999997</v>
       </c>
       <c r="F72" s="8"/>
       <c r="G72" s="8"/>
@@ -33397,7 +33936,7 @@
       </c>
       <c r="E73" s="5">
         <f t="shared" si="5"/>
-        <v>0.70364000000000004</v>
+        <v>0.70350000000000001</v>
       </c>
       <c r="F73" s="8"/>
       <c r="G73" s="8"/>
@@ -33440,7 +33979,7 @@
       </c>
       <c r="E74" s="11">
         <f t="shared" si="5"/>
-        <v>0.34089999999999998</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="F74" s="8"/>
       <c r="G74" s="8"/>
@@ -33854,15 +34393,15 @@
         <v>1</v>
       </c>
       <c r="C85" s="5">
-        <f>C78/C78</f>
+        <f>ROUND(C$78/C78,2)</f>
         <v>1</v>
       </c>
       <c r="D85" s="5">
-        <f>D78/D78</f>
+        <f>ROUND(D$78/D78,2)</f>
         <v>1</v>
       </c>
       <c r="E85" s="5">
-        <f>E78/E78</f>
+        <f>ROUND(E$78/E78,2)</f>
         <v>1</v>
       </c>
       <c r="F85" s="2"/>
@@ -33896,16 +34435,16 @@
         <v>2</v>
       </c>
       <c r="C86" s="5">
-        <f>C78/C79</f>
-        <v>2.000378787878788</v>
+        <f t="shared" ref="C86:D89" si="6">ROUND(C$78/C79,2)</f>
+        <v>2</v>
       </c>
       <c r="D86" s="5">
-        <f>D78/D79</f>
-        <v>2.050031234028054</v>
+        <f t="shared" si="6"/>
+        <v>2.0499999999999998</v>
       </c>
       <c r="E86" s="5">
-        <f>E78/E79</f>
-        <v>2.0724989172802077</v>
+        <f t="shared" ref="E86" si="7">ROUND(E$78/E79,2)</f>
+        <v>2.0699999999999998</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -33938,16 +34477,16 @@
         <v>4</v>
       </c>
       <c r="C87" s="5">
-        <f>C78/C80</f>
-        <v>4.0420972062763108</v>
+        <f t="shared" si="6"/>
+        <v>4.04</v>
       </c>
       <c r="D87" s="5">
-        <f>D78/D80</f>
-        <v>4.1636678200692039</v>
+        <f t="shared" si="6"/>
+        <v>4.16</v>
       </c>
       <c r="E87" s="5">
-        <f>E78/E80</f>
-        <v>4.2285591658461463</v>
+        <f t="shared" ref="E87" si="8">ROUND(E$78/E80,2)</f>
+        <v>4.2300000000000004</v>
       </c>
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
@@ -33980,16 +34519,16 @@
         <v>6</v>
       </c>
       <c r="C88" s="5">
-        <f>C78/C81</f>
-        <v>5.7937465715852987</v>
+        <f t="shared" si="6"/>
+        <v>5.79</v>
       </c>
       <c r="D88" s="5">
-        <f>D78/D81</f>
-        <v>6.0487600536193034</v>
+        <f t="shared" si="6"/>
+        <v>6.05</v>
       </c>
       <c r="E88" s="5">
-        <f>E78/E81</f>
-        <v>6.15428991365056</v>
+        <f t="shared" ref="E88" si="9">ROUND(E$78/E81,2)</f>
+        <v>6.15</v>
       </c>
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
@@ -34021,17 +34560,17 @@
       <c r="B89" s="15">
         <v>8</v>
       </c>
-      <c r="C89" s="14">
-        <f>C78/C82</f>
-        <v>7.5174377224199285</v>
-      </c>
-      <c r="D89" s="14">
-        <f>D78/D82</f>
-        <v>7.817020355132092</v>
-      </c>
-      <c r="E89" s="14">
-        <f>E78/E82</f>
-        <v>8.0295795579845635</v>
+      <c r="C89" s="5">
+        <f t="shared" si="6"/>
+        <v>7.52</v>
+      </c>
+      <c r="D89" s="5">
+        <f t="shared" si="6"/>
+        <v>7.82</v>
+      </c>
+      <c r="E89" s="5">
+        <f t="shared" ref="E89" si="10">ROUND(E$78/E82,2)</f>
+        <v>8.0299999999999994</v>
       </c>
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
@@ -34136,15 +34675,15 @@
         <v>1</v>
       </c>
       <c r="C92" s="5">
-        <f>C85/B85</f>
+        <f>ROUND(C85/$B85,2)</f>
         <v>1</v>
       </c>
       <c r="D92" s="5">
-        <f>D85/B85</f>
+        <f t="shared" ref="D92:E92" si="11">ROUND(D85/$B85,2)</f>
         <v>1</v>
       </c>
       <c r="E92" s="5">
-        <f>E85/B85</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="F92" s="7"/>
@@ -34178,16 +34717,16 @@
         <v>2</v>
       </c>
       <c r="C93" s="5">
-        <f>C86/B86</f>
-        <v>1.000189393939394</v>
+        <f t="shared" ref="C93:E96" si="12">ROUND(C86/$B86,2)</f>
+        <v>1</v>
       </c>
       <c r="D93" s="5">
-        <f>D86/B86</f>
-        <v>1.025015617014027</v>
+        <f t="shared" si="12"/>
+        <v>1.03</v>
       </c>
       <c r="E93" s="5">
-        <f>E86/B86</f>
-        <v>1.0362494586401039</v>
+        <f t="shared" si="12"/>
+        <v>1.04</v>
       </c>
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
@@ -34220,16 +34759,16 @@
         <v>4</v>
       </c>
       <c r="C94" s="5">
-        <f>C87/B87</f>
-        <v>1.0105243015690777</v>
+        <f t="shared" si="12"/>
+        <v>1.01</v>
       </c>
       <c r="D94" s="5">
-        <f>D87/B87</f>
-        <v>1.040916955017301</v>
+        <f t="shared" si="12"/>
+        <v>1.04</v>
       </c>
       <c r="E94" s="5">
-        <f>E87/B87</f>
-        <v>1.0571397914615366</v>
+        <f t="shared" si="12"/>
+        <v>1.06</v>
       </c>
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
@@ -34262,16 +34801,16 @@
         <v>6</v>
       </c>
       <c r="C95" s="5">
-        <f>C88/B88</f>
-        <v>0.96562442859754982</v>
+        <f t="shared" si="12"/>
+        <v>0.97</v>
       </c>
       <c r="D95" s="5">
-        <f>D88/B88</f>
-        <v>1.0081266756032172</v>
+        <f t="shared" si="12"/>
+        <v>1.01</v>
       </c>
       <c r="E95" s="5">
-        <f>E88/B88</f>
-        <v>1.0257149856084267</v>
+        <f t="shared" si="12"/>
+        <v>1.03</v>
       </c>
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
@@ -34303,17 +34842,17 @@
       <c r="B96" s="15">
         <v>8</v>
       </c>
-      <c r="C96" s="14">
-        <f>C89/B89</f>
-        <v>0.93967971530249106</v>
-      </c>
-      <c r="D96" s="14">
-        <f>D89/B89</f>
-        <v>0.9771275443915115</v>
-      </c>
-      <c r="E96" s="14">
-        <f>E89/B89</f>
-        <v>1.0036974447480704</v>
+      <c r="C96" s="5">
+        <f t="shared" si="12"/>
+        <v>0.94</v>
+      </c>
+      <c r="D96" s="5">
+        <f t="shared" si="12"/>
+        <v>0.98</v>
+      </c>
+      <c r="E96" s="5">
+        <f t="shared" si="12"/>
+        <v>1</v>
       </c>
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
@@ -36209,13 +36748,13 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="F43:F46"/>
     <mergeCell ref="F48:F51"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B55:F56"/>
     <mergeCell ref="A53:F54"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="F43:F46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -36225,48 +36764,368 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD84C2DD-E92E-448E-A6C4-C16BE6E2144A}">
-  <dimension ref="A1:A402"/>
+  <dimension ref="E1:AA402"/>
   <sheetFormatPr defaultRowHeight="13.55" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="17.7109375" style="1" customWidth="1"/>
+    <col min="2" max="3" width="10.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="1" customWidth="1"/>
+    <col min="5" max="6" width="17.7109375" style="1" customWidth="1"/>
+    <col min="7" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="9.140625" style="1"/>
+    <col min="19" max="19" width="20.7109375" style="1" customWidth="1"/>
+    <col min="20" max="23" width="10.7109375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="20.7109375" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="3" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="4" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="10" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="11" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="13" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="93" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="93"/>
+    </row>
+    <row r="4" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6">
+        <f>ROUND(L5/1000,2)</f>
+        <v>144.97999999999999</v>
+      </c>
+      <c r="L5" s="6">
+        <v>144977</v>
+      </c>
+    </row>
+    <row r="6" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" ref="F6:F16" si="0">ROUND(L6/1000,2)</f>
+        <v>71.55</v>
+      </c>
+      <c r="L6" s="6">
+        <v>71552</v>
+      </c>
+    </row>
+    <row r="7" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>36.659999999999997</v>
+      </c>
+      <c r="L7" s="6">
+        <v>36660</v>
+      </c>
+    </row>
+    <row r="8" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E8" s="4">
+        <v>6</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>25.23</v>
+      </c>
+      <c r="L8" s="6">
+        <v>25225</v>
+      </c>
+    </row>
+    <row r="9" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E9" s="13">
+        <v>8</v>
+      </c>
+      <c r="F9" s="46">
+        <f t="shared" si="0"/>
+        <v>20.73</v>
+      </c>
+      <c r="L9" s="46">
+        <v>20733</v>
+      </c>
+    </row>
+    <row r="10" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E10" s="4">
+        <v>10</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>16.91</v>
+      </c>
+      <c r="L10" s="6">
+        <v>16914</v>
+      </c>
+    </row>
+    <row r="11" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E11" s="4">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="0"/>
+        <v>13.98</v>
+      </c>
+      <c r="L11" s="6">
+        <v>13976</v>
+      </c>
+    </row>
+    <row r="12" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E12" s="4">
+        <v>14</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="0"/>
+        <v>13.03</v>
+      </c>
+      <c r="L12" s="6">
+        <v>13026</v>
+      </c>
+    </row>
+    <row r="13" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E13" s="4">
+        <v>16</v>
+      </c>
+      <c r="F13" s="6">
+        <f t="shared" si="0"/>
+        <v>11.59</v>
+      </c>
+      <c r="L13" s="6">
+        <v>11592</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E14" s="4">
+        <v>18</v>
+      </c>
+      <c r="F14" s="6">
+        <f t="shared" si="0"/>
+        <v>11.2</v>
+      </c>
+      <c r="L14" s="6">
+        <v>11199</v>
+      </c>
+    </row>
+    <row r="15" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E15" s="4">
+        <v>20</v>
+      </c>
+      <c r="F15" s="6">
+        <f t="shared" si="0"/>
+        <v>10.3</v>
+      </c>
+      <c r="L15" s="6">
+        <v>10302</v>
+      </c>
+    </row>
+    <row r="16" spans="5:12" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E16" s="10">
+        <v>40</v>
+      </c>
+      <c r="F16" s="12">
+        <f t="shared" si="0"/>
+        <v>10.63</v>
+      </c>
+      <c r="L16" s="12">
+        <v>10632</v>
+      </c>
+    </row>
+    <row r="17" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E20" s="94"/>
+      <c r="S20" s="103" t="s">
+        <v>6</v>
+      </c>
+      <c r="T20" s="97" t="s">
+        <v>77</v>
+      </c>
+      <c r="U20" s="97"/>
+      <c r="V20" s="97" t="s">
+        <v>73</v>
+      </c>
+      <c r="W20" s="97"/>
+      <c r="X20" s="98" t="s">
+        <v>74</v>
+      </c>
+      <c r="Z20" s="21"/>
+      <c r="AA20" s="21"/>
+    </row>
+    <row r="21" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S21" s="103"/>
+      <c r="T21" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="U21" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="V21" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="W21" s="98" t="s">
+        <v>76</v>
+      </c>
+      <c r="X21" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z21" s="21"/>
+      <c r="AA21" s="21"/>
+    </row>
+    <row r="22" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S22" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="T22" s="95">
+        <v>513</v>
+      </c>
+      <c r="U22" s="95">
+        <v>20892</v>
+      </c>
+      <c r="V22" s="95">
+        <v>421</v>
+      </c>
+      <c r="W22" s="95">
+        <v>26675</v>
+      </c>
+      <c r="X22" s="95">
+        <v>227</v>
+      </c>
+      <c r="Z22" s="96"/>
+      <c r="AA22" s="21"/>
+    </row>
+    <row r="23" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S23" s="97"/>
+      <c r="T23" s="95"/>
+      <c r="U23" s="95"/>
+      <c r="V23" s="95"/>
+      <c r="W23" s="95"/>
+      <c r="X23" s="95"/>
+      <c r="Z23" s="96"/>
+      <c r="AA23" s="21"/>
+    </row>
+    <row r="24" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S24" s="99" t="s">
+        <v>78</v>
+      </c>
+      <c r="T24" s="102">
+        <v>100</v>
+      </c>
+      <c r="U24" s="102"/>
+      <c r="V24" s="100">
+        <f>ROUND(V22*100/T22,2)</f>
+        <v>82.07</v>
+      </c>
+      <c r="W24" s="101">
+        <f>ROUND(W22*100/U22,2)</f>
+        <v>127.68</v>
+      </c>
+      <c r="X24" s="100">
+        <f>ROUND(X22*100/T22,2)</f>
+        <v>44.25</v>
+      </c>
+      <c r="Z24" s="96"/>
+      <c r="AA24" s="21"/>
+    </row>
+    <row r="25" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S25" s="99"/>
+      <c r="T25" s="102"/>
+      <c r="U25" s="102"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="101"/>
+      <c r="X25" s="100"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+    </row>
+    <row r="26" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+    </row>
+    <row r="27" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O28" s="6">
+        <v>167489</v>
+      </c>
+    </row>
+    <row r="29" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="93" t="s">
+        <v>6</v>
+      </c>
+      <c r="G29" s="93"/>
+      <c r="H29" s="93"/>
+      <c r="I29" s="93"/>
+      <c r="J29" s="93"/>
+      <c r="K29" s="93"/>
+      <c r="O29" s="6">
+        <v>80815</v>
+      </c>
+    </row>
+    <row r="30" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="4">
+        <v>2</v>
+      </c>
+      <c r="I30" s="4">
+        <v>4</v>
+      </c>
+      <c r="J30" s="4">
+        <v>6</v>
+      </c>
+      <c r="K30" s="13">
+        <v>8</v>
+      </c>
+      <c r="O30" s="6">
+        <v>39609</v>
+      </c>
+    </row>
+    <row r="31" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" s="6">
+        <f>ROUND(O28/1000,2)</f>
+        <v>167.49</v>
+      </c>
+      <c r="H31" s="6">
+        <f>ROUND(O29/1000,2)</f>
+        <v>80.819999999999993</v>
+      </c>
+      <c r="I31" s="6">
+        <f>ROUND(O30/1000,2)</f>
+        <v>39.61</v>
+      </c>
+      <c r="J31" s="6">
+        <f>ROUND(O31/1000,2)</f>
+        <v>27.22</v>
+      </c>
+      <c r="K31" s="46">
+        <f>ROUND(O32/1000,2)</f>
+        <v>20.86</v>
+      </c>
+      <c r="O31" s="6">
+        <v>27215</v>
+      </c>
+    </row>
+    <row r="32" spans="5:27" ht="20" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O32" s="46">
+        <v>20859</v>
+      </c>
+    </row>
     <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -36638,6 +37497,24 @@
     <row r="401" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="402" ht="20" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="T24:U25"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="F29:K29"/>
+    <mergeCell ref="S24:S25"/>
+    <mergeCell ref="V20:W20"/>
+    <mergeCell ref="V24:V25"/>
+    <mergeCell ref="W24:W25"/>
+    <mergeCell ref="X24:X25"/>
+    <mergeCell ref="S22:S23"/>
+    <mergeCell ref="V22:V23"/>
+    <mergeCell ref="W22:W23"/>
+    <mergeCell ref="X22:X23"/>
+    <mergeCell ref="S20:S21"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="T22:T23"/>
+    <mergeCell ref="U22:U23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
